--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -1504,13 +1504,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.550923449075</v>
+        <v>46073.717590115746</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.557950358794</v>
+        <v>46092.724617025466</v>
       </c>
       <c r="D4" s="5">
-        <v>46114.64592623843</v>
+        <v>46114.81259290509</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1553,13 +1553,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.550924131945</v>
+        <v>46073.71759079861</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55791815972</v>
+        <v>46092.724584826385</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55795128472</v>
+        <v>46092.72461795139</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1618,13 +1618,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.55092440972</v>
+        <v>46073.71759107639</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.557918680555</v>
+        <v>46092.72458534723</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55795116899</v>
+        <v>46092.72461783564</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1683,13 +1683,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.5509246875</v>
+        <v>46073.717591354165</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.5579190625</v>
+        <v>46092.72458572917</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.55795108796</v>
+        <v>46092.72461775463</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1746,13 +1746,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.5509249537</v>
+        <v>46073.71759162037</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.557919467596</v>
+        <v>46092.72458613426</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.5441077662</v>
+        <v>46100.71077443287</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1809,13 +1809,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.55092523148</v>
+        <v>46073.71759189815</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55792006945</v>
+        <v>46092.72458673611</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.557950636576</v>
+        <v>46092.72461730324</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1872,11 +1872,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.55092548611</v>
+        <v>46073.71759215278</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.35971239583</v>
+        <v>46097.5263790625</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1919,13 +1919,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.55092579861</v>
+        <v>46073.71759246528</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.3596971875</v>
+        <v>46097.526363854166</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.359716226856</v>
+        <v>46097.52638289351</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1984,11 +1984,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.55092606481</v>
+        <v>46073.71759273148</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46126.02834039352</v>
+        <v>46126.19500706019</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2047,13 +2047,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.55092631944</v>
+        <v>46073.71759298611</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.34359585648</v>
+        <v>46114.51026252315</v>
       </c>
       <c r="D13" s="8">
-        <v>46169.71771503473</v>
+        <v>46169.884381701384</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2096,13 +2096,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.55092393518</v>
+        <v>46073.71759060185</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.359178321756</v>
+        <v>46097.52584498843</v>
       </c>
       <c r="D14" s="5">
-        <v>46100.59471405092</v>
+        <v>46100.761380717595</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2161,13 +2161,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.55092461806</v>
+        <v>46073.71759128472</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.34212127315</v>
+        <v>46114.50878793982</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.34214091435</v>
+        <v>46114.50880758102</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2226,13 +2226,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.55092490741</v>
+        <v>46073.71759157407</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.34256148148</v>
+        <v>46114.50922814815</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.34257719907</v>
+        <v>46114.509243865745</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2291,13 +2291,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.55092519676</v>
+        <v>46073.71759186343</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34357736111</v>
+        <v>46114.51024402778</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.34359680556</v>
+        <v>46114.51026347222</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2356,13 +2356,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.55092547454</v>
+        <v>46073.717592141205</v>
       </c>
       <c r="C18" s="5">
-        <v>46169.71758038194</v>
+        <v>46169.88424704861</v>
       </c>
       <c r="D18" s="5">
-        <v>46169.71766835648</v>
+        <v>46169.88433502315</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2405,13 +2405,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.55092603009</v>
+        <v>46073.71759269676</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.35928278935</v>
+        <v>46097.525949456016</v>
       </c>
       <c r="D19" s="8">
-        <v>46156.45183452546</v>
+        <v>46156.61850119213</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2470,13 +2470,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.550925752315</v>
+        <v>46073.71759241898</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.35931177084</v>
+        <v>46097.5259784375</v>
       </c>
       <c r="D20" s="5">
-        <v>46156.451852997685</v>
+        <v>46156.61851966435</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2535,13 +2535,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.55092663194</v>
+        <v>46073.717593298614</v>
       </c>
       <c r="C21" s="8">
-        <v>46128.26706200231</v>
+        <v>46128.433728668984</v>
       </c>
       <c r="D21" s="8">
-        <v>46128.26708372685</v>
+        <v>46128.433750393524</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2600,13 +2600,13 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.55092635417</v>
+        <v>46073.71759302083</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.359934479166</v>
+        <v>46097.52660114583</v>
       </c>
       <c r="D22" s="5">
-        <v>46097.35995533565</v>
+        <v>46097.52662200232</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2665,13 +2665,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.42669133102</v>
+        <v>46076.593357997685</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.34365599537</v>
+        <v>46114.51032266204</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.34380563657</v>
+        <v>46114.51047230324</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2730,13 +2730,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.55092366898</v>
+        <v>46073.71759033565</v>
       </c>
       <c r="C24" s="5">
-        <v>46169.717562060185</v>
+        <v>46169.88422872685</v>
       </c>
       <c r="D24" s="5">
-        <v>46169.71758065972</v>
+        <v>46169.884247326394</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2795,11 +2795,11 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.55092405093</v>
+        <v>46073.71759071759</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46182.51639444444</v>
+        <v>46182.68306111111</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2842,13 +2842,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.55092359954</v>
+        <v>46073.7175902662</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.700224722226</v>
+        <v>46155.86689138889</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.70043725694</v>
+        <v>46155.86710392361</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -2907,13 +2907,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.55092391204</v>
+        <v>46073.7175905787</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.35938876157</v>
+        <v>46097.52605542824</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.359390219906</v>
+        <v>46097.52605688658</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>108</v>
@@ -2968,13 +2968,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.550924201394</v>
+        <v>46073.71759086805</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.700210358795</v>
+        <v>46155.86687702546</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.7002115625</v>
+        <v>46155.866878229164</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3029,13 +3029,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.55092451389</v>
+        <v>46073.71759118055</v>
       </c>
       <c r="C29" s="8">
-        <v>46128.47049521991</v>
+        <v>46128.637161886574</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.470505081015</v>
+        <v>46128.63717174769</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3090,13 +3090,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.550924317125</v>
+        <v>46073.7175909838</v>
       </c>
       <c r="C30" s="5">
-        <v>46155.73690275463</v>
+        <v>46155.903569421294</v>
       </c>
       <c r="D30" s="5">
-        <v>46155.73691611111</v>
+        <v>46155.90358277778</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3155,13 +3155,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.55092459491</v>
+        <v>46073.71759126158</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.35941971064</v>
+        <v>46097.526086377315</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.359421354166</v>
+        <v>46097.52608802084</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3216,13 +3216,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.55092487269</v>
+        <v>46073.71759153935</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.73688930555</v>
+        <v>46155.903555972225</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.736890844906</v>
+        <v>46155.90355751157</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3277,13 +3277,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.55092601852</v>
+        <v>46073.717592685185</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.51638877315</v>
+        <v>46182.68305543982</v>
       </c>
       <c r="D33" s="8">
-        <v>46182.51639055555</v>
+        <v>46182.683057222224</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3342,13 +3342,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.55092635417</v>
+        <v>46073.71759302083</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.51607938657</v>
+        <v>46182.68274605324</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.51608083333</v>
+        <v>46182.6827475</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3403,13 +3403,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.550923194445</v>
+        <v>46073.71758986111</v>
       </c>
       <c r="C35" s="8">
-        <v>46182.516275648144</v>
+        <v>46182.682942314816</v>
       </c>
       <c r="D35" s="8">
-        <v>46182.516276875</v>
+        <v>46182.682943541666</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3464,11 +3464,11 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.55092516204</v>
+        <v>46073.7175918287</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.67673070602</v>
+        <v>46169.843397372686</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3527,13 +3527,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.55092542824</v>
+        <v>46073.71759209491</v>
       </c>
       <c r="C37" s="8">
-        <v>46097.35999758102</v>
+        <v>46097.526664247685</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.67663081019</v>
+        <v>46169.84329747685</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3588,11 +3588,11 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.55092568287</v>
+        <v>46073.71759234954</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46183.51964167824</v>
+        <v>46183.686308344906</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3647,13 +3647,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46076.427483680556</v>
+        <v>46076.59415034722</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.70138586806</v>
+        <v>46154.86805253472</v>
       </c>
       <c r="D39" s="8">
-        <v>46156.4519491088</v>
+        <v>46156.618615775464</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3712,13 +3712,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46076.42761490741</v>
+        <v>46076.59428157407</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.70070490741</v>
+        <v>46154.86737157407</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.70070689815</v>
+        <v>46154.86737356482</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3777,13 +3777,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46076.42781732639</v>
+        <v>46076.59448399306</v>
       </c>
       <c r="C41" s="8">
-        <v>46154.70143751157</v>
+        <v>46154.86810417824</v>
       </c>
       <c r="D41" s="8">
-        <v>46154.70143878472</v>
+        <v>46154.86810545139</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3842,13 +3842,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.550924814816</v>
+        <v>46073.71759148148</v>
       </c>
       <c r="C42" s="5">
-        <v>46182.36395186343</v>
+        <v>46182.530618530094</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.36396486111</v>
+        <v>46182.53063152778</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3907,13 +3907,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.5509250926</v>
+        <v>46073.717591759254</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.36380178241</v>
+        <v>46182.53046844907</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.36380388889</v>
+        <v>46182.53047055556</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3968,13 +3968,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.55092538195</v>
+        <v>46073.71759204861</v>
       </c>
       <c r="C44" s="5">
-        <v>46182.363938344904</v>
+        <v>46182.530605011576</v>
       </c>
       <c r="D44" s="5">
-        <v>46182.36393960648</v>
+        <v>46182.53060627315</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4029,11 +4029,11 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.55092568287</v>
+        <v>46073.71759234954</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46156.45203958334</v>
+        <v>46156.618706249996</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4076,13 +4076,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.55092594908</v>
+        <v>46073.717592615736</v>
       </c>
       <c r="C46" s="5">
-        <v>46153.92835325231</v>
+        <v>46154.09501991898</v>
       </c>
       <c r="D46" s="5">
-        <v>46153.92837542824</v>
+        <v>46154.09504209491</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4141,13 +4141,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.550923310184</v>
+        <v>46073.71758997685</v>
       </c>
       <c r="C47" s="8">
-        <v>46153.92841332176</v>
+        <v>46154.09507998843</v>
       </c>
       <c r="D47" s="8">
-        <v>46153.92842795139</v>
+        <v>46154.09509461805</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4206,13 +4206,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46091.56135321759</v>
+        <v>46091.72801988426</v>
       </c>
       <c r="C48" s="5">
-        <v>46153.92845228009</v>
+        <v>46154.09511894676</v>
       </c>
       <c r="D48" s="5">
-        <v>46153.928467199075</v>
+        <v>46154.09513386574</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4271,11 +4271,11 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46091.56139127315</v>
+        <v>46091.728057939814</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46161.03471766204</v>
+        <v>46161.2013843287</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4334,11 +4334,11 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.55092363426</v>
+        <v>46073.71759030093</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46083.50214737268</v>
+        <v>46083.66881403935</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4381,11 +4381,11 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.55092391204</v>
+        <v>46073.7175905787</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46182.36395185185</v>
+        <v>46182.53061851852</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>163</v>
@@ -4444,11 +4444,11 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.55092414352</v>
+        <v>46073.717590810185</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46091.57592502315</v>
+        <v>46091.742591689814</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4507,11 +4507,11 @@
         <v>196</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.55092443287</v>
+        <v>46073.717591099536</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46129.61608821759</v>
+        <v>46129.78275488426</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>197</v>
@@ -4554,11 +4554,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.550924675925</v>
+        <v>46073.71759134259</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46129.61594559028</v>
+        <v>46129.782612256946</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4617,11 +4617,11 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.55092490741</v>
+        <v>46073.71759157407</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46153.92845734954</v>
+        <v>46154.0951240162</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4680,11 +4680,11 @@
         <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.55092515046</v>
+        <v>46073.71759181713</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46153.928458090275</v>
+        <v>46154.09512475695</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>209</v>
@@ -4743,11 +4743,11 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.550925393516</v>
+        <v>46073.71759206019</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46083.502105590276</v>
+        <v>46083.66877225695</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4790,11 +4790,11 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.550924386574</v>
+        <v>46073.71759105324</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46155.70022762731</v>
+        <v>46155.866894293984</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4853,11 +4853,11 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.550924166666</v>
+        <v>46073.71759083333</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46155.736905937505</v>
+        <v>46155.90357260416</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4916,11 +4916,11 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.5509256713</v>
+        <v>46073.71759233796</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46182.51629310186</v>
+        <v>46182.682959768514</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -4979,11 +4979,11 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.55092384259</v>
+        <v>46073.71759050926</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46119.02138759259</v>
+        <v>46119.188054259255</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5042,11 +5042,11 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.432926064816</v>
+        <v>46076.59959273148</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46154.70145581018</v>
+        <v>46154.86812247685</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5105,11 +5105,11 @@
         <v>229</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.550924641204</v>
+        <v>46073.71759130787</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46091.5677984375</v>
+        <v>46091.734465104164</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>230</v>
@@ -5152,11 +5152,11 @@
         <v>232</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.55092488426</v>
+        <v>46073.71759155093</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46126.02834055555</v>
+        <v>46126.195007222224</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>233</v>
@@ -5215,11 +5215,11 @@
         <v>235</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.55092513889</v>
+        <v>46073.71759180556</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46157.00576629629</v>
+        <v>46157.172432962965</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>236</v>
@@ -5278,11 +5278,11 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.55092537037</v>
+        <v>46073.717592037036</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46153.92845952546</v>
+        <v>46154.09512619213</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5341,11 +5341,11 @@
         <v>243</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.550925601856</v>
+        <v>46073.71759226852</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46153.9284600463</v>
+        <v>46154.095126712964</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5404,11 +5404,11 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.43405303241</v>
+        <v>46076.600719699076</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46153.92846060185</v>
+        <v>46154.09512726852</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5467,11 +5467,11 @@
         <v>248</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.550925856485</v>
+        <v>46073.71759252315</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46158.01512278935</v>
+        <v>46158.18178945602</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5530,11 +5530,11 @@
         <v>251</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.55092609954</v>
+        <v>46073.7175927662</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46162.00188083333</v>
+        <v>46162.1685475</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>182</v>
@@ -5593,11 +5593,11 @@
         <v>253</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.55092376158</v>
+        <v>46073.71759042824</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46091.56779943287</v>
+        <v>46091.73446609954</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>254</v>
@@ -5640,11 +5640,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.55092408565</v>
+        <v>46073.71759075232</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46163.03695203704</v>
+        <v>46163.2036187037</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>257</v>
@@ -5703,11 +5703,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.55092435185</v>
+        <v>46073.71759101852</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46168.019966736116</v>
+        <v>46168.18663340277</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5766,11 +5766,11 @@
         <v>263</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.550924641204</v>
+        <v>46073.71759130787</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46169.00187577546</v>
+        <v>46169.16854244213</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>264</v>
@@ -5829,11 +5829,11 @@
         <v>268</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.55092489583</v>
+        <v>46073.7175915625</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46170.031903449075</v>
+        <v>46170.19857011574</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>269</v>
@@ -5890,11 +5890,11 @@
         <v>271</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.55092517361</v>
+        <v>46073.71759184028</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46091.56779884259</v>
+        <v>46091.73446550926</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>272</v>
@@ -5943,11 +5943,11 @@
         <v>274</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.55092543981</v>
+        <v>46073.71759210648</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46179.03319190972</v>
+        <v>46179.199858576394</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>275</v>
@@ -6006,11 +6006,11 @@
         <v>278</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.55092571759</v>
+        <v>46073.71759238426</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46179.03318975694</v>
+        <v>46179.19985642361</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>279</v>
@@ -6069,11 +6069,11 @@
         <v>281</v>
       </c>
       <c r="B79" s="8">
-        <v>46091.561731678245</v>
+        <v>46091.72839834491</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46091.56899111111</v>
+        <v>46091.73565777778</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>282</v>
@@ -6122,11 +6122,11 @@
         <v>284</v>
       </c>
       <c r="B80" s="5">
-        <v>46091.56227415509</v>
+        <v>46091.72894082176</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46179.03318989583</v>
+        <v>46179.199856562496</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>285</v>
@@ -6185,11 +6185,11 @@
         <v>287</v>
       </c>
       <c r="B81" s="8">
-        <v>46091.562334999995</v>
+        <v>46091.72900166667</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46182.01741539352</v>
+        <v>46182.18408206019</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>288</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -6189,7 +6189,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46182.18408206019</v>
+        <v>46189.167653067125</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>288</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -6189,7 +6189,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46189.167653067125</v>
+        <v>46190.17451866898</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>288</v>
@@ -6236,8 +6236,8 @@
       <c r="S81" s="9">
         <v>0</v>
       </c>
-      <c r="T81" s="12" t="s">
-        <v>228</v>
+      <c r="T81" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U81" s="10" t="s">
         <v>56</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="289">
   <si>
     <t xml:space="preserve">50001498-CALABRESSE METRO STO DOMINGO  POZOS  </t>
   </si>
@@ -583,70 +583,70 @@
     <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Bodega:,Bodega:</t>
   </si>
   <si>
+    <t>1213380470331436</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Generacion OC Fabricación externa </t>
+  </si>
+  <si>
+    <t>1213380470331437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa </t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación externa ,Armado fabricación externa ,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213380470331438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion OC Fabricación externa </t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado fabricación externa ,Fabricación externa </t>
+  </si>
+  <si>
+    <t>1213380470331439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado fabricación externa </t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación externa ,Check Planos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Armado,Fabricación externa </t>
+  </si>
+  <si>
+    <t>1213380470331440</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>Armado fabricación externa ,Check Planos</t>
+  </si>
+  <si>
+    <t>Fabricación externa ,Revestimiento</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213380470331436</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Generacion OC Fabricación externa </t>
-  </si>
-  <si>
-    <t>1213380470331437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa </t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación externa ,Armado fabricación externa ,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213380470331438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion OC Fabricación externa </t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado fabricación externa ,Fabricación externa </t>
-  </si>
-  <si>
-    <t>1213380470331439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado fabricación externa </t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación externa ,Check Planos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Armado,Fabricación externa </t>
-  </si>
-  <si>
-    <t>1213380470331440</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>Armado fabricación externa ,Check Planos</t>
-  </si>
-  <si>
-    <t>Fabricación externa ,Revestimiento</t>
   </si>
   <si>
     <t>1213380470331441</t>
@@ -4336,9 +4336,11 @@
       <c r="B50" s="5">
         <v>46073.71759030093</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="5">
+        <v>46191.78929271991</v>
+      </c>
       <c r="D50" s="5">
-        <v>46083.66881403935</v>
+        <v>46191.789304328704</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4372,9 +4374,13 @@
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
-      <c r="S50" s="6"/>
+      <c r="S50" s="6">
+        <v>1</v>
+      </c>
       <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
+      <c r="U50" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
@@ -4383,9 +4389,11 @@
       <c r="B51" s="8">
         <v>46073.7175905787</v>
       </c>
-      <c r="C51" s="9"/>
+      <c r="C51" s="8">
+        <v>46191.788401875005</v>
+      </c>
       <c r="D51" s="8">
-        <v>46182.53061851852</v>
+        <v>46191.788422488426</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>163</v>
@@ -4430,37 +4438,39 @@
         <v>46070</v>
       </c>
       <c r="S51" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U51" s="12" t="s">
-        <v>190</v>
+      <c r="U51" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5">
         <v>46073.717590810185</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46191.78927659722</v>
+      </c>
       <c r="D52" s="5">
-        <v>46091.742591689814</v>
+        <v>46191.789293194444</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I52" s="5">
         <v>46071</v>
@@ -4484,7 +4494,7 @@
         <v>163</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="5">
         <v>46071</v>
@@ -4493,28 +4503,30 @@
         <v>46072</v>
       </c>
       <c r="S52" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T52" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U52" s="10" t="s">
-        <v>56</v>
+      <c r="U52" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B53" s="8">
         <v>46073.717591099536</v>
       </c>
-      <c r="C53" s="9"/>
+      <c r="C53" s="8">
+        <v>46191.79037481482</v>
+      </c>
       <c r="D53" s="8">
-        <v>46129.78275488426</v>
+        <v>46191.79038505787</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4538,39 +4550,45 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
-      <c r="S53" s="9"/>
+      <c r="S53" s="9">
+        <v>1</v>
+      </c>
       <c r="T53" s="9"/>
-      <c r="U53" s="9"/>
+      <c r="U53" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46073.71759134259</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46191.7899369213</v>
+      </c>
       <c r="D54" s="5">
-        <v>46129.782612256946</v>
+        <v>46191.7899528125</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I54" s="5">
         <v>46073</v>
@@ -4588,13 +4606,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q54" s="5">
         <v>46073</v>
@@ -4603,37 +4621,39 @@
         <v>46083</v>
       </c>
       <c r="S54" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U54" s="10" t="s">
-        <v>56</v>
+      <c r="U54" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B55" s="8">
         <v>46073.71759157407</v>
       </c>
-      <c r="C55" s="9"/>
+      <c r="C55" s="8">
+        <v>46191.79035826389</v>
+      </c>
       <c r="D55" s="8">
-        <v>46154.0951240162</v>
+        <v>46191.790375833334</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>201</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>202</v>
       </c>
       <c r="I55" s="8">
         <v>46084</v>
@@ -4651,13 +4671,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O55" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="P55" s="9" t="s">
         <v>206</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="Q55" s="8">
         <v>46084</v>
@@ -4666,37 +4686,39 @@
         <v>46101</v>
       </c>
       <c r="S55" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U55" s="10" t="s">
-        <v>56</v>
+      <c r="U55" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46073.71759181713</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46191.789681423616</v>
+      </c>
       <c r="D56" s="5">
-        <v>46154.09512475695</v>
+        <v>46191.79037549769</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I56" s="5">
         <v>46104</v>
@@ -4714,13 +4736,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="Q56" s="5">
         <v>46104</v>
@@ -4729,13 +4751,13 @@
         <v>46105</v>
       </c>
       <c r="S56" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U56" s="10" t="s">
-        <v>56</v>
+      <c r="U56" s="12" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4747,7 +4769,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46083.66877225695</v>
+        <v>46191.7884132176</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4845,7 +4867,7 @@
         <v>31</v>
       </c>
       <c r="U58" s="12" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4908,7 +4930,7 @@
         <v>31</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -4971,7 +4993,7 @@
         <v>31</v>
       </c>
       <c r="U60" s="12" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5097,7 +5119,7 @@
         <v>228</v>
       </c>
       <c r="U62" s="12" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5156,7 +5178,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46126.195007222224</v>
+        <v>46191.78969853009</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>233</v>
@@ -5189,7 +5211,7 @@
         <v>230</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>234</v>
@@ -5206,8 +5228,8 @@
       <c r="T64" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U64" s="10" t="s">
-        <v>56</v>
+      <c r="U64" s="12" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="289">
   <si>
     <t xml:space="preserve">50001498-CALABRESSE METRO STO DOMINGO  POZOS  </t>
   </si>
@@ -319,6 +319,9 @@
     <t>Alabe,Tablero OT 4201,rodete OT 4200,Motor,Sensores,Materiales a codigo // compras locales aprovisionamientomiento:OT  4200</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1213380470331424</t>
   </si>
   <si>
@@ -644,9 +647,6 @@
   </si>
   <si>
     <t>Fabricación externa ,Revestimiento</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213380470331441</t>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46182.68306111111</v>
+        <v>46191.88830023148</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2835,11 +2835,13 @@
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
       <c r="T25" s="9"/>
-      <c r="U25" s="9"/>
+      <c r="U25" s="12" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B26" s="5">
         <v>46073.7175902662</v>
@@ -2851,16 +2853,16 @@
         <v>46155.86710392361</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I26" s="5">
         <v>46006</v>
@@ -2881,7 +2883,7 @@
         <v>100</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>100</v>
@@ -2904,7 +2906,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="8">
         <v>46073.7175905787</v>
@@ -2916,16 +2918,16 @@
         <v>46097.52605688658</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I27" s="8">
         <v>46006</v>
@@ -2943,13 +2945,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>79</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2957,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U27" s="10" t="s">
         <v>56</v>
@@ -2965,7 +2967,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46073.71759086805</v>
@@ -2977,16 +2979,16 @@
         <v>46155.866878229164</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I28" s="5">
         <v>46027</v>
@@ -3004,13 +3006,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3018,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U28" s="10" t="s">
         <v>56</v>
@@ -3026,7 +3028,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="8">
         <v>46073.71759118055</v>
@@ -3038,16 +3040,16 @@
         <v>46128.63717174769</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I29" s="8">
         <v>46027</v>
@@ -3065,13 +3067,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3079,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U29" s="10" t="s">
         <v>56</v>
@@ -3087,7 +3089,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46073.7175909838</v>
@@ -3099,16 +3101,16 @@
         <v>46155.90358277778</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I30" s="5">
         <v>46013</v>
@@ -3129,7 +3131,7 @@
         <v>100</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>100</v>
@@ -3152,7 +3154,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="8">
         <v>46073.71759126158</v>
@@ -3164,16 +3166,16 @@
         <v>46097.52608802084</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I31" s="8">
         <v>46013</v>
@@ -3191,13 +3193,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>82</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3205,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U31" s="10" t="s">
         <v>56</v>
@@ -3213,7 +3215,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46073.71759153935</v>
@@ -3225,16 +3227,16 @@
         <v>46155.90355751157</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I32" s="5">
         <v>46017</v>
@@ -3252,13 +3254,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3266,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U32" s="10" t="s">
         <v>56</v>
@@ -3274,7 +3276,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="8">
         <v>46073.717592685185</v>
@@ -3286,16 +3288,16 @@
         <v>46182.683057222224</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I33" s="8">
         <v>46013</v>
@@ -3316,7 +3318,7 @@
         <v>100</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>100</v>
@@ -3339,7 +3341,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46073.71759302083</v>
@@ -3351,16 +3353,16 @@
         <v>46182.6827475</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I34" s="5">
         <v>46013</v>
@@ -3378,13 +3380,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3392,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U34" s="10" t="s">
         <v>56</v>
@@ -3400,7 +3402,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B35" s="8">
         <v>46073.71758986111</v>
@@ -3412,16 +3414,16 @@
         <v>46182.682943541666</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I35" s="8">
         <v>46017</v>
@@ -3439,13 +3441,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3453,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U35" s="10" t="s">
         <v>56</v>
@@ -3461,26 +3463,28 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46073.7175918287</v>
       </c>
-      <c r="C36" s="6"/>
+      <c r="C36" s="5">
+        <v>46191.888280127314</v>
+      </c>
       <c r="D36" s="5">
-        <v>46169.843397372686</v>
+        <v>46191.89070638889</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I36" s="5">
         <v>46007</v>
@@ -3501,7 +3505,7 @@
         <v>100</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>100</v>
@@ -3513,18 +3517,18 @@
         <v>46114</v>
       </c>
       <c r="S36" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U36" s="10" t="s">
-        <v>56</v>
+      <c r="U36" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" s="8">
         <v>46073.71759209491</v>
@@ -3536,16 +3540,16 @@
         <v>46169.84329747685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I37" s="8">
         <v>46007</v>
@@ -3563,13 +3567,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>89</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3577,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U37" s="10" t="s">
         <v>56</v>
@@ -3585,26 +3589,26 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46073.71759234954</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46183.686308344906</v>
+        <v>46191.88833190972</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I38" s="5">
         <v>46017</v>
@@ -3622,13 +3626,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3636,7 +3640,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U38" s="10" t="s">
         <v>56</v>
@@ -3644,7 +3648,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="8">
         <v>46076.59415034722</v>
@@ -3656,16 +3660,16 @@
         <v>46156.618615775464</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I39" s="8">
         <v>46013</v>
@@ -3686,7 +3690,7 @@
         <v>100</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>100</v>
@@ -3709,7 +3713,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46076.59428157407</v>
@@ -3721,16 +3725,16 @@
         <v>46154.86737356482</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46013</v>
@@ -3748,13 +3752,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>92</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="5">
         <v>46013</v>
@@ -3766,7 +3770,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U40" s="10" t="s">
         <v>56</v>
@@ -3774,7 +3778,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="8">
         <v>46076.59448399306</v>
@@ -3786,16 +3790,16 @@
         <v>46154.86810545139</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I41" s="8">
         <v>46057</v>
@@ -3813,13 +3817,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="8">
         <v>46057</v>
@@ -3831,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U41" s="10" t="s">
         <v>56</v>
@@ -3839,7 +3843,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46073.71759148148</v>
@@ -3851,16 +3855,16 @@
         <v>46182.53063152778</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I42" s="5">
         <v>46013</v>
@@ -3881,7 +3885,7 @@
         <v>100</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>100</v>
@@ -3904,7 +3908,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46073.717591759254</v>
@@ -3916,16 +3920,16 @@
         <v>46182.53047055556</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I43" s="8">
         <v>46013</v>
@@ -3943,13 +3947,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>95</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3957,7 +3961,7 @@
         <v>0</v>
       </c>
       <c r="T43" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U43" s="10" t="s">
         <v>56</v>
@@ -3965,7 +3969,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46073.71759204861</v>
@@ -3977,16 +3981,16 @@
         <v>46182.53060627315</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I44" s="5">
         <v>46037</v>
@@ -4004,13 +4008,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4018,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="T44" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U44" s="10" t="s">
         <v>56</v>
@@ -4026,7 +4030,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46073.71759234954</v>
@@ -4036,7 +4040,7 @@
         <v>46156.618706249996</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4060,7 +4064,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4073,7 +4077,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46073.717592615736</v>
@@ -4085,16 +4089,16 @@
         <v>46154.09504209491</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I46" s="5">
         <v>46009</v>
@@ -4112,13 +4116,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q46" s="5">
         <v>46009</v>
@@ -4138,7 +4142,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B47" s="8">
         <v>46073.71758997685</v>
@@ -4150,16 +4154,16 @@
         <v>46154.09509461805</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I47" s="8">
         <v>46065</v>
@@ -4177,13 +4181,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="8">
         <v>46065</v>
@@ -4203,7 +4207,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46091.72801988426</v>
@@ -4215,16 +4219,16 @@
         <v>46154.09513386574</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I48" s="5">
         <v>46072</v>
@@ -4242,13 +4246,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46072</v>
@@ -4268,7 +4272,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46091.728057939814</v>
@@ -4278,16 +4282,16 @@
         <v>46161.2013843287</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I49" s="8">
         <v>46160</v>
@@ -4305,13 +4309,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="8">
         <v>46160</v>
@@ -4331,7 +4335,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46073.71759030093</v>
@@ -4343,7 +4347,7 @@
         <v>46191.789304328704</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4367,7 +4371,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4384,7 +4388,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B51" s="8">
         <v>46073.7175905787</v>
@@ -4396,16 +4400,16 @@
         <v>46191.788422488426</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I51" s="8">
         <v>46069</v>
@@ -4423,13 +4427,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="8">
         <v>46069</v>
@@ -4449,7 +4453,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46073.717590810185</v>
@@ -4461,16 +4465,16 @@
         <v>46191.789293194444</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I52" s="5">
         <v>46071</v>
@@ -4488,13 +4492,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="5">
         <v>46071</v>
@@ -4514,7 +4518,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="8">
         <v>46073.717591099536</v>
@@ -4526,7 +4530,7 @@
         <v>46191.79038505787</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4550,7 +4554,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4567,7 +4571,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46073.71759134259</v>
@@ -4579,16 +4583,16 @@
         <v>46191.7899528125</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I54" s="5">
         <v>46073</v>
@@ -4606,13 +4610,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q54" s="5">
         <v>46073</v>
@@ -4632,7 +4636,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B55" s="8">
         <v>46073.71759157407</v>
@@ -4644,16 +4648,16 @@
         <v>46191.790375833334</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I55" s="8">
         <v>46084</v>
@@ -4671,13 +4675,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q55" s="8">
         <v>46084</v>
@@ -4697,7 +4701,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
         <v>46073.71759181713</v>
@@ -4709,16 +4713,16 @@
         <v>46191.79037549769</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I56" s="5">
         <v>46104</v>
@@ -4736,13 +4740,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q56" s="5">
         <v>46104</v>
@@ -4757,7 +4761,7 @@
         <v>31</v>
       </c>
       <c r="U56" s="12" t="s">
-        <v>211</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4772,7 +4776,7 @@
         <v>46191.7884132176</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4825,10 +4829,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I58" s="5">
         <v>46153</v>
@@ -4846,10 +4850,10 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>216</v>
@@ -4867,7 +4871,7 @@
         <v>31</v>
       </c>
       <c r="U58" s="12" t="s">
-        <v>211</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4888,10 +4892,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I59" s="8">
         <v>46135</v>
@@ -4909,10 +4913,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>219</v>
@@ -4930,7 +4934,7 @@
         <v>31</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>211</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -4951,10 +4955,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I60" s="5">
         <v>46071</v>
@@ -4972,10 +4976,10 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>222</v>
@@ -4993,7 +4997,7 @@
         <v>31</v>
       </c>
       <c r="U60" s="12" t="s">
-        <v>211</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5005,7 +5009,7 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46119.188054259255</v>
+        <v>46191.88833803241</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5014,10 +5018,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I61" s="8">
         <v>46115</v>
@@ -5035,10 +5039,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>224</v>
@@ -5055,8 +5059,8 @@
       <c r="T61" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U61" s="10" t="s">
-        <v>56</v>
+      <c r="U61" s="12" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5077,10 +5081,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I62" s="5">
         <v>46139</v>
@@ -5098,10 +5102,10 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>227</v>
@@ -5119,7 +5123,7 @@
         <v>228</v>
       </c>
       <c r="U62" s="12" t="s">
-        <v>211</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5211,7 +5215,7 @@
         <v>230</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>234</v>
@@ -5229,7 +5233,7 @@
         <v>31</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>211</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5496,7 +5500,7 @@
         <v>46158.18178945602</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5559,7 +5563,7 @@
         <v>46162.1685475</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5589,7 +5593,7 @@
         <v>230</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>252</v>
@@ -5699,7 +5703,7 @@
         <v>254</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>258</v>
@@ -5954,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U76" s="10" t="s">
         <v>56</v>
@@ -6133,7 +6137,7 @@
         <v>0</v>
       </c>
       <c r="T79" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U79" s="10" t="s">
         <v>56</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46091.734465104164</v>
+        <v>46193.60765172454</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>230</v>
@@ -5180,9 +5180,11 @@
       <c r="B64" s="5">
         <v>46073.71759155093</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46193.60723070602</v>
+      </c>
       <c r="D64" s="5">
-        <v>46191.78969853009</v>
+        <v>46193.60726542824</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>233</v>
@@ -5227,13 +5229,13 @@
         <v>46125</v>
       </c>
       <c r="S64" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U64" s="12" t="s">
-        <v>102</v>
+      <c r="U64" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5243,9 +5245,11 @@
       <c r="B65" s="8">
         <v>46073.71759180556</v>
       </c>
-      <c r="C65" s="9"/>
+      <c r="C65" s="8">
+        <v>46193.60739422454</v>
+      </c>
       <c r="D65" s="8">
-        <v>46157.172432962965</v>
+        <v>46193.60740974537</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>236</v>
@@ -5290,13 +5294,13 @@
         <v>46156</v>
       </c>
       <c r="S65" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U65" s="10" t="s">
-        <v>56</v>
+      <c r="U65" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5306,9 +5310,11 @@
       <c r="B66" s="5">
         <v>46073.717592037036</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46193.60745574074</v>
+      </c>
       <c r="D66" s="5">
-        <v>46154.09512619213</v>
+        <v>46193.607472337964</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5353,13 +5359,13 @@
         <v>46140</v>
       </c>
       <c r="S66" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="U66" s="10" t="s">
-        <v>56</v>
+      <c r="U66" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5369,9 +5375,11 @@
       <c r="B67" s="8">
         <v>46073.71759226852</v>
       </c>
-      <c r="C67" s="9"/>
+      <c r="C67" s="8">
+        <v>46193.607493668984</v>
+      </c>
       <c r="D67" s="8">
-        <v>46154.095126712964</v>
+        <v>46193.60752077546</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5416,13 +5424,13 @@
         <v>46142</v>
       </c>
       <c r="S67" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U67" s="10" t="s">
-        <v>56</v>
+      <c r="U67" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5432,9 +5440,11 @@
       <c r="B68" s="5">
         <v>46076.600719699076</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46193.60764289352</v>
+      </c>
       <c r="D68" s="5">
-        <v>46154.09512726852</v>
+        <v>46193.60765795139</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5479,13 +5489,13 @@
         <v>46147</v>
       </c>
       <c r="S68" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U68" s="10" t="s">
-        <v>56</v>
+      <c r="U68" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5497,7 +5507,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46158.18178945602</v>
+        <v>46193.60893973379</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>182</v>
@@ -5547,8 +5557,8 @@
       <c r="T69" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U69" s="10" t="s">
-        <v>56</v>
+      <c r="U69" s="12" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -4773,7 +4773,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.7884132176</v>
+        <v>46195.60909892361</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>185</v>
@@ -4818,9 +4818,11 @@
       <c r="B58" s="5">
         <v>46073.71759105324</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46195.608916770834</v>
+      </c>
       <c r="D58" s="5">
-        <v>46155.866894293984</v>
+        <v>46195.60893649305</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4865,13 +4867,13 @@
         <v>46154</v>
       </c>
       <c r="S58" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U58" s="12" t="s">
-        <v>102</v>
+      <c r="U58" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4881,9 +4883,11 @@
       <c r="B59" s="8">
         <v>46073.71759083333</v>
       </c>
-      <c r="C59" s="9"/>
+      <c r="C59" s="8">
+        <v>46195.60909078704</v>
+      </c>
       <c r="D59" s="8">
-        <v>46155.90357260416</v>
+        <v>46195.60910890046</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4928,13 +4932,13 @@
         <v>46136</v>
       </c>
       <c r="S59" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U59" s="12" t="s">
-        <v>102</v>
+      <c r="U59" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5249,7 +5253,7 @@
         <v>46193.60739422454</v>
       </c>
       <c r="D65" s="8">
-        <v>46193.60740974537</v>
+        <v>46195.608936585646</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>236</v>
@@ -5299,8 +5303,8 @@
       <c r="T65" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U65" s="11" t="s">
-        <v>32</v>
+      <c r="U65" s="12" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5314,7 +5318,7 @@
         <v>46193.60745574074</v>
       </c>
       <c r="D66" s="5">
-        <v>46193.607472337964</v>
+        <v>46195.60911005787</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5364,8 +5368,8 @@
       <c r="T66" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="U66" s="11" t="s">
-        <v>32</v>
+      <c r="U66" s="12" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5507,7 +5511,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46193.60893973379</v>
+        <v>46195.61353703703</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>182</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46161.2013843287</v>
+        <v>46195.86821980324</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4329,8 +4329,8 @@
       <c r="T49" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U49" s="10" t="s">
-        <v>56</v>
+      <c r="U49" s="12" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46193.60765172454</v>
+        <v>46195.86820844907</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>230</v>
@@ -5509,9 +5509,11 @@
       <c r="B69" s="8">
         <v>46073.71759252315</v>
       </c>
-      <c r="C69" s="9"/>
+      <c r="C69" s="8">
+        <v>46195.86820241898</v>
+      </c>
       <c r="D69" s="8">
-        <v>46195.61353703703</v>
+        <v>46195.868219131946</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>182</v>
@@ -5556,13 +5558,13 @@
         <v>46157</v>
       </c>
       <c r="S69" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U69" s="12" t="s">
-        <v>102</v>
+      <c r="U69" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -1504,13 +1504,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.717590115746</v>
+        <v>46073.550923449075</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.724617025466</v>
+        <v>46092.557950358794</v>
       </c>
       <c r="D4" s="5">
-        <v>46114.81259290509</v>
+        <v>46114.64592623843</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1553,13 +1553,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.71759079861</v>
+        <v>46073.550924131945</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.724584826385</v>
+        <v>46092.55791815972</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.72461795139</v>
+        <v>46092.55795128472</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1618,13 +1618,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.71759107639</v>
+        <v>46073.55092440972</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.72458534723</v>
+        <v>46092.557918680555</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.72461783564</v>
+        <v>46092.55795116899</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1683,13 +1683,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.717591354165</v>
+        <v>46073.5509246875</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.72458572917</v>
+        <v>46092.5579190625</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.72461775463</v>
+        <v>46092.55795108796</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1746,13 +1746,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.71759162037</v>
+        <v>46073.5509249537</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72458613426</v>
+        <v>46092.557919467596</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.71077443287</v>
+        <v>46100.5441077662</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1809,13 +1809,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.71759189815</v>
+        <v>46073.55092523148</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.72458673611</v>
+        <v>46092.55792006945</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.72461730324</v>
+        <v>46092.557950636576</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1872,11 +1872,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.71759215278</v>
+        <v>46073.55092548611</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.5263790625</v>
+        <v>46097.35971239583</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1919,13 +1919,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.71759246528</v>
+        <v>46073.55092579861</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.526363854166</v>
+        <v>46097.3596971875</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.52638289351</v>
+        <v>46097.359716226856</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1984,11 +1984,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.71759273148</v>
+        <v>46073.55092606481</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46126.19500706019</v>
+        <v>46126.02834039352</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2047,13 +2047,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.71759298611</v>
+        <v>46073.55092631944</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51026252315</v>
+        <v>46114.34359585648</v>
       </c>
       <c r="D13" s="8">
-        <v>46169.884381701384</v>
+        <v>46169.71771503473</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2096,13 +2096,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.71759060185</v>
+        <v>46073.55092393518</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.52584498843</v>
+        <v>46097.359178321756</v>
       </c>
       <c r="D14" s="5">
-        <v>46100.761380717595</v>
+        <v>46100.59471405092</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2161,13 +2161,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.71759128472</v>
+        <v>46073.55092461806</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.50878793982</v>
+        <v>46114.34212127315</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.50880758102</v>
+        <v>46114.34214091435</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2226,13 +2226,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.71759157407</v>
+        <v>46073.55092490741</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.50922814815</v>
+        <v>46114.34256148148</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.509243865745</v>
+        <v>46114.34257719907</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2291,13 +2291,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.71759186343</v>
+        <v>46073.55092519676</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.51024402778</v>
+        <v>46114.34357736111</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.51026347222</v>
+        <v>46114.34359680556</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2356,13 +2356,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.717592141205</v>
+        <v>46073.55092547454</v>
       </c>
       <c r="C18" s="5">
-        <v>46169.88424704861</v>
+        <v>46169.71758038194</v>
       </c>
       <c r="D18" s="5">
-        <v>46169.88433502315</v>
+        <v>46169.71766835648</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2405,13 +2405,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.71759269676</v>
+        <v>46073.55092603009</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.525949456016</v>
+        <v>46097.35928278935</v>
       </c>
       <c r="D19" s="8">
-        <v>46156.61850119213</v>
+        <v>46156.45183452546</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2470,13 +2470,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.71759241898</v>
+        <v>46073.550925752315</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.5259784375</v>
+        <v>46097.35931177084</v>
       </c>
       <c r="D20" s="5">
-        <v>46156.61851966435</v>
+        <v>46156.451852997685</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2535,13 +2535,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.717593298614</v>
+        <v>46073.55092663194</v>
       </c>
       <c r="C21" s="8">
-        <v>46128.433728668984</v>
+        <v>46128.26706200231</v>
       </c>
       <c r="D21" s="8">
-        <v>46128.433750393524</v>
+        <v>46128.26708372685</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2600,13 +2600,13 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.71759302083</v>
+        <v>46073.55092635417</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.52660114583</v>
+        <v>46097.359934479166</v>
       </c>
       <c r="D22" s="5">
-        <v>46097.52662200232</v>
+        <v>46097.35995533565</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2665,13 +2665,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.593357997685</v>
+        <v>46076.42669133102</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.51032266204</v>
+        <v>46114.34365599537</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.51047230324</v>
+        <v>46114.34380563657</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2730,13 +2730,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.71759033565</v>
+        <v>46073.55092366898</v>
       </c>
       <c r="C24" s="5">
-        <v>46169.88422872685</v>
+        <v>46169.717562060185</v>
       </c>
       <c r="D24" s="5">
-        <v>46169.884247326394</v>
+        <v>46169.71758065972</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2795,11 +2795,11 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.71759071759</v>
+        <v>46073.55092405093</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46191.88830023148</v>
+        <v>46191.72163356481</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2844,13 +2844,13 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.7175902662</v>
+        <v>46073.55092359954</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.86689138889</v>
+        <v>46155.700224722226</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.86710392361</v>
+        <v>46155.70043725694</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -2909,13 +2909,13 @@
         <v>108</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.7175905787</v>
+        <v>46073.55092391204</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.52605542824</v>
+        <v>46097.35938876157</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.52605688658</v>
+        <v>46097.359390219906</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>109</v>
@@ -2970,13 +2970,13 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.71759086805</v>
+        <v>46073.550924201394</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.86687702546</v>
+        <v>46155.700210358795</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.866878229164</v>
+        <v>46155.7002115625</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3031,13 +3031,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.71759118055</v>
+        <v>46073.55092451389</v>
       </c>
       <c r="C29" s="8">
-        <v>46128.637161886574</v>
+        <v>46128.47049521991</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.63717174769</v>
+        <v>46128.470505081015</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>116</v>
@@ -3092,13 +3092,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.7175909838</v>
+        <v>46073.550924317125</v>
       </c>
       <c r="C30" s="5">
-        <v>46155.903569421294</v>
+        <v>46155.73690275463</v>
       </c>
       <c r="D30" s="5">
-        <v>46155.90358277778</v>
+        <v>46155.73691611111</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3157,13 +3157,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.71759126158</v>
+        <v>46073.55092459491</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.526086377315</v>
+        <v>46097.35941971064</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.52608802084</v>
+        <v>46097.359421354166</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3218,13 +3218,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.71759153935</v>
+        <v>46073.55092487269</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.903555972225</v>
+        <v>46155.73688930555</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.90355751157</v>
+        <v>46155.736890844906</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3279,13 +3279,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.717592685185</v>
+        <v>46073.55092601852</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.68305543982</v>
+        <v>46182.51638877315</v>
       </c>
       <c r="D33" s="8">
-        <v>46182.683057222224</v>
+        <v>46182.51639055555</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3344,13 +3344,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.71759302083</v>
+        <v>46073.55092635417</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.68274605324</v>
+        <v>46182.51607938657</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.6827475</v>
+        <v>46182.51608083333</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3405,13 +3405,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.71758986111</v>
+        <v>46073.550923194445</v>
       </c>
       <c r="C35" s="8">
-        <v>46182.682942314816</v>
+        <v>46182.516275648144</v>
       </c>
       <c r="D35" s="8">
-        <v>46182.682943541666</v>
+        <v>46182.516276875</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3466,13 +3466,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.7175918287</v>
+        <v>46073.55092516204</v>
       </c>
       <c r="C36" s="5">
-        <v>46191.888280127314</v>
+        <v>46191.72161346065</v>
       </c>
       <c r="D36" s="5">
-        <v>46191.89070638889</v>
+        <v>46191.72403972222</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3531,13 +3531,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.71759209491</v>
+        <v>46073.55092542824</v>
       </c>
       <c r="C37" s="8">
-        <v>46097.526664247685</v>
+        <v>46097.35999758102</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.84329747685</v>
+        <v>46169.67663081019</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3592,11 +3592,11 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.71759234954</v>
+        <v>46073.55092568287</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46191.88833190972</v>
+        <v>46191.72166524305</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3651,13 +3651,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46076.59415034722</v>
+        <v>46076.427483680556</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.86805253472</v>
+        <v>46154.70138586806</v>
       </c>
       <c r="D39" s="8">
-        <v>46156.618615775464</v>
+        <v>46156.4519491088</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3716,13 +3716,13 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46076.59428157407</v>
+        <v>46076.42761490741</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.86737157407</v>
+        <v>46154.70070490741</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.86737356482</v>
+        <v>46154.70070689815</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3781,13 +3781,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="8">
-        <v>46076.59448399306</v>
+        <v>46076.42781732639</v>
       </c>
       <c r="C41" s="8">
-        <v>46154.86810417824</v>
+        <v>46154.70143751157</v>
       </c>
       <c r="D41" s="8">
-        <v>46154.86810545139</v>
+        <v>46154.70143878472</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>154</v>
@@ -3846,13 +3846,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.71759148148</v>
+        <v>46073.550924814816</v>
       </c>
       <c r="C42" s="5">
-        <v>46182.530618530094</v>
+        <v>46182.36395186343</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.53063152778</v>
+        <v>46182.36396486111</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3911,13 +3911,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.717591759254</v>
+        <v>46073.5509250926</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.53046844907</v>
+        <v>46182.36380178241</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.53047055556</v>
+        <v>46182.36380388889</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -3972,13 +3972,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.71759204861</v>
+        <v>46073.55092538195</v>
       </c>
       <c r="C44" s="5">
-        <v>46182.530605011576</v>
+        <v>46182.363938344904</v>
       </c>
       <c r="D44" s="5">
-        <v>46182.53060627315</v>
+        <v>46182.36393960648</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4033,11 +4033,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.71759234954</v>
+        <v>46073.55092568287</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46156.618706249996</v>
+        <v>46156.45203958334</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4080,13 +4080,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.717592615736</v>
+        <v>46073.55092594908</v>
       </c>
       <c r="C46" s="5">
-        <v>46154.09501991898</v>
+        <v>46153.92835325231</v>
       </c>
       <c r="D46" s="5">
-        <v>46154.09504209491</v>
+        <v>46153.92837542824</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4145,13 +4145,13 @@
         <v>173</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.71758997685</v>
+        <v>46073.550923310184</v>
       </c>
       <c r="C47" s="8">
-        <v>46154.09507998843</v>
+        <v>46153.92841332176</v>
       </c>
       <c r="D47" s="8">
-        <v>46154.09509461805</v>
+        <v>46153.92842795139</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>174</v>
@@ -4210,13 +4210,13 @@
         <v>177</v>
       </c>
       <c r="B48" s="5">
-        <v>46091.72801988426</v>
+        <v>46091.56135321759</v>
       </c>
       <c r="C48" s="5">
-        <v>46154.09511894676</v>
+        <v>46153.92845228009</v>
       </c>
       <c r="D48" s="5">
-        <v>46154.09513386574</v>
+        <v>46153.928467199075</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4275,11 +4275,11 @@
         <v>180</v>
       </c>
       <c r="B49" s="8">
-        <v>46091.728057939814</v>
+        <v>46091.56139127315</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46195.86821980324</v>
+        <v>46195.701553136576</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4338,13 +4338,13 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.71759030093</v>
+        <v>46073.55092363426</v>
       </c>
       <c r="C50" s="5">
-        <v>46191.78929271991</v>
+        <v>46191.62262605324</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.789304328704</v>
+        <v>46191.62263766203</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4391,13 +4391,13 @@
         <v>187</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.7175905787</v>
+        <v>46073.55092391204</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.788401875005</v>
+        <v>46191.62173520833</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.788422488426</v>
+        <v>46191.62175582176</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>164</v>
@@ -4456,13 +4456,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.717590810185</v>
+        <v>46073.55092414352</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.78927659722</v>
+        <v>46191.62260993056</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.789293194444</v>
+        <v>46191.62262652778</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4521,13 +4521,13 @@
         <v>196</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.717591099536</v>
+        <v>46073.55092443287</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.79037481482</v>
+        <v>46191.62370814815</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.79038505787</v>
+        <v>46191.6237183912</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>197</v>
@@ -4574,13 +4574,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.71759134259</v>
+        <v>46073.550924675925</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.7899369213</v>
+        <v>46191.623270254626</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.7899528125</v>
+        <v>46191.623286145834</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4639,13 +4639,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.71759157407</v>
+        <v>46073.55092490741</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.79035826389</v>
+        <v>46191.623691597226</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.790375833334</v>
+        <v>46191.62370916667</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4704,13 +4704,13 @@
         <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.71759181713</v>
+        <v>46073.55092515046</v>
       </c>
       <c r="C56" s="5">
-        <v>46191.789681423616</v>
+        <v>46191.623014756944</v>
       </c>
       <c r="D56" s="5">
-        <v>46191.79037549769</v>
+        <v>46191.623708831015</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>209</v>
@@ -4769,11 +4769,11 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.71759206019</v>
+        <v>46073.550925393516</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46195.60909892361</v>
+        <v>46195.44243225694</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>185</v>
@@ -4816,13 +4816,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.71759105324</v>
+        <v>46073.550924386574</v>
       </c>
       <c r="C58" s="5">
-        <v>46195.608916770834</v>
+        <v>46195.44225010417</v>
       </c>
       <c r="D58" s="5">
-        <v>46195.60893649305</v>
+        <v>46195.44226982639</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4881,13 +4881,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.71759083333</v>
+        <v>46073.550924166666</v>
       </c>
       <c r="C59" s="8">
-        <v>46195.60909078704</v>
+        <v>46195.44242412037</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.60910890046</v>
+        <v>46195.4424422338</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4946,11 +4946,11 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.71759233796</v>
+        <v>46073.5509256713</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46182.682959768514</v>
+        <v>46182.51629310186</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -5009,11 +5009,11 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.71759050926</v>
+        <v>46073.55092384259</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46191.88833803241</v>
+        <v>46191.72167136574</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5072,11 +5072,11 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.59959273148</v>
+        <v>46076.432926064816</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46154.86812247685</v>
+        <v>46154.70145581018</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5135,11 +5135,11 @@
         <v>229</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.71759130787</v>
+        <v>46073.550924641204</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.86820844907</v>
+        <v>46195.70154178241</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>230</v>
@@ -5182,13 +5182,13 @@
         <v>232</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.71759155093</v>
+        <v>46073.55092488426</v>
       </c>
       <c r="C64" s="5">
-        <v>46193.60723070602</v>
+        <v>46193.44056403935</v>
       </c>
       <c r="D64" s="5">
-        <v>46193.60726542824</v>
+        <v>46193.440598761576</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>233</v>
@@ -5247,13 +5247,13 @@
         <v>235</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.71759180556</v>
+        <v>46073.55092513889</v>
       </c>
       <c r="C65" s="8">
-        <v>46193.60739422454</v>
+        <v>46193.44072755787</v>
       </c>
       <c r="D65" s="8">
-        <v>46195.608936585646</v>
+        <v>46195.44226991898</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>236</v>
@@ -5312,13 +5312,13 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.717592037036</v>
+        <v>46073.55092537037</v>
       </c>
       <c r="C66" s="5">
-        <v>46193.60745574074</v>
+        <v>46193.44078907407</v>
       </c>
       <c r="D66" s="5">
-        <v>46195.60911005787</v>
+        <v>46195.442443391206</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5377,13 +5377,13 @@
         <v>243</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.71759226852</v>
+        <v>46073.550925601856</v>
       </c>
       <c r="C67" s="8">
-        <v>46193.607493668984</v>
+        <v>46193.44082700231</v>
       </c>
       <c r="D67" s="8">
-        <v>46193.60752077546</v>
+        <v>46193.4408541088</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5442,13 +5442,13 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.600719699076</v>
+        <v>46076.43405303241</v>
       </c>
       <c r="C68" s="5">
-        <v>46193.60764289352</v>
+        <v>46193.44097622685</v>
       </c>
       <c r="D68" s="5">
-        <v>46193.60765795139</v>
+        <v>46193.44099128472</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5507,13 +5507,13 @@
         <v>248</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.71759252315</v>
+        <v>46073.550925856485</v>
       </c>
       <c r="C69" s="8">
-        <v>46195.86820241898</v>
+        <v>46195.70153575232</v>
       </c>
       <c r="D69" s="8">
-        <v>46195.868219131946</v>
+        <v>46195.70155246528</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>182</v>
@@ -5572,11 +5572,11 @@
         <v>251</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.7175927662</v>
+        <v>46073.55092609954</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46162.1685475</v>
+        <v>46162.00188083333</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>183</v>
@@ -5635,11 +5635,11 @@
         <v>253</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.71759042824</v>
+        <v>46073.55092376158</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46091.73446609954</v>
+        <v>46091.56779943287</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>254</v>
@@ -5682,11 +5682,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.71759075232</v>
+        <v>46073.55092408565</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46163.2036187037</v>
+        <v>46163.03695203704</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>257</v>
@@ -5745,11 +5745,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.71759101852</v>
+        <v>46073.55092435185</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46168.18663340277</v>
+        <v>46168.019966736116</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5808,11 +5808,11 @@
         <v>263</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.71759130787</v>
+        <v>46073.550924641204</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46169.16854244213</v>
+        <v>46169.00187577546</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>264</v>
@@ -5871,11 +5871,11 @@
         <v>268</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.7175915625</v>
+        <v>46073.55092489583</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46170.19857011574</v>
+        <v>46170.031903449075</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>269</v>
@@ -5932,11 +5932,11 @@
         <v>271</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.71759184028</v>
+        <v>46073.55092517361</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46091.73446550926</v>
+        <v>46091.56779884259</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>272</v>
@@ -5985,11 +5985,11 @@
         <v>274</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.71759210648</v>
+        <v>46073.55092543981</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46179.199858576394</v>
+        <v>46179.03319190972</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>275</v>
@@ -6048,11 +6048,11 @@
         <v>278</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.71759238426</v>
+        <v>46073.55092571759</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46179.19985642361</v>
+        <v>46179.03318975694</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>279</v>
@@ -6111,11 +6111,11 @@
         <v>281</v>
       </c>
       <c r="B79" s="8">
-        <v>46091.72839834491</v>
+        <v>46091.561731678245</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46091.73565777778</v>
+        <v>46091.56899111111</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>282</v>
@@ -6164,11 +6164,11 @@
         <v>284</v>
       </c>
       <c r="B80" s="5">
-        <v>46091.72894082176</v>
+        <v>46091.56227415509</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46179.199856562496</v>
+        <v>46179.03318989583</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>285</v>
@@ -6227,11 +6227,11 @@
         <v>287</v>
       </c>
       <c r="B81" s="8">
-        <v>46091.72900166667</v>
+        <v>46091.562334999995</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46190.17451866898</v>
+        <v>46190.007852002316</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>288</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -1504,13 +1504,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.550923449075</v>
+        <v>46073.717590115746</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.557950358794</v>
+        <v>46092.724617025466</v>
       </c>
       <c r="D4" s="5">
-        <v>46114.64592623843</v>
+        <v>46114.81259290509</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1553,13 +1553,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.550924131945</v>
+        <v>46073.71759079861</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55791815972</v>
+        <v>46092.724584826385</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55795128472</v>
+        <v>46092.72461795139</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1618,13 +1618,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.55092440972</v>
+        <v>46073.71759107639</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.557918680555</v>
+        <v>46092.72458534723</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55795116899</v>
+        <v>46092.72461783564</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1683,13 +1683,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.5509246875</v>
+        <v>46073.717591354165</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.5579190625</v>
+        <v>46092.72458572917</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.55795108796</v>
+        <v>46092.72461775463</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1746,13 +1746,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.5509249537</v>
+        <v>46073.71759162037</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.557919467596</v>
+        <v>46092.72458613426</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.5441077662</v>
+        <v>46100.71077443287</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1809,13 +1809,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.55092523148</v>
+        <v>46073.71759189815</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55792006945</v>
+        <v>46092.72458673611</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.557950636576</v>
+        <v>46092.72461730324</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1872,11 +1872,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.55092548611</v>
+        <v>46073.71759215278</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.35971239583</v>
+        <v>46097.5263790625</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1919,13 +1919,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.55092579861</v>
+        <v>46073.71759246528</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.3596971875</v>
+        <v>46097.526363854166</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.359716226856</v>
+        <v>46097.52638289351</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1984,11 +1984,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.55092606481</v>
+        <v>46073.71759273148</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46126.02834039352</v>
+        <v>46126.19500706019</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2047,13 +2047,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.55092631944</v>
+        <v>46073.71759298611</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.34359585648</v>
+        <v>46114.51026252315</v>
       </c>
       <c r="D13" s="8">
-        <v>46169.71771503473</v>
+        <v>46169.884381701384</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2096,13 +2096,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.55092393518</v>
+        <v>46073.71759060185</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.359178321756</v>
+        <v>46097.52584498843</v>
       </c>
       <c r="D14" s="5">
-        <v>46100.59471405092</v>
+        <v>46100.761380717595</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2161,13 +2161,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.55092461806</v>
+        <v>46073.71759128472</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.34212127315</v>
+        <v>46114.50878793982</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.34214091435</v>
+        <v>46114.50880758102</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2226,13 +2226,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.55092490741</v>
+        <v>46073.71759157407</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.34256148148</v>
+        <v>46114.50922814815</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.34257719907</v>
+        <v>46114.509243865745</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2291,13 +2291,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.55092519676</v>
+        <v>46073.71759186343</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34357736111</v>
+        <v>46114.51024402778</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.34359680556</v>
+        <v>46114.51026347222</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2356,13 +2356,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.55092547454</v>
+        <v>46073.717592141205</v>
       </c>
       <c r="C18" s="5">
-        <v>46169.71758038194</v>
+        <v>46169.88424704861</v>
       </c>
       <c r="D18" s="5">
-        <v>46169.71766835648</v>
+        <v>46169.88433502315</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2405,13 +2405,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.55092603009</v>
+        <v>46073.71759269676</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.35928278935</v>
+        <v>46097.525949456016</v>
       </c>
       <c r="D19" s="8">
-        <v>46156.45183452546</v>
+        <v>46156.61850119213</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2470,13 +2470,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.550925752315</v>
+        <v>46073.71759241898</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.35931177084</v>
+        <v>46097.5259784375</v>
       </c>
       <c r="D20" s="5">
-        <v>46156.451852997685</v>
+        <v>46156.61851966435</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2535,13 +2535,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.55092663194</v>
+        <v>46073.717593298614</v>
       </c>
       <c r="C21" s="8">
-        <v>46128.26706200231</v>
+        <v>46128.433728668984</v>
       </c>
       <c r="D21" s="8">
-        <v>46128.26708372685</v>
+        <v>46128.433750393524</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2600,13 +2600,13 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.55092635417</v>
+        <v>46073.71759302083</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.359934479166</v>
+        <v>46097.52660114583</v>
       </c>
       <c r="D22" s="5">
-        <v>46097.35995533565</v>
+        <v>46097.52662200232</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2665,13 +2665,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.42669133102</v>
+        <v>46076.593357997685</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.34365599537</v>
+        <v>46114.51032266204</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.34380563657</v>
+        <v>46114.51047230324</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2730,13 +2730,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.55092366898</v>
+        <v>46073.71759033565</v>
       </c>
       <c r="C24" s="5">
-        <v>46169.717562060185</v>
+        <v>46169.88422872685</v>
       </c>
       <c r="D24" s="5">
-        <v>46169.71758065972</v>
+        <v>46169.884247326394</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2795,11 +2795,11 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.55092405093</v>
+        <v>46073.71759071759</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46191.72163356481</v>
+        <v>46191.88830023148</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2844,13 +2844,13 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.55092359954</v>
+        <v>46073.7175902662</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.700224722226</v>
+        <v>46155.86689138889</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.70043725694</v>
+        <v>46155.86710392361</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -2909,13 +2909,13 @@
         <v>108</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.55092391204</v>
+        <v>46073.7175905787</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.35938876157</v>
+        <v>46097.52605542824</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.359390219906</v>
+        <v>46097.52605688658</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>109</v>
@@ -2970,13 +2970,13 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.550924201394</v>
+        <v>46073.71759086805</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.700210358795</v>
+        <v>46155.86687702546</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.7002115625</v>
+        <v>46155.866878229164</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3031,13 +3031,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.55092451389</v>
+        <v>46073.71759118055</v>
       </c>
       <c r="C29" s="8">
-        <v>46128.47049521991</v>
+        <v>46128.637161886574</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.470505081015</v>
+        <v>46128.63717174769</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>116</v>
@@ -3092,13 +3092,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.550924317125</v>
+        <v>46073.7175909838</v>
       </c>
       <c r="C30" s="5">
-        <v>46155.73690275463</v>
+        <v>46155.903569421294</v>
       </c>
       <c r="D30" s="5">
-        <v>46155.73691611111</v>
+        <v>46155.90358277778</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3157,13 +3157,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.55092459491</v>
+        <v>46073.71759126158</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.35941971064</v>
+        <v>46097.526086377315</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.359421354166</v>
+        <v>46097.52608802084</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3218,13 +3218,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.55092487269</v>
+        <v>46073.71759153935</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.73688930555</v>
+        <v>46155.903555972225</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.736890844906</v>
+        <v>46155.90355751157</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3279,13 +3279,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.55092601852</v>
+        <v>46073.717592685185</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.51638877315</v>
+        <v>46182.68305543982</v>
       </c>
       <c r="D33" s="8">
-        <v>46182.51639055555</v>
+        <v>46182.683057222224</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3344,13 +3344,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.55092635417</v>
+        <v>46073.71759302083</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.51607938657</v>
+        <v>46182.68274605324</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.51608083333</v>
+        <v>46182.6827475</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3405,13 +3405,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.550923194445</v>
+        <v>46073.71758986111</v>
       </c>
       <c r="C35" s="8">
-        <v>46182.516275648144</v>
+        <v>46182.682942314816</v>
       </c>
       <c r="D35" s="8">
-        <v>46182.516276875</v>
+        <v>46182.682943541666</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3466,13 +3466,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.55092516204</v>
+        <v>46073.7175918287</v>
       </c>
       <c r="C36" s="5">
-        <v>46191.72161346065</v>
+        <v>46191.888280127314</v>
       </c>
       <c r="D36" s="5">
-        <v>46191.72403972222</v>
+        <v>46191.89070638889</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3531,13 +3531,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.55092542824</v>
+        <v>46073.71759209491</v>
       </c>
       <c r="C37" s="8">
-        <v>46097.35999758102</v>
+        <v>46097.526664247685</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.67663081019</v>
+        <v>46169.84329747685</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3592,11 +3592,11 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.55092568287</v>
+        <v>46073.71759234954</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46191.72166524305</v>
+        <v>46191.88833190972</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3651,13 +3651,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46076.427483680556</v>
+        <v>46076.59415034722</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.70138586806</v>
+        <v>46154.86805253472</v>
       </c>
       <c r="D39" s="8">
-        <v>46156.4519491088</v>
+        <v>46156.618615775464</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3716,13 +3716,13 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46076.42761490741</v>
+        <v>46076.59428157407</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.70070490741</v>
+        <v>46154.86737157407</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.70070689815</v>
+        <v>46154.86737356482</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3781,13 +3781,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="8">
-        <v>46076.42781732639</v>
+        <v>46076.59448399306</v>
       </c>
       <c r="C41" s="8">
-        <v>46154.70143751157</v>
+        <v>46154.86810417824</v>
       </c>
       <c r="D41" s="8">
-        <v>46154.70143878472</v>
+        <v>46154.86810545139</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>154</v>
@@ -3846,13 +3846,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.550924814816</v>
+        <v>46073.71759148148</v>
       </c>
       <c r="C42" s="5">
-        <v>46182.36395186343</v>
+        <v>46182.530618530094</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.36396486111</v>
+        <v>46182.53063152778</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3911,13 +3911,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.5509250926</v>
+        <v>46073.717591759254</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.36380178241</v>
+        <v>46182.53046844907</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.36380388889</v>
+        <v>46182.53047055556</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -3972,13 +3972,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.55092538195</v>
+        <v>46073.71759204861</v>
       </c>
       <c r="C44" s="5">
-        <v>46182.363938344904</v>
+        <v>46182.530605011576</v>
       </c>
       <c r="D44" s="5">
-        <v>46182.36393960648</v>
+        <v>46182.53060627315</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4033,11 +4033,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.55092568287</v>
+        <v>46073.71759234954</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46156.45203958334</v>
+        <v>46156.618706249996</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4080,13 +4080,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.55092594908</v>
+        <v>46073.717592615736</v>
       </c>
       <c r="C46" s="5">
-        <v>46153.92835325231</v>
+        <v>46154.09501991898</v>
       </c>
       <c r="D46" s="5">
-        <v>46153.92837542824</v>
+        <v>46154.09504209491</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4145,13 +4145,13 @@
         <v>173</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.550923310184</v>
+        <v>46073.71758997685</v>
       </c>
       <c r="C47" s="8">
-        <v>46153.92841332176</v>
+        <v>46154.09507998843</v>
       </c>
       <c r="D47" s="8">
-        <v>46153.92842795139</v>
+        <v>46154.09509461805</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>174</v>
@@ -4210,13 +4210,13 @@
         <v>177</v>
       </c>
       <c r="B48" s="5">
-        <v>46091.56135321759</v>
+        <v>46091.72801988426</v>
       </c>
       <c r="C48" s="5">
-        <v>46153.92845228009</v>
+        <v>46154.09511894676</v>
       </c>
       <c r="D48" s="5">
-        <v>46153.928467199075</v>
+        <v>46154.09513386574</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4275,11 +4275,11 @@
         <v>180</v>
       </c>
       <c r="B49" s="8">
-        <v>46091.56139127315</v>
+        <v>46091.728057939814</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46195.701553136576</v>
+        <v>46195.86821980324</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4338,13 +4338,13 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.55092363426</v>
+        <v>46073.71759030093</v>
       </c>
       <c r="C50" s="5">
-        <v>46191.62262605324</v>
+        <v>46191.78929271991</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.62263766203</v>
+        <v>46191.789304328704</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4391,13 +4391,13 @@
         <v>187</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.55092391204</v>
+        <v>46073.7175905787</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.62173520833</v>
+        <v>46191.788401875005</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.62175582176</v>
+        <v>46191.788422488426</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>164</v>
@@ -4456,13 +4456,13 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.55092414352</v>
+        <v>46073.717590810185</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.62260993056</v>
+        <v>46191.78927659722</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.62262652778</v>
+        <v>46191.789293194444</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>192</v>
@@ -4521,13 +4521,13 @@
         <v>196</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.55092443287</v>
+        <v>46073.717591099536</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.62370814815</v>
+        <v>46191.79037481482</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.6237183912</v>
+        <v>46191.79038505787</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>197</v>
@@ -4574,13 +4574,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.550924675925</v>
+        <v>46073.71759134259</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.623270254626</v>
+        <v>46191.7899369213</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.623286145834</v>
+        <v>46191.7899528125</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4639,13 +4639,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.55092490741</v>
+        <v>46073.71759157407</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.623691597226</v>
+        <v>46191.79035826389</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.62370916667</v>
+        <v>46191.790375833334</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>205</v>
@@ -4704,13 +4704,13 @@
         <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.55092515046</v>
+        <v>46073.71759181713</v>
       </c>
       <c r="C56" s="5">
-        <v>46191.623014756944</v>
+        <v>46191.789681423616</v>
       </c>
       <c r="D56" s="5">
-        <v>46191.623708831015</v>
+        <v>46191.79037549769</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>209</v>
@@ -4769,11 +4769,11 @@
         <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.550925393516</v>
+        <v>46073.71759206019</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46195.44243225694</v>
+        <v>46195.60909892361</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>185</v>
@@ -4816,13 +4816,13 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.550924386574</v>
+        <v>46073.71759105324</v>
       </c>
       <c r="C58" s="5">
-        <v>46195.44225010417</v>
+        <v>46195.608916770834</v>
       </c>
       <c r="D58" s="5">
-        <v>46195.44226982639</v>
+        <v>46195.60893649305</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4881,13 +4881,13 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.550924166666</v>
+        <v>46073.71759083333</v>
       </c>
       <c r="C59" s="8">
-        <v>46195.44242412037</v>
+        <v>46195.60909078704</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.4424422338</v>
+        <v>46195.60910890046</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -4946,11 +4946,11 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.5509256713</v>
+        <v>46073.71759233796</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46182.51629310186</v>
+        <v>46182.682959768514</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -5009,11 +5009,11 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.55092384259</v>
+        <v>46073.71759050926</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46191.72167136574</v>
+        <v>46191.88833803241</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5072,11 +5072,11 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.432926064816</v>
+        <v>46076.59959273148</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46154.70145581018</v>
+        <v>46154.86812247685</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5135,11 +5135,11 @@
         <v>229</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.550924641204</v>
+        <v>46073.71759130787</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.70154178241</v>
+        <v>46195.86820844907</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>230</v>
@@ -5182,13 +5182,13 @@
         <v>232</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.55092488426</v>
+        <v>46073.71759155093</v>
       </c>
       <c r="C64" s="5">
-        <v>46193.44056403935</v>
+        <v>46193.60723070602</v>
       </c>
       <c r="D64" s="5">
-        <v>46193.440598761576</v>
+        <v>46193.60726542824</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>233</v>
@@ -5247,13 +5247,13 @@
         <v>235</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.55092513889</v>
+        <v>46073.71759180556</v>
       </c>
       <c r="C65" s="8">
-        <v>46193.44072755787</v>
+        <v>46193.60739422454</v>
       </c>
       <c r="D65" s="8">
-        <v>46195.44226991898</v>
+        <v>46195.608936585646</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>236</v>
@@ -5312,13 +5312,13 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.55092537037</v>
+        <v>46073.717592037036</v>
       </c>
       <c r="C66" s="5">
-        <v>46193.44078907407</v>
+        <v>46193.60745574074</v>
       </c>
       <c r="D66" s="5">
-        <v>46195.442443391206</v>
+        <v>46195.60911005787</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5377,13 +5377,13 @@
         <v>243</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.550925601856</v>
+        <v>46073.71759226852</v>
       </c>
       <c r="C67" s="8">
-        <v>46193.44082700231</v>
+        <v>46193.607493668984</v>
       </c>
       <c r="D67" s="8">
-        <v>46193.4408541088</v>
+        <v>46193.60752077546</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5442,13 +5442,13 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.43405303241</v>
+        <v>46076.600719699076</v>
       </c>
       <c r="C68" s="5">
-        <v>46193.44097622685</v>
+        <v>46193.60764289352</v>
       </c>
       <c r="D68" s="5">
-        <v>46193.44099128472</v>
+        <v>46193.60765795139</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>227</v>
@@ -5507,13 +5507,13 @@
         <v>248</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.550925856485</v>
+        <v>46073.71759252315</v>
       </c>
       <c r="C69" s="8">
-        <v>46195.70153575232</v>
+        <v>46195.86820241898</v>
       </c>
       <c r="D69" s="8">
-        <v>46195.70155246528</v>
+        <v>46195.868219131946</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>182</v>
@@ -5572,11 +5572,11 @@
         <v>251</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.55092609954</v>
+        <v>46073.7175927662</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46162.00188083333</v>
+        <v>46162.1685475</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>183</v>
@@ -5635,11 +5635,11 @@
         <v>253</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.55092376158</v>
+        <v>46073.71759042824</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46091.56779943287</v>
+        <v>46091.73446609954</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>254</v>
@@ -5682,11 +5682,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.55092408565</v>
+        <v>46073.71759075232</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46163.03695203704</v>
+        <v>46163.2036187037</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>257</v>
@@ -5745,11 +5745,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.55092435185</v>
+        <v>46073.71759101852</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46168.019966736116</v>
+        <v>46168.18663340277</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5808,11 +5808,11 @@
         <v>263</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.550924641204</v>
+        <v>46073.71759130787</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46169.00187577546</v>
+        <v>46169.16854244213</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>264</v>
@@ -5871,11 +5871,11 @@
         <v>268</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.55092489583</v>
+        <v>46073.7175915625</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46170.031903449075</v>
+        <v>46170.19857011574</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>269</v>
@@ -5932,11 +5932,11 @@
         <v>271</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.55092517361</v>
+        <v>46073.71759184028</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46091.56779884259</v>
+        <v>46091.73446550926</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>272</v>
@@ -5985,11 +5985,11 @@
         <v>274</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.55092543981</v>
+        <v>46073.71759210648</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46179.03319190972</v>
+        <v>46179.199858576394</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>275</v>
@@ -6048,11 +6048,11 @@
         <v>278</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.55092571759</v>
+        <v>46073.71759238426</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46179.03318975694</v>
+        <v>46179.19985642361</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>279</v>
@@ -6111,11 +6111,11 @@
         <v>281</v>
       </c>
       <c r="B79" s="8">
-        <v>46091.561731678245</v>
+        <v>46091.72839834491</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46091.56899111111</v>
+        <v>46091.73565777778</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>282</v>
@@ -6164,11 +6164,11 @@
         <v>284</v>
       </c>
       <c r="B80" s="5">
-        <v>46091.56227415509</v>
+        <v>46091.72894082176</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46179.03318989583</v>
+        <v>46179.199856562496</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>285</v>
@@ -6227,11 +6227,11 @@
         <v>287</v>
       </c>
       <c r="B81" s="8">
-        <v>46091.562334999995</v>
+        <v>46091.72900166667</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46190.007852002316</v>
+        <v>46190.17451866898</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>288</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="291">
   <si>
     <t xml:space="preserve">50001498-CALABRESSE METRO STO DOMINGO  POZOS  </t>
   </si>
@@ -557,6 +557,12 @@
   </si>
   <si>
     <t>Check Pruebas fat</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
   </si>
   <si>
     <t>Pruebas FAT</t>
@@ -4279,7 +4285,7 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46195.86821980324</v>
+        <v>46198.821597800925</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>181</v>
@@ -4288,10 +4294,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="I49" s="8">
         <v>46160</v>
@@ -4312,10 +4318,10 @@
         <v>166</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q49" s="8">
         <v>46160</v>
@@ -4335,7 +4341,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B50" s="5">
         <v>46073.71759030093</v>
@@ -4347,7 +4353,7 @@
         <v>46191.789304328704</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4371,7 +4377,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4388,7 +4394,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B51" s="8">
         <v>46073.7175905787</v>
@@ -4406,10 +4412,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I51" s="8">
         <v>46069</v>
@@ -4427,13 +4433,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>163</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="8">
         <v>46069</v>
@@ -4453,7 +4459,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46073.717590810185</v>
@@ -4465,16 +4471,16 @@
         <v>46191.789293194444</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I52" s="5">
         <v>46071</v>
@@ -4492,13 +4498,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>164</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q52" s="5">
         <v>46071</v>
@@ -4518,7 +4524,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B53" s="8">
         <v>46073.717591099536</v>
@@ -4530,7 +4536,7 @@
         <v>46191.79038505787</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4554,7 +4560,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4571,7 +4577,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B54" s="5">
         <v>46073.71759134259</v>
@@ -4583,16 +4589,16 @@
         <v>46191.7899528125</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I54" s="5">
         <v>46073</v>
@@ -4610,13 +4616,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q54" s="5">
         <v>46073</v>
@@ -4636,7 +4642,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B55" s="8">
         <v>46073.71759157407</v>
@@ -4648,16 +4654,16 @@
         <v>46191.790375833334</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I55" s="8">
         <v>46084</v>
@@ -4675,13 +4681,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q55" s="8">
         <v>46084</v>
@@ -4701,7 +4707,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B56" s="5">
         <v>46073.71759181713</v>
@@ -4713,16 +4719,16 @@
         <v>46191.79037549769</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I56" s="5">
         <v>46104</v>
@@ -4740,13 +4746,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q56" s="5">
         <v>46104</v>
@@ -4766,17 +4772,17 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B57" s="8">
         <v>46073.71759206019</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46195.60909892361</v>
+        <v>46198.827981574075</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4800,7 +4806,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4813,7 +4819,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B58" s="5">
         <v>46073.71759105324</v>
@@ -4825,16 +4831,16 @@
         <v>46195.60893649305</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I58" s="5">
         <v>46153</v>
@@ -4852,13 +4858,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>113</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q58" s="5">
         <v>46153</v>
@@ -4878,7 +4884,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B59" s="8">
         <v>46073.71759083333</v>
@@ -4890,16 +4896,16 @@
         <v>46195.60910890046</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I59" s="8">
         <v>46135</v>
@@ -4917,13 +4923,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>125</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q59" s="8">
         <v>46134</v>
@@ -4943,26 +4949,28 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B60" s="5">
         <v>46073.71759233796</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46198.82797583334</v>
+      </c>
       <c r="D60" s="5">
-        <v>46182.682959768514</v>
+        <v>46198.82799237268</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I60" s="5">
         <v>46071</v>
@@ -4980,13 +4988,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>134</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q60" s="5">
         <v>46071</v>
@@ -4995,18 +5003,18 @@
         <v>46072</v>
       </c>
       <c r="S60" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U60" s="12" t="s">
-        <v>102</v>
+      <c r="U60" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B61" s="8">
         <v>46073.71759050926</v>
@@ -5022,10 +5030,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I61" s="8">
         <v>46115</v>
@@ -5043,13 +5051,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>143</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q61" s="8">
         <v>46115</v>
@@ -5069,26 +5077,28 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B62" s="5">
         <v>46076.59959273148</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46198.82946502315</v>
+      </c>
       <c r="D62" s="5">
-        <v>46154.86812247685</v>
+        <v>46198.829483009264</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I62" s="5">
         <v>46139</v>
@@ -5106,13 +5116,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>154</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q62" s="5">
         <v>46139</v>
@@ -5121,18 +5131,18 @@
         <v>46140</v>
       </c>
       <c r="S62" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="U62" s="12" t="s">
-        <v>102</v>
+        <v>230</v>
+      </c>
+      <c r="U62" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B63" s="8">
         <v>46073.71759130787</v>
@@ -5142,7 +5152,7 @@
         <v>46195.86820844907</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5166,7 +5176,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5179,7 +5189,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B64" s="5">
         <v>46073.71759155093</v>
@@ -5191,7 +5201,7 @@
         <v>46193.60726542824</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5218,13 +5228,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q64" s="5">
         <v>46106</v>
@@ -5244,7 +5254,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B65" s="8">
         <v>46073.71759180556</v>
@@ -5256,7 +5266,7 @@
         <v>46195.608936585646</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5283,13 +5293,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q65" s="8">
         <v>46155</v>
@@ -5309,7 +5319,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B66" s="5">
         <v>46073.717592037036</v>
@@ -5321,7 +5331,7 @@
         <v>46195.60911005787</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5348,13 +5358,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q66" s="5">
         <v>46139</v>
@@ -5366,7 +5376,7 @@
         <v>1</v>
       </c>
       <c r="T66" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="U66" s="12" t="s">
         <v>102</v>
@@ -5374,7 +5384,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B67" s="8">
         <v>46073.71759226852</v>
@@ -5383,10 +5393,10 @@
         <v>46193.607493668984</v>
       </c>
       <c r="D67" s="8">
-        <v>46193.60752077546</v>
+        <v>46198.82799127315</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5413,13 +5423,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q67" s="8">
         <v>46141</v>
@@ -5433,13 +5443,13 @@
       <c r="T67" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U67" s="11" t="s">
-        <v>32</v>
+      <c r="U67" s="12" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B68" s="5">
         <v>46076.600719699076</v>
@@ -5448,10 +5458,10 @@
         <v>46193.60764289352</v>
       </c>
       <c r="D68" s="5">
-        <v>46193.60765795139</v>
+        <v>46198.82948185185</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5478,13 +5488,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q68" s="5">
         <v>46146</v>
@@ -5498,13 +5508,13 @@
       <c r="T68" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U68" s="11" t="s">
-        <v>32</v>
+      <c r="U68" s="12" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B69" s="8">
         <v>46073.71759252315</v>
@@ -5516,7 +5526,7 @@
         <v>46195.868219131946</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5543,13 +5553,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q69" s="8">
         <v>46157</v>
@@ -5569,7 +5579,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B70" s="5">
         <v>46073.7175927662</v>
@@ -5579,7 +5589,7 @@
         <v>46162.1685475</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5606,13 +5616,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q70" s="5">
         <v>46161</v>
@@ -5632,7 +5642,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B71" s="8">
         <v>46073.71759042824</v>
@@ -5642,7 +5652,7 @@
         <v>46091.73446609954</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5666,7 +5676,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5679,7 +5689,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B72" s="5">
         <v>46073.71759075232</v>
@@ -5689,7 +5699,7 @@
         <v>46163.2036187037</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5716,13 +5726,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q72" s="5">
         <v>46162</v>
@@ -5742,7 +5752,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B73" s="8">
         <v>46073.71759101852</v>
@@ -5752,7 +5762,7 @@
         <v>46168.18663340277</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5779,13 +5789,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q73" s="8">
         <v>46163</v>
@@ -5805,7 +5815,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B74" s="5">
         <v>46073.71759130787</v>
@@ -5815,16 +5825,16 @@
         <v>46169.16854244213</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I74" s="5">
         <v>46168</v>
@@ -5842,13 +5852,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q74" s="5">
         <v>46168</v>
@@ -5868,7 +5878,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B75" s="8">
         <v>46073.7175915625</v>
@@ -5878,16 +5888,16 @@
         <v>46170.19857011574</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -5903,13 +5913,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q75" s="8">
         <v>46169</v>
@@ -5929,7 +5939,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B76" s="5">
         <v>46073.71759184028</v>
@@ -5939,7 +5949,7 @@
         <v>46091.73446550926</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5963,7 +5973,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5982,7 +5992,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B77" s="8">
         <v>46073.71759210648</v>
@@ -5992,16 +6002,16 @@
         <v>46179.199858576394</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I77" s="8">
         <v>46170</v>
@@ -6019,13 +6029,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q77" s="8">
         <v>46170</v>
@@ -6045,7 +6055,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B78" s="5">
         <v>46073.71759238426</v>
@@ -6055,16 +6065,16 @@
         <v>46179.19985642361</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>279</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I78" s="5">
         <v>46170</v>
@@ -6082,13 +6092,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q78" s="5">
         <v>46170</v>
@@ -6108,7 +6118,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B79" s="8">
         <v>46091.72839834491</v>
@@ -6118,7 +6128,7 @@
         <v>46091.73565777778</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6142,7 +6152,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6161,7 +6171,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B80" s="5">
         <v>46091.72894082176</v>
@@ -6171,7 +6181,7 @@
         <v>46179.199856562496</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6198,13 +6208,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q80" s="5">
         <v>46170</v>
@@ -6224,7 +6234,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B81" s="8">
         <v>46091.72900166667</v>
@@ -6234,7 +6244,7 @@
         <v>46190.17451866898</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6261,13 +6271,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q81" s="8">
         <v>46181</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="293">
   <si>
     <t xml:space="preserve">50001498-CALABRESSE METRO STO DOMINGO  POZOS  </t>
   </si>
@@ -319,258 +319,258 @@
     <t>Alabe,Tablero OT 4201,rodete OT 4200,Motor,Sensores,Materiales a codigo // compras locales aprovisionamientomiento:OT  4200</t>
   </si>
   <si>
+    <t>1213380470331424</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC motor,Fabricación motor,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>1213380470331425</t>
+  </si>
+  <si>
+    <t>Generación OC motor</t>
+  </si>
+  <si>
+    <t>Fabricación motor,Planos motor proveedor,Motor</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>1213380470331426</t>
+  </si>
+  <si>
+    <t>Fabricación motor</t>
+  </si>
+  <si>
+    <t>Motor,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1213380470331427</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>Motor,Planos Definitivos</t>
+  </si>
+  <si>
+    <t>1213380470331415</t>
+  </si>
+  <si>
+    <t>Alabe</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe,Fabricación Alabe</t>
+  </si>
+  <si>
+    <t>1213380470331416</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe,Alabe</t>
+  </si>
+  <si>
+    <t>1213380470331417</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe</t>
+  </si>
+  <si>
+    <t>Alabe,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1213380470331421</t>
+  </si>
+  <si>
+    <t>rodete OT 4200</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4200,Fabricación Rodete OT 4200</t>
+  </si>
+  <si>
+    <t>1213380470331422</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4200</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4200,rodete OT 4200</t>
+  </si>
+  <si>
+    <t>1213380470331423</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4200</t>
+  </si>
+  <si>
+    <t>rodete OT 4200,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1213380470331418</t>
+  </si>
+  <si>
+    <t>Tablero OT 4201</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros ot 4201,Fabricación Tablero ot 4201</t>
+  </si>
+  <si>
+    <t>1213380470331419</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros ot 4201</t>
+  </si>
+  <si>
+    <t>Fabricación Tablero ot 4201,Tablero OT 4201</t>
+  </si>
+  <si>
+    <t>1213380470331420</t>
+  </si>
+  <si>
+    <t>Fabricación Tablero ot 4201</t>
+  </si>
+  <si>
+    <t>Tablero OT 4201,Recepcion Tableros</t>
+  </si>
+  <si>
+    <t>1213402049403980</t>
+  </si>
+  <si>
+    <t>Sensores</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Sensores ,Fabricación Sensores </t>
+  </si>
+  <si>
+    <t>1213402049403981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Sensores </t>
+  </si>
+  <si>
+    <t>Fabricación Sensores ,Sensores</t>
+  </si>
+  <si>
+    <t>1213402049403982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Sensores </t>
+  </si>
+  <si>
+    <t>Sensores,Materiales a codigo // compras locales aprovisionamientomiento:OT  4200,Recepción Sensores</t>
+  </si>
+  <si>
+    <t>1213380470331428</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento:OT  4200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC materiales OT 4200,Fabricación Sensores </t>
+  </si>
+  <si>
+    <t>1213380470331429</t>
+  </si>
+  <si>
+    <t>Generación OC materiales OT 4200</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales OT 4200,Materiales a codigo // compras locales aprovisionamientomiento:OT  4200</t>
+  </si>
+  <si>
+    <t>1213380470331430</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales OT 4200</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213380470331431</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Planos Definitivos,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>1213380470331432</t>
+  </si>
+  <si>
+    <t>Planos Preliminar</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Planos Definitivos</t>
+  </si>
+  <si>
+    <t>1213380470331433</t>
+  </si>
+  <si>
+    <t>Planos Definitivos</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Check Planos</t>
+  </si>
+  <si>
+    <t>1213595645393446</t>
+  </si>
+  <si>
+    <t>Check Planos</t>
+  </si>
+  <si>
+    <t>Armado fabricación externa ,Control de calidad Armado,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje Sensores</t>
+  </si>
+  <si>
+    <t>1213595645393447</t>
+  </si>
+  <si>
+    <t>Check Pruebas fat</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
-    <t>1213380470331424</t>
-  </si>
-  <si>
-    <t>Motor</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC motor,Fabricación motor,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>1213380470331425</t>
-  </si>
-  <si>
-    <t>Generación OC motor</t>
-  </si>
-  <si>
-    <t>Fabricación motor,Planos motor proveedor,Motor</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>1213380470331426</t>
-  </si>
-  <si>
-    <t>Fabricación motor</t>
-  </si>
-  <si>
-    <t>Motor,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1213380470331427</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>Motor,Planos Definitivos</t>
-  </si>
-  <si>
-    <t>1213380470331415</t>
-  </si>
-  <si>
-    <t>Alabe</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe,Fabricación Alabe</t>
-  </si>
-  <si>
-    <t>1213380470331416</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe,Alabe</t>
-  </si>
-  <si>
-    <t>1213380470331417</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe</t>
-  </si>
-  <si>
-    <t>Alabe,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1213380470331421</t>
-  </si>
-  <si>
-    <t>rodete OT 4200</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4200,Fabricación Rodete OT 4200</t>
-  </si>
-  <si>
-    <t>1213380470331422</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4200</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4200,rodete OT 4200</t>
-  </si>
-  <si>
-    <t>1213380470331423</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4200</t>
-  </si>
-  <si>
-    <t>rodete OT 4200,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1213380470331418</t>
-  </si>
-  <si>
-    <t>Tablero OT 4201</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros ot 4201,Fabricación Tablero ot 4201</t>
-  </si>
-  <si>
-    <t>1213380470331419</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros ot 4201</t>
-  </si>
-  <si>
-    <t>Fabricación Tablero ot 4201,Tablero OT 4201</t>
-  </si>
-  <si>
-    <t>1213380470331420</t>
-  </si>
-  <si>
-    <t>Fabricación Tablero ot 4201</t>
-  </si>
-  <si>
-    <t>Tablero OT 4201,Recepcion Tableros</t>
-  </si>
-  <si>
-    <t>1213402049403980</t>
-  </si>
-  <si>
-    <t>Sensores</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Sensores ,Fabricación Sensores </t>
-  </si>
-  <si>
-    <t>1213402049403981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Sensores </t>
-  </si>
-  <si>
-    <t>Fabricación Sensores ,Sensores</t>
-  </si>
-  <si>
-    <t>1213402049403982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Sensores </t>
-  </si>
-  <si>
-    <t>Sensores,Materiales a codigo // compras locales aprovisionamientomiento:OT  4200,Recepción Sensores</t>
-  </si>
-  <si>
-    <t>1213380470331428</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento:OT  4200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC materiales OT 4200,Fabricación Sensores </t>
-  </si>
-  <si>
-    <t>1213380470331429</t>
-  </si>
-  <si>
-    <t>Generación OC materiales OT 4200</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales OT 4200,Materiales a codigo // compras locales aprovisionamientomiento:OT  4200</t>
-  </si>
-  <si>
-    <t>1213380470331430</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales OT 4200</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213380470331431</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Planos Definitivos,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1213380470331432</t>
-  </si>
-  <si>
-    <t>Planos Preliminar</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Planos Definitivos</t>
-  </si>
-  <si>
-    <t>1213380470331433</t>
-  </si>
-  <si>
-    <t>Planos Definitivos</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Check Planos</t>
-  </si>
-  <si>
-    <t>1213595645393446</t>
-  </si>
-  <si>
-    <t>Check Planos</t>
-  </si>
-  <si>
-    <t>Armado fabricación externa ,Control de calidad Armado,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje Sensores</t>
-  </si>
-  <si>
-    <t>1213595645393447</t>
-  </si>
-  <si>
-    <t>Check Pruebas fat</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
     <t>1213380470331434</t>
   </si>
   <si>
@@ -791,6 +791,12 @@
   </si>
   <si>
     <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
   </si>
   <si>
     <t>Embalaje,Logistica:</t>
@@ -2803,9 +2809,11 @@
       <c r="B25" s="8">
         <v>46073.71759071759</v>
       </c>
-      <c r="C25" s="9"/>
+      <c r="C25" s="8">
+        <v>46204.6994087037</v>
+      </c>
       <c r="D25" s="8">
-        <v>46191.88830023148</v>
+        <v>46204.69942763889</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2839,15 +2847,17 @@
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
+      <c r="S25" s="9">
+        <v>1</v>
+      </c>
       <c r="T25" s="9"/>
-      <c r="U25" s="12" t="s">
-        <v>102</v>
+      <c r="U25" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B26" s="5">
         <v>46073.7175902662</v>
@@ -2859,16 +2869,16 @@
         <v>46155.86710392361</v>
       </c>
       <c r="E26" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="I26" s="5">
         <v>46006</v>
@@ -2889,7 +2899,7 @@
         <v>100</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>100</v>
@@ -2912,7 +2922,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B27" s="8">
         <v>46073.7175905787</v>
@@ -2924,16 +2934,16 @@
         <v>46097.52605688658</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="I27" s="8">
         <v>46006</v>
@@ -2951,13 +2961,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>79</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2965,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U27" s="10" t="s">
         <v>56</v>
@@ -2973,7 +2983,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46073.71759086805</v>
@@ -2985,16 +2995,16 @@
         <v>46155.866878229164</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="I28" s="5">
         <v>46027</v>
@@ -3012,13 +3022,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3026,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U28" s="10" t="s">
         <v>56</v>
@@ -3034,7 +3044,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46073.71759118055</v>
@@ -3046,16 +3056,16 @@
         <v>46128.63717174769</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="I29" s="8">
         <v>46027</v>
@@ -3073,13 +3083,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3087,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U29" s="10" t="s">
         <v>56</v>
@@ -3095,7 +3105,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46073.7175909838</v>
@@ -3107,16 +3117,16 @@
         <v>46155.90358277778</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="I30" s="5">
         <v>46013</v>
@@ -3137,7 +3147,7 @@
         <v>100</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>100</v>
@@ -3160,7 +3170,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B31" s="8">
         <v>46073.71759126158</v>
@@ -3172,16 +3182,16 @@
         <v>46097.52608802084</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="I31" s="8">
         <v>46013</v>
@@ -3199,13 +3209,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>82</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3213,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U31" s="10" t="s">
         <v>56</v>
@@ -3221,7 +3231,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46073.71759153935</v>
@@ -3233,16 +3243,16 @@
         <v>46155.90355751157</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="I32" s="5">
         <v>46017</v>
@@ -3260,13 +3270,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3274,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U32" s="10" t="s">
         <v>56</v>
@@ -3282,7 +3292,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46073.717592685185</v>
@@ -3294,16 +3304,16 @@
         <v>46182.683057222224</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="I33" s="8">
         <v>46013</v>
@@ -3324,7 +3334,7 @@
         <v>100</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>100</v>
@@ -3347,7 +3357,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46073.71759302083</v>
@@ -3359,16 +3369,16 @@
         <v>46182.6827475</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="I34" s="5">
         <v>46013</v>
@@ -3386,13 +3396,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3400,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U34" s="10" t="s">
         <v>56</v>
@@ -3408,7 +3418,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46073.71758986111</v>
@@ -3420,16 +3430,16 @@
         <v>46182.682943541666</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="I35" s="8">
         <v>46017</v>
@@ -3447,13 +3457,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3461,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U35" s="10" t="s">
         <v>56</v>
@@ -3469,7 +3479,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46073.7175918287</v>
@@ -3481,16 +3491,16 @@
         <v>46191.89070638889</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="I36" s="5">
         <v>46007</v>
@@ -3511,7 +3521,7 @@
         <v>100</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>100</v>
@@ -3534,7 +3544,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8">
         <v>46073.71759209491</v>
@@ -3546,16 +3556,16 @@
         <v>46169.84329747685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="I37" s="8">
         <v>46007</v>
@@ -3573,13 +3583,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>89</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3587,7 +3597,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U37" s="10" t="s">
         <v>56</v>
@@ -3595,7 +3605,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46073.71759234954</v>
@@ -3605,16 +3615,16 @@
         <v>46191.88833190972</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="I38" s="5">
         <v>46017</v>
@@ -3632,13 +3642,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3646,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U38" s="10" t="s">
         <v>56</v>
@@ -3654,7 +3664,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46076.59415034722</v>
@@ -3666,16 +3676,16 @@
         <v>46156.618615775464</v>
       </c>
       <c r="E39" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="9" t="s">
+      <c r="H39" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>148</v>
       </c>
       <c r="I39" s="8">
         <v>46013</v>
@@ -3696,7 +3706,7 @@
         <v>100</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>100</v>
@@ -3719,7 +3729,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46076.59428157407</v>
@@ -3731,16 +3741,16 @@
         <v>46154.86737356482</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46013</v>
@@ -3758,13 +3768,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>92</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="5">
         <v>46013</v>
@@ -3776,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U40" s="10" t="s">
         <v>56</v>
@@ -3784,7 +3794,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46076.59448399306</v>
@@ -3796,16 +3806,16 @@
         <v>46154.86810545139</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>148</v>
       </c>
       <c r="I41" s="8">
         <v>46057</v>
@@ -3823,13 +3833,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="8">
         <v>46057</v>
@@ -3841,7 +3851,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U41" s="10" t="s">
         <v>56</v>
@@ -3849,7 +3859,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46073.71759148148</v>
@@ -3861,16 +3871,16 @@
         <v>46182.53063152778</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I42" s="5">
         <v>46013</v>
@@ -3891,7 +3901,7 @@
         <v>100</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>100</v>
@@ -3914,7 +3924,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46073.717591759254</v>
@@ -3926,16 +3936,16 @@
         <v>46182.53047055556</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>148</v>
       </c>
       <c r="I43" s="8">
         <v>46013</v>
@@ -3953,13 +3963,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>95</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3967,7 +3977,7 @@
         <v>0</v>
       </c>
       <c r="T43" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U43" s="10" t="s">
         <v>56</v>
@@ -3975,7 +3985,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46073.71759204861</v>
@@ -3987,16 +3997,16 @@
         <v>46182.53060627315</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I44" s="5">
         <v>46037</v>
@@ -4014,13 +4024,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4028,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="T44" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U44" s="10" t="s">
         <v>56</v>
@@ -4036,7 +4046,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8">
         <v>46073.71759234954</v>
@@ -4046,7 +4056,7 @@
         <v>46156.618706249996</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4070,7 +4080,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4083,7 +4093,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46073.717592615736</v>
@@ -4095,16 +4105,16 @@
         <v>46154.09504209491</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>170</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>171</v>
       </c>
       <c r="I46" s="5">
         <v>46009</v>
@@ -4122,13 +4132,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q46" s="5">
         <v>46009</v>
@@ -4148,7 +4158,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B47" s="8">
         <v>46073.71758997685</v>
@@ -4160,16 +4170,16 @@
         <v>46154.09509461805</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="H47" s="9" t="s">
         <v>170</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>171</v>
       </c>
       <c r="I47" s="8">
         <v>46065</v>
@@ -4187,13 +4197,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O47" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="P47" s="9" t="s">
         <v>175</v>
-      </c>
-      <c r="P47" s="9" t="s">
-        <v>176</v>
       </c>
       <c r="Q47" s="8">
         <v>46065</v>
@@ -4213,7 +4223,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46091.72801988426</v>
@@ -4225,16 +4235,16 @@
         <v>46154.09513386574</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>170</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>171</v>
       </c>
       <c r="I48" s="5">
         <v>46072</v>
@@ -4252,13 +4262,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="5">
         <v>46072</v>
@@ -4278,7 +4288,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46091.728057939814</v>
@@ -4288,16 +4298,16 @@
         <v>46198.821597800925</v>
       </c>
       <c r="E49" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="9" t="s">
+      <c r="H49" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I49" s="8">
         <v>46160</v>
@@ -4315,13 +4325,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O49" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="P49" s="9" t="s">
         <v>184</v>
-      </c>
-      <c r="P49" s="9" t="s">
-        <v>185</v>
       </c>
       <c r="Q49" s="8">
         <v>46160</v>
@@ -4336,7 +4346,7 @@
         <v>31</v>
       </c>
       <c r="U49" s="12" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4406,7 +4416,7 @@
         <v>46191.788422488426</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
@@ -4436,7 +4446,7 @@
         <v>187</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>192</v>
@@ -4501,7 +4511,7 @@
         <v>187</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>197</v>
@@ -4767,7 +4777,7 @@
         <v>31</v>
       </c>
       <c r="U56" s="12" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4861,7 +4871,7 @@
         <v>187</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>218</v>
@@ -4926,7 +4936,7 @@
         <v>187</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>221</v>
@@ -4991,7 +5001,7 @@
         <v>187</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>224</v>
@@ -5054,7 +5064,7 @@
         <v>187</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>226</v>
@@ -5072,7 +5082,7 @@
         <v>31</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5119,7 +5129,7 @@
         <v>187</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>229</v>
@@ -5314,7 +5324,7 @@
         <v>31</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5379,7 +5389,7 @@
         <v>230</v>
       </c>
       <c r="U66" s="12" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5444,7 +5454,7 @@
         <v>31</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5509,7 +5519,7 @@
         <v>31</v>
       </c>
       <c r="U68" s="12" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5526,7 +5536,7 @@
         <v>46195.868219131946</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5589,7 +5599,7 @@
         <v>46162.1685475</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5619,7 +5629,7 @@
         <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>254</v>
@@ -5696,7 +5706,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46163.2036187037</v>
+        <v>46204.700362476855</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5705,10 +5715,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>35</v>
+        <v>260</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>36</v>
+        <v>261</v>
       </c>
       <c r="I72" s="5">
         <v>46162</v>
@@ -5729,10 +5739,10 @@
         <v>256</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q72" s="5">
         <v>46162</v>
@@ -5752,7 +5762,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B73" s="8">
         <v>46073.71759101852</v>
@@ -5762,7 +5772,7 @@
         <v>46168.18663340277</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5792,10 +5802,10 @@
         <v>256</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q73" s="8">
         <v>46163</v>
@@ -5815,7 +5825,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B74" s="5">
         <v>46073.71759130787</v>
@@ -5825,16 +5835,16 @@
         <v>46169.16854244213</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I74" s="5">
         <v>46168</v>
@@ -5855,10 +5865,10 @@
         <v>256</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q74" s="5">
         <v>46168</v>
@@ -5878,7 +5888,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B75" s="8">
         <v>46073.7175915625</v>
@@ -5888,16 +5898,16 @@
         <v>46170.19857011574</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -5916,10 +5926,10 @@
         <v>256</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q75" s="8">
         <v>46169</v>
@@ -5939,7 +5949,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B76" s="5">
         <v>46073.71759184028</v>
@@ -5949,7 +5959,7 @@
         <v>46091.73446550926</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5973,7 +5983,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5984,7 +5994,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U76" s="10" t="s">
         <v>56</v>
@@ -5992,7 +6002,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B77" s="8">
         <v>46073.71759210648</v>
@@ -6002,16 +6012,16 @@
         <v>46179.199858576394</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I77" s="8">
         <v>46170</v>
@@ -6029,13 +6039,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q77" s="8">
         <v>46170</v>
@@ -6055,7 +6065,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B78" s="5">
         <v>46073.71759238426</v>
@@ -6065,16 +6075,16 @@
         <v>46179.19985642361</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>281</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>279</v>
       </c>
       <c r="I78" s="5">
         <v>46170</v>
@@ -6092,13 +6102,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q78" s="5">
         <v>46170</v>
@@ -6118,7 +6128,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B79" s="8">
         <v>46091.72839834491</v>
@@ -6128,7 +6138,7 @@
         <v>46091.73565777778</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6152,7 +6162,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6163,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="T79" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="U79" s="10" t="s">
         <v>56</v>
@@ -6171,7 +6181,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B80" s="5">
         <v>46091.72894082176</v>
@@ -6181,7 +6191,7 @@
         <v>46179.199856562496</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6208,13 +6218,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q80" s="5">
         <v>46170</v>
@@ -6234,7 +6244,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B81" s="8">
         <v>46091.72900166667</v>
@@ -6244,7 +6254,7 @@
         <v>46190.17451866898</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6271,13 +6281,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q81" s="8">
         <v>46181</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -1516,13 +1516,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.717590115746</v>
+        <v>46073.550923449075</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.724617025466</v>
+        <v>46092.557950358794</v>
       </c>
       <c r="D4" s="5">
-        <v>46114.81259290509</v>
+        <v>46114.64592623843</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1565,13 +1565,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.71759079861</v>
+        <v>46073.550924131945</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.724584826385</v>
+        <v>46092.55791815972</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.72461795139</v>
+        <v>46092.55795128472</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1630,13 +1630,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.71759107639</v>
+        <v>46073.55092440972</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.72458534723</v>
+        <v>46092.557918680555</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.72461783564</v>
+        <v>46092.55795116899</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1695,13 +1695,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.717591354165</v>
+        <v>46073.5509246875</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.72458572917</v>
+        <v>46092.5579190625</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.72461775463</v>
+        <v>46092.55795108796</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1758,13 +1758,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.71759162037</v>
+        <v>46073.5509249537</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72458613426</v>
+        <v>46092.557919467596</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.71077443287</v>
+        <v>46100.5441077662</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1821,13 +1821,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.71759189815</v>
+        <v>46073.55092523148</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.72458673611</v>
+        <v>46092.55792006945</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.72461730324</v>
+        <v>46092.557950636576</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1884,11 +1884,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.71759215278</v>
+        <v>46073.55092548611</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.5263790625</v>
+        <v>46097.35971239583</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1931,13 +1931,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.71759246528</v>
+        <v>46073.55092579861</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.526363854166</v>
+        <v>46097.3596971875</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.52638289351</v>
+        <v>46097.359716226856</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1996,11 +1996,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.71759273148</v>
+        <v>46073.55092606481</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46126.19500706019</v>
+        <v>46126.02834039352</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2059,13 +2059,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.71759298611</v>
+        <v>46073.55092631944</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51026252315</v>
+        <v>46114.34359585648</v>
       </c>
       <c r="D13" s="8">
-        <v>46169.884381701384</v>
+        <v>46169.71771503473</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2108,13 +2108,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.71759060185</v>
+        <v>46073.55092393518</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.52584498843</v>
+        <v>46097.359178321756</v>
       </c>
       <c r="D14" s="5">
-        <v>46100.761380717595</v>
+        <v>46100.59471405092</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2173,13 +2173,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.71759128472</v>
+        <v>46073.55092461806</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.50878793982</v>
+        <v>46114.34212127315</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.50880758102</v>
+        <v>46114.34214091435</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2238,13 +2238,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.71759157407</v>
+        <v>46073.55092490741</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.50922814815</v>
+        <v>46114.34256148148</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.509243865745</v>
+        <v>46114.34257719907</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2303,13 +2303,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.71759186343</v>
+        <v>46073.55092519676</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.51024402778</v>
+        <v>46114.34357736111</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.51026347222</v>
+        <v>46114.34359680556</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2368,13 +2368,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.717592141205</v>
+        <v>46073.55092547454</v>
       </c>
       <c r="C18" s="5">
-        <v>46169.88424704861</v>
+        <v>46169.71758038194</v>
       </c>
       <c r="D18" s="5">
-        <v>46169.88433502315</v>
+        <v>46169.71766835648</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2417,13 +2417,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.71759269676</v>
+        <v>46073.55092603009</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.525949456016</v>
+        <v>46097.35928278935</v>
       </c>
       <c r="D19" s="8">
-        <v>46156.61850119213</v>
+        <v>46156.45183452546</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2482,13 +2482,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.71759241898</v>
+        <v>46073.550925752315</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.5259784375</v>
+        <v>46097.35931177084</v>
       </c>
       <c r="D20" s="5">
-        <v>46156.61851966435</v>
+        <v>46156.451852997685</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2547,13 +2547,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.717593298614</v>
+        <v>46073.55092663194</v>
       </c>
       <c r="C21" s="8">
-        <v>46128.433728668984</v>
+        <v>46128.26706200231</v>
       </c>
       <c r="D21" s="8">
-        <v>46128.433750393524</v>
+        <v>46128.26708372685</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2612,13 +2612,13 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.71759302083</v>
+        <v>46073.55092635417</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.52660114583</v>
+        <v>46097.359934479166</v>
       </c>
       <c r="D22" s="5">
-        <v>46097.52662200232</v>
+        <v>46097.35995533565</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2677,13 +2677,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.593357997685</v>
+        <v>46076.42669133102</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.51032266204</v>
+        <v>46114.34365599537</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.51047230324</v>
+        <v>46114.34380563657</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2742,13 +2742,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.71759033565</v>
+        <v>46073.55092366898</v>
       </c>
       <c r="C24" s="5">
-        <v>46169.88422872685</v>
+        <v>46169.717562060185</v>
       </c>
       <c r="D24" s="5">
-        <v>46169.884247326394</v>
+        <v>46169.71758065972</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2807,13 +2807,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.71759071759</v>
+        <v>46073.55092405093</v>
       </c>
       <c r="C25" s="8">
-        <v>46204.6994087037</v>
+        <v>46204.53274203704</v>
       </c>
       <c r="D25" s="8">
-        <v>46204.69942763889</v>
+        <v>46204.53276097222</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2860,13 +2860,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.7175902662</v>
+        <v>46073.55092359954</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.86689138889</v>
+        <v>46155.700224722226</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.86710392361</v>
+        <v>46155.70043725694</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -2925,13 +2925,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.7175905787</v>
+        <v>46073.55092391204</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.52605542824</v>
+        <v>46097.35938876157</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.52605688658</v>
+        <v>46097.359390219906</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>108</v>
@@ -2986,13 +2986,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.71759086805</v>
+        <v>46073.550924201394</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.86687702546</v>
+        <v>46155.700210358795</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.866878229164</v>
+        <v>46155.7002115625</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3047,13 +3047,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.71759118055</v>
+        <v>46073.55092451389</v>
       </c>
       <c r="C29" s="8">
-        <v>46128.637161886574</v>
+        <v>46128.47049521991</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.63717174769</v>
+        <v>46128.470505081015</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3108,13 +3108,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.7175909838</v>
+        <v>46073.550924317125</v>
       </c>
       <c r="C30" s="5">
-        <v>46155.903569421294</v>
+        <v>46155.73690275463</v>
       </c>
       <c r="D30" s="5">
-        <v>46155.90358277778</v>
+        <v>46155.73691611111</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3173,13 +3173,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.71759126158</v>
+        <v>46073.55092459491</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.526086377315</v>
+        <v>46097.35941971064</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.52608802084</v>
+        <v>46097.359421354166</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3234,13 +3234,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.71759153935</v>
+        <v>46073.55092487269</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.903555972225</v>
+        <v>46155.73688930555</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.90355751157</v>
+        <v>46155.736890844906</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3295,13 +3295,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.717592685185</v>
+        <v>46073.55092601852</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.68305543982</v>
+        <v>46182.51638877315</v>
       </c>
       <c r="D33" s="8">
-        <v>46182.683057222224</v>
+        <v>46182.51639055555</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3360,13 +3360,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.71759302083</v>
+        <v>46073.55092635417</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.68274605324</v>
+        <v>46182.51607938657</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.6827475</v>
+        <v>46182.51608083333</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3421,13 +3421,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.71758986111</v>
+        <v>46073.550923194445</v>
       </c>
       <c r="C35" s="8">
-        <v>46182.682942314816</v>
+        <v>46182.516275648144</v>
       </c>
       <c r="D35" s="8">
-        <v>46182.682943541666</v>
+        <v>46182.516276875</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3482,13 +3482,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.7175918287</v>
+        <v>46073.55092516204</v>
       </c>
       <c r="C36" s="5">
-        <v>46191.888280127314</v>
+        <v>46191.72161346065</v>
       </c>
       <c r="D36" s="5">
-        <v>46191.89070638889</v>
+        <v>46191.72403972222</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3547,13 +3547,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.71759209491</v>
+        <v>46073.55092542824</v>
       </c>
       <c r="C37" s="8">
-        <v>46097.526664247685</v>
+        <v>46097.35999758102</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.84329747685</v>
+        <v>46169.67663081019</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3608,11 +3608,11 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.71759234954</v>
+        <v>46073.55092568287</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46191.88833190972</v>
+        <v>46191.72166524305</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3667,13 +3667,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46076.59415034722</v>
+        <v>46076.427483680556</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.86805253472</v>
+        <v>46154.70138586806</v>
       </c>
       <c r="D39" s="8">
-        <v>46156.618615775464</v>
+        <v>46156.4519491088</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3732,13 +3732,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46076.59428157407</v>
+        <v>46076.42761490741</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.86737157407</v>
+        <v>46154.70070490741</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.86737356482</v>
+        <v>46154.70070689815</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3797,13 +3797,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46076.59448399306</v>
+        <v>46076.42781732639</v>
       </c>
       <c r="C41" s="8">
-        <v>46154.86810417824</v>
+        <v>46154.70143751157</v>
       </c>
       <c r="D41" s="8">
-        <v>46154.86810545139</v>
+        <v>46154.70143878472</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3862,13 +3862,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.71759148148</v>
+        <v>46073.550924814816</v>
       </c>
       <c r="C42" s="5">
-        <v>46182.530618530094</v>
+        <v>46182.36395186343</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.53063152778</v>
+        <v>46182.36396486111</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3927,13 +3927,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.717591759254</v>
+        <v>46073.5509250926</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.53046844907</v>
+        <v>46182.36380178241</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.53047055556</v>
+        <v>46182.36380388889</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3988,13 +3988,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.71759204861</v>
+        <v>46073.55092538195</v>
       </c>
       <c r="C44" s="5">
-        <v>46182.530605011576</v>
+        <v>46182.363938344904</v>
       </c>
       <c r="D44" s="5">
-        <v>46182.53060627315</v>
+        <v>46182.36393960648</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4049,11 +4049,11 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.71759234954</v>
+        <v>46073.55092568287</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46156.618706249996</v>
+        <v>46156.45203958334</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4096,13 +4096,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.717592615736</v>
+        <v>46073.55092594908</v>
       </c>
       <c r="C46" s="5">
-        <v>46154.09501991898</v>
+        <v>46153.92835325231</v>
       </c>
       <c r="D46" s="5">
-        <v>46154.09504209491</v>
+        <v>46153.92837542824</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4161,13 +4161,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.71758997685</v>
+        <v>46073.550923310184</v>
       </c>
       <c r="C47" s="8">
-        <v>46154.09507998843</v>
+        <v>46153.92841332176</v>
       </c>
       <c r="D47" s="8">
-        <v>46154.09509461805</v>
+        <v>46153.92842795139</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4226,13 +4226,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46091.72801988426</v>
+        <v>46091.56135321759</v>
       </c>
       <c r="C48" s="5">
-        <v>46154.09511894676</v>
+        <v>46153.92845228009</v>
       </c>
       <c r="D48" s="5">
-        <v>46154.09513386574</v>
+        <v>46153.928467199075</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4291,11 +4291,11 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46091.728057939814</v>
+        <v>46091.56139127315</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46198.821597800925</v>
+        <v>46198.65493113426</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4354,13 +4354,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.71759030093</v>
+        <v>46073.55092363426</v>
       </c>
       <c r="C50" s="5">
-        <v>46191.78929271991</v>
+        <v>46191.62262605324</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.789304328704</v>
+        <v>46191.62263766203</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>187</v>
@@ -4407,13 +4407,13 @@
         <v>189</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.7175905787</v>
+        <v>46073.55092391204</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.788401875005</v>
+        <v>46191.62173520833</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.788422488426</v>
+        <v>46191.62175582176</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>163</v>
@@ -4472,13 +4472,13 @@
         <v>193</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.717590810185</v>
+        <v>46073.55092414352</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.78927659722</v>
+        <v>46191.62260993056</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.789293194444</v>
+        <v>46191.62262652778</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>194</v>
@@ -4537,13 +4537,13 @@
         <v>198</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.717591099536</v>
+        <v>46073.55092443287</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.79037481482</v>
+        <v>46191.62370814815</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.79038505787</v>
+        <v>46191.6237183912</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>199</v>
@@ -4590,13 +4590,13 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.71759134259</v>
+        <v>46073.550924675925</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.7899369213</v>
+        <v>46191.623270254626</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.7899528125</v>
+        <v>46191.623286145834</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4655,13 +4655,13 @@
         <v>206</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.71759157407</v>
+        <v>46073.55092490741</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.79035826389</v>
+        <v>46191.623691597226</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.790375833334</v>
+        <v>46191.62370916667</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>207</v>
@@ -4720,13 +4720,13 @@
         <v>210</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.71759181713</v>
+        <v>46073.55092515046</v>
       </c>
       <c r="C56" s="5">
-        <v>46191.789681423616</v>
+        <v>46191.623014756944</v>
       </c>
       <c r="D56" s="5">
-        <v>46191.79037549769</v>
+        <v>46191.623708831015</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>211</v>
@@ -4785,11 +4785,11 @@
         <v>214</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.71759206019</v>
+        <v>46073.550925393516</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46198.827981574075</v>
+        <v>46198.66131490741</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>187</v>
@@ -4832,13 +4832,13 @@
         <v>216</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.71759105324</v>
+        <v>46073.550924386574</v>
       </c>
       <c r="C58" s="5">
-        <v>46195.608916770834</v>
+        <v>46195.44225010417</v>
       </c>
       <c r="D58" s="5">
-        <v>46195.60893649305</v>
+        <v>46195.44226982639</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>217</v>
@@ -4897,13 +4897,13 @@
         <v>219</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.71759083333</v>
+        <v>46073.550924166666</v>
       </c>
       <c r="C59" s="8">
-        <v>46195.60909078704</v>
+        <v>46195.44242412037</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.60910890046</v>
+        <v>46195.4424422338</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>220</v>
@@ -4962,13 +4962,13 @@
         <v>222</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.71759233796</v>
+        <v>46073.5509256713</v>
       </c>
       <c r="C60" s="5">
-        <v>46198.82797583334</v>
+        <v>46198.661309166666</v>
       </c>
       <c r="D60" s="5">
-        <v>46198.82799237268</v>
+        <v>46198.66132570602</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>223</v>
@@ -5027,11 +5027,11 @@
         <v>225</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.71759050926</v>
+        <v>46073.55092384259</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46191.88833803241</v>
+        <v>46191.72167136574</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5090,13 +5090,13 @@
         <v>227</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.59959273148</v>
+        <v>46076.432926064816</v>
       </c>
       <c r="C62" s="5">
-        <v>46198.82946502315</v>
+        <v>46198.66279835648</v>
       </c>
       <c r="D62" s="5">
-        <v>46198.829483009264</v>
+        <v>46198.66281634259</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>228</v>
@@ -5155,11 +5155,11 @@
         <v>231</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.71759130787</v>
+        <v>46073.550924641204</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.86820844907</v>
+        <v>46195.70154178241</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>232</v>
@@ -5202,13 +5202,13 @@
         <v>234</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.71759155093</v>
+        <v>46073.55092488426</v>
       </c>
       <c r="C64" s="5">
-        <v>46193.60723070602</v>
+        <v>46193.44056403935</v>
       </c>
       <c r="D64" s="5">
-        <v>46193.60726542824</v>
+        <v>46193.440598761576</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>235</v>
@@ -5267,13 +5267,13 @@
         <v>237</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.71759180556</v>
+        <v>46073.55092513889</v>
       </c>
       <c r="C65" s="8">
-        <v>46193.60739422454</v>
+        <v>46193.44072755787</v>
       </c>
       <c r="D65" s="8">
-        <v>46195.608936585646</v>
+        <v>46195.44226991898</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5332,13 +5332,13 @@
         <v>241</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.717592037036</v>
+        <v>46073.55092537037</v>
       </c>
       <c r="C66" s="5">
-        <v>46193.60745574074</v>
+        <v>46193.44078907407</v>
       </c>
       <c r="D66" s="5">
-        <v>46195.60911005787</v>
+        <v>46195.442443391206</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>242</v>
@@ -5397,13 +5397,13 @@
         <v>245</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.71759226852</v>
+        <v>46073.550925601856</v>
       </c>
       <c r="C67" s="8">
-        <v>46193.607493668984</v>
+        <v>46193.44082700231</v>
       </c>
       <c r="D67" s="8">
-        <v>46198.82799127315</v>
+        <v>46198.66132460648</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>246</v>
@@ -5462,13 +5462,13 @@
         <v>248</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.600719699076</v>
+        <v>46076.43405303241</v>
       </c>
       <c r="C68" s="5">
-        <v>46193.60764289352</v>
+        <v>46193.44097622685</v>
       </c>
       <c r="D68" s="5">
-        <v>46198.82948185185</v>
+        <v>46198.662815185184</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>229</v>
@@ -5527,13 +5527,13 @@
         <v>250</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.71759252315</v>
+        <v>46073.550925856485</v>
       </c>
       <c r="C69" s="8">
-        <v>46195.86820241898</v>
+        <v>46195.70153575232</v>
       </c>
       <c r="D69" s="8">
-        <v>46195.868219131946</v>
+        <v>46195.70155246528</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>183</v>
@@ -5592,11 +5592,11 @@
         <v>253</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.7175927662</v>
+        <v>46073.55092609954</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46162.1685475</v>
+        <v>46162.00188083333</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>184</v>
@@ -5655,11 +5655,11 @@
         <v>255</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.71759042824</v>
+        <v>46073.55092376158</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46091.73446609954</v>
+        <v>46091.56779943287</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>256</v>
@@ -5702,11 +5702,11 @@
         <v>258</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.71759075232</v>
+        <v>46073.55092408565</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46204.700362476855</v>
+        <v>46204.53369581018</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5765,11 +5765,11 @@
         <v>263</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.71759101852</v>
+        <v>46073.55092435185</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46168.18663340277</v>
+        <v>46168.019966736116</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>264</v>
@@ -5828,11 +5828,11 @@
         <v>267</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.71759130787</v>
+        <v>46073.550924641204</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46169.16854244213</v>
+        <v>46169.00187577546</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>268</v>
@@ -5891,11 +5891,11 @@
         <v>272</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.7175915625</v>
+        <v>46073.55092489583</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46170.19857011574</v>
+        <v>46170.031903449075</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>273</v>
@@ -5952,11 +5952,11 @@
         <v>275</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.71759184028</v>
+        <v>46073.55092517361</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46091.73446550926</v>
+        <v>46091.56779884259</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>276</v>
@@ -6005,11 +6005,11 @@
         <v>278</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.71759210648</v>
+        <v>46073.55092543981</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46179.199858576394</v>
+        <v>46179.03319190972</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>279</v>
@@ -6068,11 +6068,11 @@
         <v>282</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.71759238426</v>
+        <v>46073.55092571759</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46179.19985642361</v>
+        <v>46179.03318975694</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>283</v>
@@ -6131,11 +6131,11 @@
         <v>285</v>
       </c>
       <c r="B79" s="8">
-        <v>46091.72839834491</v>
+        <v>46091.561731678245</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46091.73565777778</v>
+        <v>46091.56899111111</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>286</v>
@@ -6184,11 +6184,11 @@
         <v>288</v>
       </c>
       <c r="B80" s="5">
-        <v>46091.72894082176</v>
+        <v>46091.56227415509</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46179.199856562496</v>
+        <v>46179.03318989583</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>289</v>
@@ -6247,11 +6247,11 @@
         <v>291</v>
       </c>
       <c r="B81" s="8">
-        <v>46091.72900166667</v>
+        <v>46091.562334999995</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46190.17451866898</v>
+        <v>46190.007852002316</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>292</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -1516,13 +1516,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.550923449075</v>
+        <v>46073.717590115746</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.557950358794</v>
+        <v>46092.724617025466</v>
       </c>
       <c r="D4" s="5">
-        <v>46114.64592623843</v>
+        <v>46114.81259290509</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1565,13 +1565,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.550924131945</v>
+        <v>46073.71759079861</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55791815972</v>
+        <v>46092.724584826385</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55795128472</v>
+        <v>46092.72461795139</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1630,13 +1630,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.55092440972</v>
+        <v>46073.71759107639</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.557918680555</v>
+        <v>46092.72458534723</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55795116899</v>
+        <v>46092.72461783564</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1695,13 +1695,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.5509246875</v>
+        <v>46073.717591354165</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.5579190625</v>
+        <v>46092.72458572917</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.55795108796</v>
+        <v>46092.72461775463</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1758,13 +1758,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.5509249537</v>
+        <v>46073.71759162037</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.557919467596</v>
+        <v>46092.72458613426</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.5441077662</v>
+        <v>46100.71077443287</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1821,13 +1821,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.55092523148</v>
+        <v>46073.71759189815</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55792006945</v>
+        <v>46092.72458673611</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.557950636576</v>
+        <v>46092.72461730324</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1884,11 +1884,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.55092548611</v>
+        <v>46073.71759215278</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.35971239583</v>
+        <v>46097.5263790625</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1931,13 +1931,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.55092579861</v>
+        <v>46073.71759246528</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.3596971875</v>
+        <v>46097.526363854166</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.359716226856</v>
+        <v>46097.52638289351</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1996,11 +1996,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.55092606481</v>
+        <v>46073.71759273148</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46126.02834039352</v>
+        <v>46126.19500706019</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2059,13 +2059,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.55092631944</v>
+        <v>46073.71759298611</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.34359585648</v>
+        <v>46114.51026252315</v>
       </c>
       <c r="D13" s="8">
-        <v>46169.71771503473</v>
+        <v>46169.884381701384</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2108,13 +2108,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.55092393518</v>
+        <v>46073.71759060185</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.359178321756</v>
+        <v>46097.52584498843</v>
       </c>
       <c r="D14" s="5">
-        <v>46100.59471405092</v>
+        <v>46100.761380717595</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2173,13 +2173,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.55092461806</v>
+        <v>46073.71759128472</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.34212127315</v>
+        <v>46114.50878793982</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.34214091435</v>
+        <v>46114.50880758102</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2238,13 +2238,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.55092490741</v>
+        <v>46073.71759157407</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.34256148148</v>
+        <v>46114.50922814815</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.34257719907</v>
+        <v>46114.509243865745</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2303,13 +2303,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.55092519676</v>
+        <v>46073.71759186343</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34357736111</v>
+        <v>46114.51024402778</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.34359680556</v>
+        <v>46114.51026347222</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2368,13 +2368,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.55092547454</v>
+        <v>46073.717592141205</v>
       </c>
       <c r="C18" s="5">
-        <v>46169.71758038194</v>
+        <v>46169.88424704861</v>
       </c>
       <c r="D18" s="5">
-        <v>46169.71766835648</v>
+        <v>46169.88433502315</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2417,13 +2417,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.55092603009</v>
+        <v>46073.71759269676</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.35928278935</v>
+        <v>46097.525949456016</v>
       </c>
       <c r="D19" s="8">
-        <v>46156.45183452546</v>
+        <v>46156.61850119213</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2482,13 +2482,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.550925752315</v>
+        <v>46073.71759241898</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.35931177084</v>
+        <v>46097.5259784375</v>
       </c>
       <c r="D20" s="5">
-        <v>46156.451852997685</v>
+        <v>46156.61851966435</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2547,13 +2547,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.55092663194</v>
+        <v>46073.717593298614</v>
       </c>
       <c r="C21" s="8">
-        <v>46128.26706200231</v>
+        <v>46128.433728668984</v>
       </c>
       <c r="D21" s="8">
-        <v>46128.26708372685</v>
+        <v>46128.433750393524</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2612,13 +2612,13 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.55092635417</v>
+        <v>46073.71759302083</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.359934479166</v>
+        <v>46097.52660114583</v>
       </c>
       <c r="D22" s="5">
-        <v>46097.35995533565</v>
+        <v>46097.52662200232</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2677,13 +2677,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.42669133102</v>
+        <v>46076.593357997685</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.34365599537</v>
+        <v>46114.51032266204</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.34380563657</v>
+        <v>46114.51047230324</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2742,13 +2742,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.55092366898</v>
+        <v>46073.71759033565</v>
       </c>
       <c r="C24" s="5">
-        <v>46169.717562060185</v>
+        <v>46169.88422872685</v>
       </c>
       <c r="D24" s="5">
-        <v>46169.71758065972</v>
+        <v>46169.884247326394</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2807,13 +2807,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.55092405093</v>
+        <v>46073.71759071759</v>
       </c>
       <c r="C25" s="8">
-        <v>46204.53274203704</v>
+        <v>46204.6994087037</v>
       </c>
       <c r="D25" s="8">
-        <v>46204.53276097222</v>
+        <v>46204.69942763889</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2860,13 +2860,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.55092359954</v>
+        <v>46073.7175902662</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.700224722226</v>
+        <v>46155.86689138889</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.70043725694</v>
+        <v>46155.86710392361</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -2925,13 +2925,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.55092391204</v>
+        <v>46073.7175905787</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.35938876157</v>
+        <v>46097.52605542824</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.359390219906</v>
+        <v>46097.52605688658</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>108</v>
@@ -2986,13 +2986,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.550924201394</v>
+        <v>46073.71759086805</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.700210358795</v>
+        <v>46155.86687702546</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.7002115625</v>
+        <v>46155.866878229164</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3047,13 +3047,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.55092451389</v>
+        <v>46073.71759118055</v>
       </c>
       <c r="C29" s="8">
-        <v>46128.47049521991</v>
+        <v>46128.637161886574</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.470505081015</v>
+        <v>46128.63717174769</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3108,13 +3108,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.550924317125</v>
+        <v>46073.7175909838</v>
       </c>
       <c r="C30" s="5">
-        <v>46155.73690275463</v>
+        <v>46155.903569421294</v>
       </c>
       <c r="D30" s="5">
-        <v>46155.73691611111</v>
+        <v>46155.90358277778</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3173,13 +3173,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.55092459491</v>
+        <v>46073.71759126158</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.35941971064</v>
+        <v>46097.526086377315</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.359421354166</v>
+        <v>46097.52608802084</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3234,13 +3234,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.55092487269</v>
+        <v>46073.71759153935</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.73688930555</v>
+        <v>46155.903555972225</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.736890844906</v>
+        <v>46155.90355751157</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3295,13 +3295,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.55092601852</v>
+        <v>46073.717592685185</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.51638877315</v>
+        <v>46182.68305543982</v>
       </c>
       <c r="D33" s="8">
-        <v>46182.51639055555</v>
+        <v>46182.683057222224</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3360,13 +3360,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.55092635417</v>
+        <v>46073.71759302083</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.51607938657</v>
+        <v>46182.68274605324</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.51608083333</v>
+        <v>46182.6827475</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3421,13 +3421,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.550923194445</v>
+        <v>46073.71758986111</v>
       </c>
       <c r="C35" s="8">
-        <v>46182.516275648144</v>
+        <v>46182.682942314816</v>
       </c>
       <c r="D35" s="8">
-        <v>46182.516276875</v>
+        <v>46182.682943541666</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3482,13 +3482,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.55092516204</v>
+        <v>46073.7175918287</v>
       </c>
       <c r="C36" s="5">
-        <v>46191.72161346065</v>
+        <v>46191.888280127314</v>
       </c>
       <c r="D36" s="5">
-        <v>46191.72403972222</v>
+        <v>46191.89070638889</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3547,13 +3547,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.55092542824</v>
+        <v>46073.71759209491</v>
       </c>
       <c r="C37" s="8">
-        <v>46097.35999758102</v>
+        <v>46097.526664247685</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.67663081019</v>
+        <v>46169.84329747685</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3608,11 +3608,11 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.55092568287</v>
+        <v>46073.71759234954</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46191.72166524305</v>
+        <v>46191.88833190972</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3667,13 +3667,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46076.427483680556</v>
+        <v>46076.59415034722</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.70138586806</v>
+        <v>46154.86805253472</v>
       </c>
       <c r="D39" s="8">
-        <v>46156.4519491088</v>
+        <v>46156.618615775464</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3732,13 +3732,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46076.42761490741</v>
+        <v>46076.59428157407</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.70070490741</v>
+        <v>46154.86737157407</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.70070689815</v>
+        <v>46154.86737356482</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3797,13 +3797,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46076.42781732639</v>
+        <v>46076.59448399306</v>
       </c>
       <c r="C41" s="8">
-        <v>46154.70143751157</v>
+        <v>46154.86810417824</v>
       </c>
       <c r="D41" s="8">
-        <v>46154.70143878472</v>
+        <v>46154.86810545139</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3862,13 +3862,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.550924814816</v>
+        <v>46073.71759148148</v>
       </c>
       <c r="C42" s="5">
-        <v>46182.36395186343</v>
+        <v>46182.530618530094</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.36396486111</v>
+        <v>46182.53063152778</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3927,13 +3927,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.5509250926</v>
+        <v>46073.717591759254</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.36380178241</v>
+        <v>46182.53046844907</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.36380388889</v>
+        <v>46182.53047055556</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3988,13 +3988,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.55092538195</v>
+        <v>46073.71759204861</v>
       </c>
       <c r="C44" s="5">
-        <v>46182.363938344904</v>
+        <v>46182.530605011576</v>
       </c>
       <c r="D44" s="5">
-        <v>46182.36393960648</v>
+        <v>46182.53060627315</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4049,11 +4049,11 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.55092568287</v>
+        <v>46073.71759234954</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46156.45203958334</v>
+        <v>46156.618706249996</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4096,13 +4096,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.55092594908</v>
+        <v>46073.717592615736</v>
       </c>
       <c r="C46" s="5">
-        <v>46153.92835325231</v>
+        <v>46154.09501991898</v>
       </c>
       <c r="D46" s="5">
-        <v>46153.92837542824</v>
+        <v>46154.09504209491</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4161,13 +4161,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.550923310184</v>
+        <v>46073.71758997685</v>
       </c>
       <c r="C47" s="8">
-        <v>46153.92841332176</v>
+        <v>46154.09507998843</v>
       </c>
       <c r="D47" s="8">
-        <v>46153.92842795139</v>
+        <v>46154.09509461805</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4226,13 +4226,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46091.56135321759</v>
+        <v>46091.72801988426</v>
       </c>
       <c r="C48" s="5">
-        <v>46153.92845228009</v>
+        <v>46154.09511894676</v>
       </c>
       <c r="D48" s="5">
-        <v>46153.928467199075</v>
+        <v>46154.09513386574</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4291,11 +4291,11 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46091.56139127315</v>
+        <v>46091.728057939814</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46198.65493113426</v>
+        <v>46198.821597800925</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4354,13 +4354,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.55092363426</v>
+        <v>46073.71759030093</v>
       </c>
       <c r="C50" s="5">
-        <v>46191.62262605324</v>
+        <v>46191.78929271991</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.62263766203</v>
+        <v>46191.789304328704</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>187</v>
@@ -4407,13 +4407,13 @@
         <v>189</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.55092391204</v>
+        <v>46073.7175905787</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.62173520833</v>
+        <v>46191.788401875005</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.62175582176</v>
+        <v>46191.788422488426</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>163</v>
@@ -4472,13 +4472,13 @@
         <v>193</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.55092414352</v>
+        <v>46073.717590810185</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.62260993056</v>
+        <v>46191.78927659722</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.62262652778</v>
+        <v>46191.789293194444</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>194</v>
@@ -4537,13 +4537,13 @@
         <v>198</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.55092443287</v>
+        <v>46073.717591099536</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.62370814815</v>
+        <v>46191.79037481482</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.6237183912</v>
+        <v>46191.79038505787</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>199</v>
@@ -4590,13 +4590,13 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.550924675925</v>
+        <v>46073.71759134259</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.623270254626</v>
+        <v>46191.7899369213</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.623286145834</v>
+        <v>46191.7899528125</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4655,13 +4655,13 @@
         <v>206</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.55092490741</v>
+        <v>46073.71759157407</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.623691597226</v>
+        <v>46191.79035826389</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.62370916667</v>
+        <v>46191.790375833334</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>207</v>
@@ -4720,13 +4720,13 @@
         <v>210</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.55092515046</v>
+        <v>46073.71759181713</v>
       </c>
       <c r="C56" s="5">
-        <v>46191.623014756944</v>
+        <v>46191.789681423616</v>
       </c>
       <c r="D56" s="5">
-        <v>46191.623708831015</v>
+        <v>46191.79037549769</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>211</v>
@@ -4785,11 +4785,11 @@
         <v>214</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.550925393516</v>
+        <v>46073.71759206019</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46198.66131490741</v>
+        <v>46198.827981574075</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>187</v>
@@ -4832,13 +4832,13 @@
         <v>216</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.550924386574</v>
+        <v>46073.71759105324</v>
       </c>
       <c r="C58" s="5">
-        <v>46195.44225010417</v>
+        <v>46195.608916770834</v>
       </c>
       <c r="D58" s="5">
-        <v>46195.44226982639</v>
+        <v>46195.60893649305</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>217</v>
@@ -4897,13 +4897,13 @@
         <v>219</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.550924166666</v>
+        <v>46073.71759083333</v>
       </c>
       <c r="C59" s="8">
-        <v>46195.44242412037</v>
+        <v>46195.60909078704</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.4424422338</v>
+        <v>46195.60910890046</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>220</v>
@@ -4962,13 +4962,13 @@
         <v>222</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.5509256713</v>
+        <v>46073.71759233796</v>
       </c>
       <c r="C60" s="5">
-        <v>46198.661309166666</v>
+        <v>46198.82797583334</v>
       </c>
       <c r="D60" s="5">
-        <v>46198.66132570602</v>
+        <v>46198.82799237268</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>223</v>
@@ -5027,11 +5027,11 @@
         <v>225</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.55092384259</v>
+        <v>46073.71759050926</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46191.72167136574</v>
+        <v>46191.88833803241</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5090,13 +5090,13 @@
         <v>227</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.432926064816</v>
+        <v>46076.59959273148</v>
       </c>
       <c r="C62" s="5">
-        <v>46198.66279835648</v>
+        <v>46198.82946502315</v>
       </c>
       <c r="D62" s="5">
-        <v>46198.66281634259</v>
+        <v>46198.829483009264</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>228</v>
@@ -5155,11 +5155,11 @@
         <v>231</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.550924641204</v>
+        <v>46073.71759130787</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.70154178241</v>
+        <v>46195.86820844907</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>232</v>
@@ -5202,13 +5202,13 @@
         <v>234</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.55092488426</v>
+        <v>46073.71759155093</v>
       </c>
       <c r="C64" s="5">
-        <v>46193.44056403935</v>
+        <v>46193.60723070602</v>
       </c>
       <c r="D64" s="5">
-        <v>46193.440598761576</v>
+        <v>46193.60726542824</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>235</v>
@@ -5267,13 +5267,13 @@
         <v>237</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.55092513889</v>
+        <v>46073.71759180556</v>
       </c>
       <c r="C65" s="8">
-        <v>46193.44072755787</v>
+        <v>46193.60739422454</v>
       </c>
       <c r="D65" s="8">
-        <v>46195.44226991898</v>
+        <v>46195.608936585646</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5332,13 +5332,13 @@
         <v>241</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.55092537037</v>
+        <v>46073.717592037036</v>
       </c>
       <c r="C66" s="5">
-        <v>46193.44078907407</v>
+        <v>46193.60745574074</v>
       </c>
       <c r="D66" s="5">
-        <v>46195.442443391206</v>
+        <v>46195.60911005787</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>242</v>
@@ -5397,13 +5397,13 @@
         <v>245</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.550925601856</v>
+        <v>46073.71759226852</v>
       </c>
       <c r="C67" s="8">
-        <v>46193.44082700231</v>
+        <v>46193.607493668984</v>
       </c>
       <c r="D67" s="8">
-        <v>46198.66132460648</v>
+        <v>46198.82799127315</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>246</v>
@@ -5462,13 +5462,13 @@
         <v>248</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.43405303241</v>
+        <v>46076.600719699076</v>
       </c>
       <c r="C68" s="5">
-        <v>46193.44097622685</v>
+        <v>46193.60764289352</v>
       </c>
       <c r="D68" s="5">
-        <v>46198.662815185184</v>
+        <v>46198.82948185185</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>229</v>
@@ -5527,13 +5527,13 @@
         <v>250</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.550925856485</v>
+        <v>46073.71759252315</v>
       </c>
       <c r="C69" s="8">
-        <v>46195.70153575232</v>
+        <v>46195.86820241898</v>
       </c>
       <c r="D69" s="8">
-        <v>46195.70155246528</v>
+        <v>46195.868219131946</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>183</v>
@@ -5592,11 +5592,11 @@
         <v>253</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.55092609954</v>
+        <v>46073.7175927662</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46162.00188083333</v>
+        <v>46162.1685475</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>184</v>
@@ -5655,11 +5655,11 @@
         <v>255</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.55092376158</v>
+        <v>46073.71759042824</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46091.56779943287</v>
+        <v>46091.73446609954</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>256</v>
@@ -5702,11 +5702,11 @@
         <v>258</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.55092408565</v>
+        <v>46073.71759075232</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46204.53369581018</v>
+        <v>46204.700362476855</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5765,11 +5765,11 @@
         <v>263</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.55092435185</v>
+        <v>46073.71759101852</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46168.019966736116</v>
+        <v>46168.18663340277</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>264</v>
@@ -5828,11 +5828,11 @@
         <v>267</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.550924641204</v>
+        <v>46073.71759130787</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46169.00187577546</v>
+        <v>46169.16854244213</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>268</v>
@@ -5891,11 +5891,11 @@
         <v>272</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.55092489583</v>
+        <v>46073.7175915625</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46170.031903449075</v>
+        <v>46170.19857011574</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>273</v>
@@ -5952,11 +5952,11 @@
         <v>275</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.55092517361</v>
+        <v>46073.71759184028</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46091.56779884259</v>
+        <v>46091.73446550926</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>276</v>
@@ -6005,11 +6005,11 @@
         <v>278</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.55092543981</v>
+        <v>46073.71759210648</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46179.03319190972</v>
+        <v>46179.199858576394</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>279</v>
@@ -6068,11 +6068,11 @@
         <v>282</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.55092571759</v>
+        <v>46073.71759238426</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46179.03318975694</v>
+        <v>46179.19985642361</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>283</v>
@@ -6131,11 +6131,11 @@
         <v>285</v>
       </c>
       <c r="B79" s="8">
-        <v>46091.561731678245</v>
+        <v>46091.72839834491</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46091.56899111111</v>
+        <v>46091.73565777778</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>286</v>
@@ -6184,11 +6184,11 @@
         <v>288</v>
       </c>
       <c r="B80" s="5">
-        <v>46091.56227415509</v>
+        <v>46091.72894082176</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46179.03318989583</v>
+        <v>46179.199856562496</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>289</v>
@@ -6247,11 +6247,11 @@
         <v>291</v>
       </c>
       <c r="B81" s="8">
-        <v>46091.562334999995</v>
+        <v>46091.72900166667</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46190.007852002316</v>
+        <v>46190.17451866898</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>292</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="293">
   <si>
     <t xml:space="preserve">50001498-CALABRESSE METRO STO DOMINGO  POZOS  </t>
   </si>
@@ -568,91 +568,91 @@
     <t>RE-PINTADO</t>
   </si>
   <si>
+    <t>1213380470331434</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213380470331435</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Bodega:,Bodega:</t>
+  </si>
+  <si>
+    <t>1213380470331436</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Generacion OC Fabricación externa </t>
+  </si>
+  <si>
+    <t>1213380470331437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa </t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación externa ,Armado fabricación externa ,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213380470331438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion OC Fabricación externa </t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado fabricación externa ,Fabricación externa </t>
+  </si>
+  <si>
+    <t>1213380470331439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado fabricación externa </t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación externa ,Check Planos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Armado,Fabricación externa </t>
+  </si>
+  <si>
+    <t>1213380470331440</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>Armado fabricación externa ,Check Planos</t>
+  </si>
+  <si>
+    <t>Fabricación externa ,Revestimiento</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213380470331434</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213380470331435</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento,Bodega:,Bodega:</t>
-  </si>
-  <si>
-    <t>1213380470331436</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Generacion OC Fabricación externa </t>
-  </si>
-  <si>
-    <t>1213380470331437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa </t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación externa ,Armado fabricación externa ,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213380470331438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion OC Fabricación externa </t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado fabricación externa ,Fabricación externa </t>
-  </si>
-  <si>
-    <t>1213380470331439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado fabricación externa </t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación externa ,Check Planos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Armado,Fabricación externa </t>
-  </si>
-  <si>
-    <t>1213380470331440</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>Armado fabricación externa ,Check Planos</t>
-  </si>
-  <si>
-    <t>Fabricación externa ,Revestimiento</t>
   </si>
   <si>
     <t>1213380470331441</t>
@@ -4051,9 +4051,11 @@
       <c r="B45" s="8">
         <v>46073.71759234954</v>
       </c>
-      <c r="C45" s="9"/>
+      <c r="C45" s="8">
+        <v>46210.531775787036</v>
+      </c>
       <c r="D45" s="8">
-        <v>46156.618706249996</v>
+        <v>46210.531792002315</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4087,9 +4089,13 @@
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
-      <c r="S45" s="9"/>
+      <c r="S45" s="9">
+        <v>1</v>
+      </c>
       <c r="T45" s="9"/>
-      <c r="U45" s="9"/>
+      <c r="U45" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
@@ -4293,9 +4299,11 @@
       <c r="B49" s="8">
         <v>46091.728057939814</v>
       </c>
-      <c r="C49" s="9"/>
+      <c r="C49" s="8">
+        <v>46210.531998136576</v>
+      </c>
       <c r="D49" s="8">
-        <v>46198.821597800925</v>
+        <v>46210.53201784722</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4340,18 +4348,18 @@
         <v>46160</v>
       </c>
       <c r="S49" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U49" s="12" t="s">
-        <v>185</v>
+      <c r="U49" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46073.71759030093</v>
@@ -4363,7 +4371,7 @@
         <v>46191.789304328704</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4387,7 +4395,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4404,7 +4412,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B51" s="8">
         <v>46073.7175905787</v>
@@ -4422,10 +4430,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="I51" s="8">
         <v>46069</v>
@@ -4443,13 +4451,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>162</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="8">
         <v>46069</v>
@@ -4469,7 +4477,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46073.717590810185</v>
@@ -4481,16 +4489,16 @@
         <v>46191.789293194444</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I52" s="5">
         <v>46071</v>
@@ -4508,13 +4516,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>163</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q52" s="5">
         <v>46071</v>
@@ -4534,7 +4542,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B53" s="8">
         <v>46073.717591099536</v>
@@ -4546,7 +4554,7 @@
         <v>46191.79038505787</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4570,7 +4578,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4587,7 +4595,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B54" s="5">
         <v>46073.71759134259</v>
@@ -4599,16 +4607,16 @@
         <v>46191.7899528125</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I54" s="5">
         <v>46073</v>
@@ -4626,13 +4634,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q54" s="5">
         <v>46073</v>
@@ -4652,7 +4660,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B55" s="8">
         <v>46073.71759157407</v>
@@ -4664,16 +4672,16 @@
         <v>46191.790375833334</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="I55" s="8">
         <v>46084</v>
@@ -4691,13 +4699,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O55" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="P55" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="Q55" s="8">
         <v>46084</v>
@@ -4717,7 +4725,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B56" s="5">
         <v>46073.71759181713</v>
@@ -4729,16 +4737,16 @@
         <v>46191.79037549769</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="I56" s="5">
         <v>46104</v>
@@ -4756,13 +4764,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="Q56" s="5">
         <v>46104</v>
@@ -4777,7 +4785,7 @@
         <v>31</v>
       </c>
       <c r="U56" s="12" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4792,7 +4800,7 @@
         <v>46198.827981574075</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4847,10 +4855,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I58" s="5">
         <v>46153</v>
@@ -4868,7 +4876,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>112</v>
@@ -4912,10 +4920,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="I59" s="8">
         <v>46135</v>
@@ -4933,7 +4941,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>124</v>
@@ -4977,10 +4985,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I60" s="5">
         <v>46071</v>
@@ -4998,7 +5006,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>133</v>
@@ -5040,10 +5048,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="I61" s="8">
         <v>46115</v>
@@ -5061,7 +5069,7 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>142</v>
@@ -5082,7 +5090,7 @@
         <v>31</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5105,10 +5113,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I62" s="5">
         <v>46139</v>
@@ -5126,7 +5134,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>153</v>
@@ -5241,7 +5249,7 @@
         <v>232</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>236</v>
@@ -5324,7 +5332,7 @@
         <v>31</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5389,7 +5397,7 @@
         <v>230</v>
       </c>
       <c r="U66" s="12" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5454,7 +5462,7 @@
         <v>31</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5519,7 +5527,7 @@
         <v>31</v>
       </c>
       <c r="U68" s="12" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5596,7 +5604,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46162.1685475</v>
+        <v>46210.53201621528</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>184</v>
@@ -5646,8 +5654,8 @@
       <c r="T70" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U70" s="10" t="s">
-        <v>56</v>
+      <c r="U70" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -5281,7 +5281,7 @@
         <v>46193.60739422454</v>
       </c>
       <c r="D65" s="8">
-        <v>46195.608936585646</v>
+        <v>46210.82564115741</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5331,8 +5331,8 @@
       <c r="T65" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U65" s="12" t="s">
-        <v>213</v>
+      <c r="U65" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5346,7 +5346,7 @@
         <v>46193.60745574074</v>
       </c>
       <c r="D66" s="5">
-        <v>46195.60911005787</v>
+        <v>46210.825641759264</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>242</v>
@@ -5396,8 +5396,8 @@
       <c r="T66" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="U66" s="12" t="s">
-        <v>213</v>
+      <c r="U66" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5411,7 +5411,7 @@
         <v>46193.607493668984</v>
       </c>
       <c r="D67" s="8">
-        <v>46198.82799127315</v>
+        <v>46210.82564222222</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>246</v>
@@ -5461,8 +5461,8 @@
       <c r="T67" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U67" s="12" t="s">
-        <v>213</v>
+      <c r="U67" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5476,7 +5476,7 @@
         <v>46193.60764289352</v>
       </c>
       <c r="D68" s="5">
-        <v>46198.82948185185</v>
+        <v>46210.82564268519</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>229</v>
@@ -5526,8 +5526,8 @@
       <c r="T68" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U68" s="12" t="s">
-        <v>213</v>
+      <c r="U68" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -1516,13 +1516,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.717590115746</v>
+        <v>46073.550923449075</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.724617025466</v>
+        <v>46092.557950358794</v>
       </c>
       <c r="D4" s="5">
-        <v>46114.81259290509</v>
+        <v>46114.64592623843</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1565,13 +1565,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.71759079861</v>
+        <v>46073.550924131945</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.724584826385</v>
+        <v>46092.55791815972</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.72461795139</v>
+        <v>46092.55795128472</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1630,13 +1630,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.71759107639</v>
+        <v>46073.55092440972</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.72458534723</v>
+        <v>46092.557918680555</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.72461783564</v>
+        <v>46092.55795116899</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1695,13 +1695,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.717591354165</v>
+        <v>46073.5509246875</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.72458572917</v>
+        <v>46092.5579190625</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.72461775463</v>
+        <v>46092.55795108796</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1758,13 +1758,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.71759162037</v>
+        <v>46073.5509249537</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72458613426</v>
+        <v>46092.557919467596</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.71077443287</v>
+        <v>46100.5441077662</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1821,13 +1821,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.71759189815</v>
+        <v>46073.55092523148</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.72458673611</v>
+        <v>46092.55792006945</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.72461730324</v>
+        <v>46092.557950636576</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1884,11 +1884,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.71759215278</v>
+        <v>46073.55092548611</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.5263790625</v>
+        <v>46097.35971239583</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1931,13 +1931,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.71759246528</v>
+        <v>46073.55092579861</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.526363854166</v>
+        <v>46097.3596971875</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.52638289351</v>
+        <v>46097.359716226856</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1996,11 +1996,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.71759273148</v>
+        <v>46073.55092606481</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46126.19500706019</v>
+        <v>46126.02834039352</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2059,13 +2059,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.71759298611</v>
+        <v>46073.55092631944</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51026252315</v>
+        <v>46114.34359585648</v>
       </c>
       <c r="D13" s="8">
-        <v>46169.884381701384</v>
+        <v>46169.71771503473</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2108,13 +2108,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.71759060185</v>
+        <v>46073.55092393518</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.52584498843</v>
+        <v>46097.359178321756</v>
       </c>
       <c r="D14" s="5">
-        <v>46100.761380717595</v>
+        <v>46100.59471405092</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2173,13 +2173,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.71759128472</v>
+        <v>46073.55092461806</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.50878793982</v>
+        <v>46114.34212127315</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.50880758102</v>
+        <v>46114.34214091435</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2238,13 +2238,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.71759157407</v>
+        <v>46073.55092490741</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.50922814815</v>
+        <v>46114.34256148148</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.509243865745</v>
+        <v>46114.34257719907</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2303,13 +2303,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.71759186343</v>
+        <v>46073.55092519676</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.51024402778</v>
+        <v>46114.34357736111</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.51026347222</v>
+        <v>46114.34359680556</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2368,13 +2368,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.717592141205</v>
+        <v>46073.55092547454</v>
       </c>
       <c r="C18" s="5">
-        <v>46169.88424704861</v>
+        <v>46169.71758038194</v>
       </c>
       <c r="D18" s="5">
-        <v>46169.88433502315</v>
+        <v>46169.71766835648</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2417,13 +2417,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.71759269676</v>
+        <v>46073.55092603009</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.525949456016</v>
+        <v>46097.35928278935</v>
       </c>
       <c r="D19" s="8">
-        <v>46156.61850119213</v>
+        <v>46156.45183452546</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2482,13 +2482,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.71759241898</v>
+        <v>46073.550925752315</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.5259784375</v>
+        <v>46097.35931177084</v>
       </c>
       <c r="D20" s="5">
-        <v>46156.61851966435</v>
+        <v>46156.451852997685</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2547,13 +2547,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.717593298614</v>
+        <v>46073.55092663194</v>
       </c>
       <c r="C21" s="8">
-        <v>46128.433728668984</v>
+        <v>46128.26706200231</v>
       </c>
       <c r="D21" s="8">
-        <v>46128.433750393524</v>
+        <v>46128.26708372685</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2612,13 +2612,13 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.71759302083</v>
+        <v>46073.55092635417</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.52660114583</v>
+        <v>46097.359934479166</v>
       </c>
       <c r="D22" s="5">
-        <v>46097.52662200232</v>
+        <v>46097.35995533565</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2677,13 +2677,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.593357997685</v>
+        <v>46076.42669133102</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.51032266204</v>
+        <v>46114.34365599537</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.51047230324</v>
+        <v>46114.34380563657</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2742,13 +2742,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.71759033565</v>
+        <v>46073.55092366898</v>
       </c>
       <c r="C24" s="5">
-        <v>46169.88422872685</v>
+        <v>46169.717562060185</v>
       </c>
       <c r="D24" s="5">
-        <v>46169.884247326394</v>
+        <v>46169.71758065972</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2807,13 +2807,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.71759071759</v>
+        <v>46073.55092405093</v>
       </c>
       <c r="C25" s="8">
-        <v>46204.6994087037</v>
+        <v>46204.53274203704</v>
       </c>
       <c r="D25" s="8">
-        <v>46204.69942763889</v>
+        <v>46204.53276097222</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2860,13 +2860,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.7175902662</v>
+        <v>46073.55092359954</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.86689138889</v>
+        <v>46155.700224722226</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.86710392361</v>
+        <v>46155.70043725694</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -2925,13 +2925,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.7175905787</v>
+        <v>46073.55092391204</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.52605542824</v>
+        <v>46097.35938876157</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.52605688658</v>
+        <v>46097.359390219906</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>108</v>
@@ -2986,13 +2986,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.71759086805</v>
+        <v>46073.550924201394</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.86687702546</v>
+        <v>46155.700210358795</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.866878229164</v>
+        <v>46155.7002115625</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3047,13 +3047,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.71759118055</v>
+        <v>46073.55092451389</v>
       </c>
       <c r="C29" s="8">
-        <v>46128.637161886574</v>
+        <v>46128.47049521991</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.63717174769</v>
+        <v>46128.470505081015</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3108,13 +3108,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.7175909838</v>
+        <v>46073.550924317125</v>
       </c>
       <c r="C30" s="5">
-        <v>46155.903569421294</v>
+        <v>46155.73690275463</v>
       </c>
       <c r="D30" s="5">
-        <v>46155.90358277778</v>
+        <v>46155.73691611111</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3173,13 +3173,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.71759126158</v>
+        <v>46073.55092459491</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.526086377315</v>
+        <v>46097.35941971064</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.52608802084</v>
+        <v>46097.359421354166</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3234,13 +3234,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.71759153935</v>
+        <v>46073.55092487269</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.903555972225</v>
+        <v>46155.73688930555</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.90355751157</v>
+        <v>46155.736890844906</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3295,13 +3295,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.717592685185</v>
+        <v>46073.55092601852</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.68305543982</v>
+        <v>46182.51638877315</v>
       </c>
       <c r="D33" s="8">
-        <v>46182.683057222224</v>
+        <v>46182.51639055555</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3360,13 +3360,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.71759302083</v>
+        <v>46073.55092635417</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.68274605324</v>
+        <v>46182.51607938657</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.6827475</v>
+        <v>46182.51608083333</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3421,13 +3421,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.71758986111</v>
+        <v>46073.550923194445</v>
       </c>
       <c r="C35" s="8">
-        <v>46182.682942314816</v>
+        <v>46182.516275648144</v>
       </c>
       <c r="D35" s="8">
-        <v>46182.682943541666</v>
+        <v>46182.516276875</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3482,13 +3482,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.7175918287</v>
+        <v>46073.55092516204</v>
       </c>
       <c r="C36" s="5">
-        <v>46191.888280127314</v>
+        <v>46191.72161346065</v>
       </c>
       <c r="D36" s="5">
-        <v>46191.89070638889</v>
+        <v>46191.72403972222</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3547,13 +3547,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.71759209491</v>
+        <v>46073.55092542824</v>
       </c>
       <c r="C37" s="8">
-        <v>46097.526664247685</v>
+        <v>46097.35999758102</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.84329747685</v>
+        <v>46169.67663081019</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3608,11 +3608,11 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.71759234954</v>
+        <v>46073.55092568287</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46191.88833190972</v>
+        <v>46191.72166524305</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3667,13 +3667,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46076.59415034722</v>
+        <v>46076.427483680556</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.86805253472</v>
+        <v>46154.70138586806</v>
       </c>
       <c r="D39" s="8">
-        <v>46156.618615775464</v>
+        <v>46156.4519491088</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3732,13 +3732,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46076.59428157407</v>
+        <v>46076.42761490741</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.86737157407</v>
+        <v>46154.70070490741</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.86737356482</v>
+        <v>46154.70070689815</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3797,13 +3797,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46076.59448399306</v>
+        <v>46076.42781732639</v>
       </c>
       <c r="C41" s="8">
-        <v>46154.86810417824</v>
+        <v>46154.70143751157</v>
       </c>
       <c r="D41" s="8">
-        <v>46154.86810545139</v>
+        <v>46154.70143878472</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3862,13 +3862,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.71759148148</v>
+        <v>46073.550924814816</v>
       </c>
       <c r="C42" s="5">
-        <v>46182.530618530094</v>
+        <v>46182.36395186343</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.53063152778</v>
+        <v>46182.36396486111</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3927,13 +3927,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.717591759254</v>
+        <v>46073.5509250926</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.53046844907</v>
+        <v>46182.36380178241</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.53047055556</v>
+        <v>46182.36380388889</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3988,13 +3988,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.71759204861</v>
+        <v>46073.55092538195</v>
       </c>
       <c r="C44" s="5">
-        <v>46182.530605011576</v>
+        <v>46182.363938344904</v>
       </c>
       <c r="D44" s="5">
-        <v>46182.53060627315</v>
+        <v>46182.36393960648</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4049,13 +4049,13 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.71759234954</v>
+        <v>46073.55092568287</v>
       </c>
       <c r="C45" s="8">
-        <v>46210.531775787036</v>
+        <v>46210.36510912037</v>
       </c>
       <c r="D45" s="8">
-        <v>46210.531792002315</v>
+        <v>46210.36512533565</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4102,13 +4102,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.717592615736</v>
+        <v>46073.55092594908</v>
       </c>
       <c r="C46" s="5">
-        <v>46154.09501991898</v>
+        <v>46153.92835325231</v>
       </c>
       <c r="D46" s="5">
-        <v>46154.09504209491</v>
+        <v>46153.92837542824</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4167,13 +4167,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.71758997685</v>
+        <v>46073.550923310184</v>
       </c>
       <c r="C47" s="8">
-        <v>46154.09507998843</v>
+        <v>46153.92841332176</v>
       </c>
       <c r="D47" s="8">
-        <v>46154.09509461805</v>
+        <v>46153.92842795139</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4232,13 +4232,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46091.72801988426</v>
+        <v>46091.56135321759</v>
       </c>
       <c r="C48" s="5">
-        <v>46154.09511894676</v>
+        <v>46153.92845228009</v>
       </c>
       <c r="D48" s="5">
-        <v>46154.09513386574</v>
+        <v>46153.928467199075</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4297,13 +4297,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46091.728057939814</v>
+        <v>46091.56139127315</v>
       </c>
       <c r="C49" s="8">
-        <v>46210.531998136576</v>
+        <v>46210.365331469904</v>
       </c>
       <c r="D49" s="8">
-        <v>46210.53201784722</v>
+        <v>46210.36535118056</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4362,13 +4362,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.71759030093</v>
+        <v>46073.55092363426</v>
       </c>
       <c r="C50" s="5">
-        <v>46191.78929271991</v>
+        <v>46191.62262605324</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.789304328704</v>
+        <v>46191.62263766203</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4415,13 +4415,13 @@
         <v>188</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.7175905787</v>
+        <v>46073.55092391204</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.788401875005</v>
+        <v>46191.62173520833</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.788422488426</v>
+        <v>46191.62175582176</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>163</v>
@@ -4480,13 +4480,13 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.717590810185</v>
+        <v>46073.55092414352</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.78927659722</v>
+        <v>46191.62260993056</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.789293194444</v>
+        <v>46191.62262652778</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4545,13 +4545,13 @@
         <v>197</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.717591099536</v>
+        <v>46073.55092443287</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.79037481482</v>
+        <v>46191.62370814815</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.79038505787</v>
+        <v>46191.6237183912</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>198</v>
@@ -4598,13 +4598,13 @@
         <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.71759134259</v>
+        <v>46073.550924675925</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.7899369213</v>
+        <v>46191.623270254626</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.7899528125</v>
+        <v>46191.623286145834</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>201</v>
@@ -4663,13 +4663,13 @@
         <v>205</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.71759157407</v>
+        <v>46073.55092490741</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.79035826389</v>
+        <v>46191.623691597226</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.790375833334</v>
+        <v>46191.62370916667</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>206</v>
@@ -4728,13 +4728,13 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.71759181713</v>
+        <v>46073.55092515046</v>
       </c>
       <c r="C56" s="5">
-        <v>46191.789681423616</v>
+        <v>46191.623014756944</v>
       </c>
       <c r="D56" s="5">
-        <v>46191.79037549769</v>
+        <v>46191.623708831015</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4793,11 +4793,11 @@
         <v>214</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.71759206019</v>
+        <v>46073.550925393516</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46198.827981574075</v>
+        <v>46198.66131490741</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>186</v>
@@ -4840,13 +4840,13 @@
         <v>216</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.71759105324</v>
+        <v>46073.550924386574</v>
       </c>
       <c r="C58" s="5">
-        <v>46195.608916770834</v>
+        <v>46195.44225010417</v>
       </c>
       <c r="D58" s="5">
-        <v>46195.60893649305</v>
+        <v>46195.44226982639</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>217</v>
@@ -4905,13 +4905,13 @@
         <v>219</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.71759083333</v>
+        <v>46073.550924166666</v>
       </c>
       <c r="C59" s="8">
-        <v>46195.60909078704</v>
+        <v>46195.44242412037</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.60910890046</v>
+        <v>46195.4424422338</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>220</v>
@@ -4970,13 +4970,13 @@
         <v>222</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.71759233796</v>
+        <v>46073.5509256713</v>
       </c>
       <c r="C60" s="5">
-        <v>46198.82797583334</v>
+        <v>46198.661309166666</v>
       </c>
       <c r="D60" s="5">
-        <v>46198.82799237268</v>
+        <v>46198.66132570602</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>223</v>
@@ -5035,11 +5035,11 @@
         <v>225</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.71759050926</v>
+        <v>46073.55092384259</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46191.88833803241</v>
+        <v>46191.72167136574</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5098,13 +5098,13 @@
         <v>227</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.59959273148</v>
+        <v>46076.432926064816</v>
       </c>
       <c r="C62" s="5">
-        <v>46198.82946502315</v>
+        <v>46198.66279835648</v>
       </c>
       <c r="D62" s="5">
-        <v>46198.829483009264</v>
+        <v>46198.66281634259</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>228</v>
@@ -5163,11 +5163,11 @@
         <v>231</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.71759130787</v>
+        <v>46073.550924641204</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.86820844907</v>
+        <v>46195.70154178241</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>232</v>
@@ -5210,13 +5210,13 @@
         <v>234</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.71759155093</v>
+        <v>46073.55092488426</v>
       </c>
       <c r="C64" s="5">
-        <v>46193.60723070602</v>
+        <v>46193.44056403935</v>
       </c>
       <c r="D64" s="5">
-        <v>46193.60726542824</v>
+        <v>46193.440598761576</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>235</v>
@@ -5275,13 +5275,13 @@
         <v>237</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.71759180556</v>
+        <v>46073.55092513889</v>
       </c>
       <c r="C65" s="8">
-        <v>46193.60739422454</v>
+        <v>46193.44072755787</v>
       </c>
       <c r="D65" s="8">
-        <v>46210.82564115741</v>
+        <v>46210.65897449074</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5340,13 +5340,13 @@
         <v>241</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.717592037036</v>
+        <v>46073.55092537037</v>
       </c>
       <c r="C66" s="5">
-        <v>46193.60745574074</v>
+        <v>46193.44078907407</v>
       </c>
       <c r="D66" s="5">
-        <v>46210.825641759264</v>
+        <v>46210.65897509259</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>242</v>
@@ -5405,13 +5405,13 @@
         <v>245</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.71759226852</v>
+        <v>46073.550925601856</v>
       </c>
       <c r="C67" s="8">
-        <v>46193.607493668984</v>
+        <v>46193.44082700231</v>
       </c>
       <c r="D67" s="8">
-        <v>46210.82564222222</v>
+        <v>46210.658975555554</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>246</v>
@@ -5470,13 +5470,13 @@
         <v>248</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.600719699076</v>
+        <v>46076.43405303241</v>
       </c>
       <c r="C68" s="5">
-        <v>46193.60764289352</v>
+        <v>46193.44097622685</v>
       </c>
       <c r="D68" s="5">
-        <v>46210.82564268519</v>
+        <v>46210.658976018516</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>229</v>
@@ -5535,13 +5535,13 @@
         <v>250</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.71759252315</v>
+        <v>46073.550925856485</v>
       </c>
       <c r="C69" s="8">
-        <v>46195.86820241898</v>
+        <v>46195.70153575232</v>
       </c>
       <c r="D69" s="8">
-        <v>46195.868219131946</v>
+        <v>46195.70155246528</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>183</v>
@@ -5600,11 +5600,11 @@
         <v>253</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.7175927662</v>
+        <v>46073.55092609954</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46210.53201621528</v>
+        <v>46210.36534954861</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>184</v>
@@ -5663,11 +5663,11 @@
         <v>255</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.71759042824</v>
+        <v>46073.55092376158</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46091.73446609954</v>
+        <v>46091.56779943287</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>256</v>
@@ -5710,11 +5710,11 @@
         <v>258</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.71759075232</v>
+        <v>46073.55092408565</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46204.700362476855</v>
+        <v>46204.53369581018</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5773,11 +5773,11 @@
         <v>263</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.71759101852</v>
+        <v>46073.55092435185</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46168.18663340277</v>
+        <v>46168.019966736116</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>264</v>
@@ -5836,11 +5836,11 @@
         <v>267</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.71759130787</v>
+        <v>46073.550924641204</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46169.16854244213</v>
+        <v>46169.00187577546</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>268</v>
@@ -5899,11 +5899,11 @@
         <v>272</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.7175915625</v>
+        <v>46073.55092489583</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46170.19857011574</v>
+        <v>46170.031903449075</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>273</v>
@@ -5960,11 +5960,11 @@
         <v>275</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.71759184028</v>
+        <v>46073.55092517361</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46091.73446550926</v>
+        <v>46091.56779884259</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>276</v>
@@ -6013,11 +6013,11 @@
         <v>278</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.71759210648</v>
+        <v>46073.55092543981</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46179.199858576394</v>
+        <v>46179.03319190972</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>279</v>
@@ -6076,11 +6076,11 @@
         <v>282</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.71759238426</v>
+        <v>46073.55092571759</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46179.19985642361</v>
+        <v>46179.03318975694</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>283</v>
@@ -6139,11 +6139,11 @@
         <v>285</v>
       </c>
       <c r="B79" s="8">
-        <v>46091.72839834491</v>
+        <v>46091.561731678245</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46091.73565777778</v>
+        <v>46091.56899111111</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>286</v>
@@ -6192,11 +6192,11 @@
         <v>288</v>
       </c>
       <c r="B80" s="5">
-        <v>46091.72894082176</v>
+        <v>46091.56227415509</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46179.199856562496</v>
+        <v>46179.03318989583</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>289</v>
@@ -6255,11 +6255,11 @@
         <v>291</v>
       </c>
       <c r="B81" s="8">
-        <v>46091.72900166667</v>
+        <v>46091.562334999995</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46190.17451866898</v>
+        <v>46190.007852002316</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>292</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -1516,13 +1516,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.550923449075</v>
+        <v>46073.717590115746</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.557950358794</v>
+        <v>46092.724617025466</v>
       </c>
       <c r="D4" s="5">
-        <v>46114.64592623843</v>
+        <v>46114.81259290509</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1565,13 +1565,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.550924131945</v>
+        <v>46073.71759079861</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55791815972</v>
+        <v>46092.724584826385</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55795128472</v>
+        <v>46092.72461795139</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1630,13 +1630,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.55092440972</v>
+        <v>46073.71759107639</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.557918680555</v>
+        <v>46092.72458534723</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55795116899</v>
+        <v>46092.72461783564</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1695,13 +1695,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.5509246875</v>
+        <v>46073.717591354165</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.5579190625</v>
+        <v>46092.72458572917</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.55795108796</v>
+        <v>46092.72461775463</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1758,13 +1758,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.5509249537</v>
+        <v>46073.71759162037</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.557919467596</v>
+        <v>46092.72458613426</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.5441077662</v>
+        <v>46100.71077443287</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1821,13 +1821,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.55092523148</v>
+        <v>46073.71759189815</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55792006945</v>
+        <v>46092.72458673611</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.557950636576</v>
+        <v>46092.72461730324</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1884,11 +1884,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.55092548611</v>
+        <v>46073.71759215278</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.35971239583</v>
+        <v>46097.5263790625</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1931,13 +1931,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.55092579861</v>
+        <v>46073.71759246528</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.3596971875</v>
+        <v>46097.526363854166</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.359716226856</v>
+        <v>46097.52638289351</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1996,11 +1996,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.55092606481</v>
+        <v>46073.71759273148</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46126.02834039352</v>
+        <v>46126.19500706019</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2059,13 +2059,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.55092631944</v>
+        <v>46073.71759298611</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.34359585648</v>
+        <v>46114.51026252315</v>
       </c>
       <c r="D13" s="8">
-        <v>46169.71771503473</v>
+        <v>46169.884381701384</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2108,13 +2108,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.55092393518</v>
+        <v>46073.71759060185</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.359178321756</v>
+        <v>46097.52584498843</v>
       </c>
       <c r="D14" s="5">
-        <v>46100.59471405092</v>
+        <v>46100.761380717595</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2173,13 +2173,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.55092461806</v>
+        <v>46073.71759128472</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.34212127315</v>
+        <v>46114.50878793982</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.34214091435</v>
+        <v>46114.50880758102</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2238,13 +2238,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.55092490741</v>
+        <v>46073.71759157407</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.34256148148</v>
+        <v>46114.50922814815</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.34257719907</v>
+        <v>46114.509243865745</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2303,13 +2303,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.55092519676</v>
+        <v>46073.71759186343</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34357736111</v>
+        <v>46114.51024402778</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.34359680556</v>
+        <v>46114.51026347222</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2368,13 +2368,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.55092547454</v>
+        <v>46073.717592141205</v>
       </c>
       <c r="C18" s="5">
-        <v>46169.71758038194</v>
+        <v>46169.88424704861</v>
       </c>
       <c r="D18" s="5">
-        <v>46169.71766835648</v>
+        <v>46169.88433502315</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2417,13 +2417,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.55092603009</v>
+        <v>46073.71759269676</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.35928278935</v>
+        <v>46097.525949456016</v>
       </c>
       <c r="D19" s="8">
-        <v>46156.45183452546</v>
+        <v>46156.61850119213</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2482,13 +2482,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.550925752315</v>
+        <v>46073.71759241898</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.35931177084</v>
+        <v>46097.5259784375</v>
       </c>
       <c r="D20" s="5">
-        <v>46156.451852997685</v>
+        <v>46156.61851966435</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2547,13 +2547,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.55092663194</v>
+        <v>46073.717593298614</v>
       </c>
       <c r="C21" s="8">
-        <v>46128.26706200231</v>
+        <v>46128.433728668984</v>
       </c>
       <c r="D21" s="8">
-        <v>46128.26708372685</v>
+        <v>46128.433750393524</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2612,13 +2612,13 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.55092635417</v>
+        <v>46073.71759302083</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.359934479166</v>
+        <v>46097.52660114583</v>
       </c>
       <c r="D22" s="5">
-        <v>46097.35995533565</v>
+        <v>46097.52662200232</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>89</v>
@@ -2677,13 +2677,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.42669133102</v>
+        <v>46076.593357997685</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.34365599537</v>
+        <v>46114.51032266204</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.34380563657</v>
+        <v>46114.51047230324</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2742,13 +2742,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.55092366898</v>
+        <v>46073.71759033565</v>
       </c>
       <c r="C24" s="5">
-        <v>46169.717562060185</v>
+        <v>46169.88422872685</v>
       </c>
       <c r="D24" s="5">
-        <v>46169.71758065972</v>
+        <v>46169.884247326394</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2807,13 +2807,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.55092405093</v>
+        <v>46073.71759071759</v>
       </c>
       <c r="C25" s="8">
-        <v>46204.53274203704</v>
+        <v>46204.6994087037</v>
       </c>
       <c r="D25" s="8">
-        <v>46204.53276097222</v>
+        <v>46204.69942763889</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2860,13 +2860,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.55092359954</v>
+        <v>46073.7175902662</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.700224722226</v>
+        <v>46155.86689138889</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.70043725694</v>
+        <v>46155.86710392361</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -2925,13 +2925,13 @@
         <v>107</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.55092391204</v>
+        <v>46073.7175905787</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.35938876157</v>
+        <v>46097.52605542824</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.359390219906</v>
+        <v>46097.52605688658</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>108</v>
@@ -2986,13 +2986,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.550924201394</v>
+        <v>46073.71759086805</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.700210358795</v>
+        <v>46155.86687702546</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.7002115625</v>
+        <v>46155.866878229164</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3047,13 +3047,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.55092451389</v>
+        <v>46073.71759118055</v>
       </c>
       <c r="C29" s="8">
-        <v>46128.47049521991</v>
+        <v>46128.637161886574</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.470505081015</v>
+        <v>46128.63717174769</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3108,13 +3108,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.550924317125</v>
+        <v>46073.7175909838</v>
       </c>
       <c r="C30" s="5">
-        <v>46155.73690275463</v>
+        <v>46155.903569421294</v>
       </c>
       <c r="D30" s="5">
-        <v>46155.73691611111</v>
+        <v>46155.90358277778</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3173,13 +3173,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.55092459491</v>
+        <v>46073.71759126158</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.35941971064</v>
+        <v>46097.526086377315</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.359421354166</v>
+        <v>46097.52608802084</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3234,13 +3234,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.55092487269</v>
+        <v>46073.71759153935</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.73688930555</v>
+        <v>46155.903555972225</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.736890844906</v>
+        <v>46155.90355751157</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3295,13 +3295,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.55092601852</v>
+        <v>46073.717592685185</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.51638877315</v>
+        <v>46182.68305543982</v>
       </c>
       <c r="D33" s="8">
-        <v>46182.51639055555</v>
+        <v>46182.683057222224</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3360,13 +3360,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.55092635417</v>
+        <v>46073.71759302083</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.51607938657</v>
+        <v>46182.68274605324</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.51608083333</v>
+        <v>46182.6827475</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3421,13 +3421,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.550923194445</v>
+        <v>46073.71758986111</v>
       </c>
       <c r="C35" s="8">
-        <v>46182.516275648144</v>
+        <v>46182.682942314816</v>
       </c>
       <c r="D35" s="8">
-        <v>46182.516276875</v>
+        <v>46182.682943541666</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3482,13 +3482,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.55092516204</v>
+        <v>46073.7175918287</v>
       </c>
       <c r="C36" s="5">
-        <v>46191.72161346065</v>
+        <v>46191.888280127314</v>
       </c>
       <c r="D36" s="5">
-        <v>46191.72403972222</v>
+        <v>46191.89070638889</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3547,13 +3547,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.55092542824</v>
+        <v>46073.71759209491</v>
       </c>
       <c r="C37" s="8">
-        <v>46097.35999758102</v>
+        <v>46097.526664247685</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.67663081019</v>
+        <v>46169.84329747685</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3608,11 +3608,11 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.55092568287</v>
+        <v>46073.71759234954</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46191.72166524305</v>
+        <v>46191.88833190972</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3667,13 +3667,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46076.427483680556</v>
+        <v>46076.59415034722</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.70138586806</v>
+        <v>46154.86805253472</v>
       </c>
       <c r="D39" s="8">
-        <v>46156.4519491088</v>
+        <v>46156.618615775464</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3732,13 +3732,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46076.42761490741</v>
+        <v>46076.59428157407</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.70070490741</v>
+        <v>46154.86737157407</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.70070689815</v>
+        <v>46154.86737356482</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3797,13 +3797,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46076.42781732639</v>
+        <v>46076.59448399306</v>
       </c>
       <c r="C41" s="8">
-        <v>46154.70143751157</v>
+        <v>46154.86810417824</v>
       </c>
       <c r="D41" s="8">
-        <v>46154.70143878472</v>
+        <v>46154.86810545139</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3862,13 +3862,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.550924814816</v>
+        <v>46073.71759148148</v>
       </c>
       <c r="C42" s="5">
-        <v>46182.36395186343</v>
+        <v>46182.530618530094</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.36396486111</v>
+        <v>46182.53063152778</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3927,13 +3927,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.5509250926</v>
+        <v>46073.717591759254</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.36380178241</v>
+        <v>46182.53046844907</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.36380388889</v>
+        <v>46182.53047055556</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3988,13 +3988,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.55092538195</v>
+        <v>46073.71759204861</v>
       </c>
       <c r="C44" s="5">
-        <v>46182.363938344904</v>
+        <v>46182.530605011576</v>
       </c>
       <c r="D44" s="5">
-        <v>46182.36393960648</v>
+        <v>46182.53060627315</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4049,13 +4049,13 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.55092568287</v>
+        <v>46073.71759234954</v>
       </c>
       <c r="C45" s="8">
-        <v>46210.36510912037</v>
+        <v>46210.531775787036</v>
       </c>
       <c r="D45" s="8">
-        <v>46210.36512533565</v>
+        <v>46210.531792002315</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4102,13 +4102,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.55092594908</v>
+        <v>46073.717592615736</v>
       </c>
       <c r="C46" s="5">
-        <v>46153.92835325231</v>
+        <v>46154.09501991898</v>
       </c>
       <c r="D46" s="5">
-        <v>46153.92837542824</v>
+        <v>46154.09504209491</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4167,13 +4167,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.550923310184</v>
+        <v>46073.71758997685</v>
       </c>
       <c r="C47" s="8">
-        <v>46153.92841332176</v>
+        <v>46154.09507998843</v>
       </c>
       <c r="D47" s="8">
-        <v>46153.92842795139</v>
+        <v>46154.09509461805</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4232,13 +4232,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46091.56135321759</v>
+        <v>46091.72801988426</v>
       </c>
       <c r="C48" s="5">
-        <v>46153.92845228009</v>
+        <v>46154.09511894676</v>
       </c>
       <c r="D48" s="5">
-        <v>46153.928467199075</v>
+        <v>46154.09513386574</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4297,13 +4297,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46091.56139127315</v>
+        <v>46091.728057939814</v>
       </c>
       <c r="C49" s="8">
-        <v>46210.365331469904</v>
+        <v>46210.531998136576</v>
       </c>
       <c r="D49" s="8">
-        <v>46210.36535118056</v>
+        <v>46210.53201784722</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4362,13 +4362,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.55092363426</v>
+        <v>46073.71759030093</v>
       </c>
       <c r="C50" s="5">
-        <v>46191.62262605324</v>
+        <v>46191.78929271991</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.62263766203</v>
+        <v>46191.789304328704</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4415,13 +4415,13 @@
         <v>188</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.55092391204</v>
+        <v>46073.7175905787</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.62173520833</v>
+        <v>46191.788401875005</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.62175582176</v>
+        <v>46191.788422488426</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>163</v>
@@ -4480,13 +4480,13 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.55092414352</v>
+        <v>46073.717590810185</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.62260993056</v>
+        <v>46191.78927659722</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.62262652778</v>
+        <v>46191.789293194444</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4545,13 +4545,13 @@
         <v>197</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.55092443287</v>
+        <v>46073.717591099536</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.62370814815</v>
+        <v>46191.79037481482</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.6237183912</v>
+        <v>46191.79038505787</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>198</v>
@@ -4598,13 +4598,13 @@
         <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.550924675925</v>
+        <v>46073.71759134259</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.623270254626</v>
+        <v>46191.7899369213</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.623286145834</v>
+        <v>46191.7899528125</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>201</v>
@@ -4663,13 +4663,13 @@
         <v>205</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.55092490741</v>
+        <v>46073.71759157407</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.623691597226</v>
+        <v>46191.79035826389</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.62370916667</v>
+        <v>46191.790375833334</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>206</v>
@@ -4728,13 +4728,13 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.55092515046</v>
+        <v>46073.71759181713</v>
       </c>
       <c r="C56" s="5">
-        <v>46191.623014756944</v>
+        <v>46191.789681423616</v>
       </c>
       <c r="D56" s="5">
-        <v>46191.623708831015</v>
+        <v>46191.79037549769</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4793,11 +4793,11 @@
         <v>214</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.550925393516</v>
+        <v>46073.71759206019</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46198.66131490741</v>
+        <v>46198.827981574075</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>186</v>
@@ -4840,13 +4840,13 @@
         <v>216</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.550924386574</v>
+        <v>46073.71759105324</v>
       </c>
       <c r="C58" s="5">
-        <v>46195.44225010417</v>
+        <v>46195.608916770834</v>
       </c>
       <c r="D58" s="5">
-        <v>46195.44226982639</v>
+        <v>46195.60893649305</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>217</v>
@@ -4905,13 +4905,13 @@
         <v>219</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.550924166666</v>
+        <v>46073.71759083333</v>
       </c>
       <c r="C59" s="8">
-        <v>46195.44242412037</v>
+        <v>46195.60909078704</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.4424422338</v>
+        <v>46195.60910890046</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>220</v>
@@ -4970,13 +4970,13 @@
         <v>222</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.5509256713</v>
+        <v>46073.71759233796</v>
       </c>
       <c r="C60" s="5">
-        <v>46198.661309166666</v>
+        <v>46198.82797583334</v>
       </c>
       <c r="D60" s="5">
-        <v>46198.66132570602</v>
+        <v>46198.82799237268</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>223</v>
@@ -5035,11 +5035,11 @@
         <v>225</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.55092384259</v>
+        <v>46073.71759050926</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46191.72167136574</v>
+        <v>46191.88833803241</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5098,13 +5098,13 @@
         <v>227</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.432926064816</v>
+        <v>46076.59959273148</v>
       </c>
       <c r="C62" s="5">
-        <v>46198.66279835648</v>
+        <v>46198.82946502315</v>
       </c>
       <c r="D62" s="5">
-        <v>46198.66281634259</v>
+        <v>46198.829483009264</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>228</v>
@@ -5163,11 +5163,11 @@
         <v>231</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.550924641204</v>
+        <v>46073.71759130787</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.70154178241</v>
+        <v>46195.86820844907</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>232</v>
@@ -5210,13 +5210,13 @@
         <v>234</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.55092488426</v>
+        <v>46073.71759155093</v>
       </c>
       <c r="C64" s="5">
-        <v>46193.44056403935</v>
+        <v>46193.60723070602</v>
       </c>
       <c r="D64" s="5">
-        <v>46193.440598761576</v>
+        <v>46193.60726542824</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>235</v>
@@ -5275,13 +5275,13 @@
         <v>237</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.55092513889</v>
+        <v>46073.71759180556</v>
       </c>
       <c r="C65" s="8">
-        <v>46193.44072755787</v>
+        <v>46193.60739422454</v>
       </c>
       <c r="D65" s="8">
-        <v>46210.65897449074</v>
+        <v>46210.82564115741</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5340,13 +5340,13 @@
         <v>241</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.55092537037</v>
+        <v>46073.717592037036</v>
       </c>
       <c r="C66" s="5">
-        <v>46193.44078907407</v>
+        <v>46193.60745574074</v>
       </c>
       <c r="D66" s="5">
-        <v>46210.65897509259</v>
+        <v>46210.825641759264</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>242</v>
@@ -5405,13 +5405,13 @@
         <v>245</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.550925601856</v>
+        <v>46073.71759226852</v>
       </c>
       <c r="C67" s="8">
-        <v>46193.44082700231</v>
+        <v>46193.607493668984</v>
       </c>
       <c r="D67" s="8">
-        <v>46210.658975555554</v>
+        <v>46210.82564222222</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>246</v>
@@ -5470,13 +5470,13 @@
         <v>248</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.43405303241</v>
+        <v>46076.600719699076</v>
       </c>
       <c r="C68" s="5">
-        <v>46193.44097622685</v>
+        <v>46193.60764289352</v>
       </c>
       <c r="D68" s="5">
-        <v>46210.658976018516</v>
+        <v>46210.82564268519</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>229</v>
@@ -5535,13 +5535,13 @@
         <v>250</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.550925856485</v>
+        <v>46073.71759252315</v>
       </c>
       <c r="C69" s="8">
-        <v>46195.70153575232</v>
+        <v>46195.86820241898</v>
       </c>
       <c r="D69" s="8">
-        <v>46195.70155246528</v>
+        <v>46195.868219131946</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>183</v>
@@ -5600,11 +5600,11 @@
         <v>253</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.55092609954</v>
+        <v>46073.7175927662</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46210.36534954861</v>
+        <v>46210.53201621528</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>184</v>
@@ -5663,11 +5663,11 @@
         <v>255</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.55092376158</v>
+        <v>46073.71759042824</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46091.56779943287</v>
+        <v>46091.73446609954</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>256</v>
@@ -5710,11 +5710,11 @@
         <v>258</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.55092408565</v>
+        <v>46073.71759075232</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46204.53369581018</v>
+        <v>46204.700362476855</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5773,11 +5773,11 @@
         <v>263</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.55092435185</v>
+        <v>46073.71759101852</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46168.019966736116</v>
+        <v>46168.18663340277</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>264</v>
@@ -5836,11 +5836,11 @@
         <v>267</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.550924641204</v>
+        <v>46073.71759130787</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46169.00187577546</v>
+        <v>46169.16854244213</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>268</v>
@@ -5899,11 +5899,11 @@
         <v>272</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.55092489583</v>
+        <v>46073.7175915625</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46170.031903449075</v>
+        <v>46170.19857011574</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>273</v>
@@ -5960,11 +5960,11 @@
         <v>275</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.55092517361</v>
+        <v>46073.71759184028</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46091.56779884259</v>
+        <v>46091.73446550926</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>276</v>
@@ -6013,11 +6013,11 @@
         <v>278</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.55092543981</v>
+        <v>46073.71759210648</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46179.03319190972</v>
+        <v>46179.199858576394</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>279</v>
@@ -6076,11 +6076,11 @@
         <v>282</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.55092571759</v>
+        <v>46073.71759238426</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46179.03318975694</v>
+        <v>46179.19985642361</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>283</v>
@@ -6139,11 +6139,11 @@
         <v>285</v>
       </c>
       <c r="B79" s="8">
-        <v>46091.561731678245</v>
+        <v>46091.72839834491</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46091.56899111111</v>
+        <v>46091.73565777778</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>286</v>
@@ -6192,11 +6192,11 @@
         <v>288</v>
       </c>
       <c r="B80" s="5">
-        <v>46091.56227415509</v>
+        <v>46091.72894082176</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46179.03318989583</v>
+        <v>46179.199856562496</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>289</v>
@@ -6255,11 +6255,11 @@
         <v>291</v>
       </c>
       <c r="B81" s="8">
-        <v>46091.562334999995</v>
+        <v>46091.72900166667</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46190.007852002316</v>
+        <v>46190.17451866898</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>292</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -178,7 +178,7 @@
     <t>Recepcion Tableros</t>
   </si>
   <si>
-    <t>Ingenieria Servicios:,Embalaje</t>
+    <t>Ingenieria Servicios:,4200-4201 Embalaje</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
@@ -565,7 +565,7 @@
     <t>Pruebas FAT</t>
   </si>
   <si>
-    <t>RE-PINTADO</t>
+    <t>4200 - RE-PINTADO</t>
   </si>
   <si>
     <t>1213380470331434</t>
@@ -712,7 +712,7 @@
     <t>Montaje:</t>
   </si>
   <si>
-    <t>Revestimiento,Montaje motor,Montaje Sensores,Montaje Alabe,Montaje Rodete,Pruebas FAT,RE-PINTADO</t>
+    <t>Revestimiento,Montaje motor,Montaje Sensores,Montaje Alabe,Montaje Rodete,Pruebas FAT,4200 - RE-PINTADO</t>
   </si>
   <si>
     <t>1213380471139137</t>
@@ -775,7 +775,7 @@
     <t>1213380471139142</t>
   </si>
   <si>
-    <t>Montaje:,Coordinacion Entrega con Cliente</t>
+    <t>Montaje:,4200-4201Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>1213380471139143</t>
@@ -784,13 +784,13 @@
     <t>Logistica:</t>
   </si>
   <si>
-    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
+    <t>4200-4201Coordinacion Entrega con Cliente,4200-4201 Embalaje,4200-4201 PACKING LIST,4200-4201 Despacho</t>
   </si>
   <si>
     <t>1213380471139144</t>
   </si>
   <si>
-    <t>Coordinacion Entrega con Cliente</t>
+    <t>4200-4201Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>Karin Pinto</t>
@@ -799,25 +799,25 @@
     <t>kpinto@zitron.com</t>
   </si>
   <si>
-    <t>Embalaje,Logistica:</t>
+    <t>4200-4201 Embalaje,Logistica:</t>
   </si>
   <si>
     <t>1213380471139145</t>
   </si>
   <si>
-    <t>Embalaje</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Revisión tableros pruebas</t>
-  </si>
-  <si>
-    <t>PACKING LIST,Logistica:</t>
+    <t>4200-4201 Embalaje</t>
+  </si>
+  <si>
+    <t>4200-4201Coordinacion Entrega con Cliente,Revisión tableros pruebas</t>
+  </si>
+  <si>
+    <t>4200-4201 PACKING LIST,Logistica:</t>
   </si>
   <si>
     <t>1213380471139146</t>
   </si>
   <si>
-    <t>PACKING LIST</t>
+    <t>4200-4201 PACKING LIST</t>
   </si>
   <si>
     <t>Nicolás Mol</t>
@@ -826,13 +826,13 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>Despacho,Logistica:</t>
+    <t>4200-4201 Despacho,Logistica:</t>
   </si>
   <si>
     <t>1213380471139147</t>
   </si>
   <si>
-    <t>Despacho</t>
+    <t>4200-4201 Despacho</t>
   </si>
   <si>
     <t>Gestion,Costos,Logistica:,Instalación componentes</t>
@@ -865,7 +865,7 @@
     <t>Costos</t>
   </si>
   <si>
-    <t>Despacho,Analisis de costeo</t>
+    <t>4200-4201 Despacho,Analisis de costeo</t>
   </si>
   <si>
     <t>1213595645393448</t>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46210.53201621528</v>
+        <v>46212.62926046296</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>184</v>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46204.700362476855</v>
+        <v>46212.62932537037</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46168.18663340277</v>
+        <v>46212.62935025463</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>264</v>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46169.16854244213</v>
+        <v>46212.62937076389</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>268</v>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46170.19857011574</v>
+        <v>46212.62939324074</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>273</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="290">
   <si>
     <t xml:space="preserve">50001498-CALABRESSE METRO STO DOMINGO  POZOS  </t>
   </si>
@@ -271,9 +271,6 @@
     <t>propuesta Nucleo rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete OT 4200</t>
   </si>
   <si>
@@ -299,12 +296,6 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento 4200</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC materiales OT 4200</t>
@@ -2562,11 +2553,9 @@
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>86</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H21" s="9"/>
       <c r="I21" s="8">
         <v>46009</v>
       </c>
@@ -2589,7 +2578,7 @@
         <v>66</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q21" s="8">
         <v>46009</v>
@@ -2609,7 +2598,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B22" s="5">
         <v>46073.71759302083</v>
@@ -2621,7 +2610,7 @@
         <v>46097.52662200232</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2654,7 +2643,7 @@
         <v>48</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q22" s="5">
         <v>46004</v>
@@ -2674,7 +2663,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B23" s="8">
         <v>46076.593357997685</v>
@@ -2686,7 +2675,7 @@
         <v>46114.51047230324</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2719,7 +2708,7 @@
         <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="8">
         <v>46009</v>
@@ -2739,7 +2728,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5">
         <v>46073.71759033565</v>
@@ -2751,17 +2740,15 @@
         <v>46169.884247326394</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>97</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H24" s="6"/>
       <c r="I24" s="5">
         <v>46009</v>
       </c>
@@ -2784,7 +2771,7 @@
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q24" s="5">
         <v>46009</v>
@@ -2804,7 +2791,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B25" s="8">
         <v>46073.71759071759</v>
@@ -2816,7 +2803,7 @@
         <v>46204.69942763889</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2840,7 +2827,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2857,7 +2844,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B26" s="5">
         <v>46073.7175902662</v>
@@ -2869,16 +2856,16 @@
         <v>46155.86710392361</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I26" s="5">
         <v>46006</v>
@@ -2896,13 +2883,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q26" s="5">
         <v>46006</v>
@@ -2922,7 +2909,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B27" s="8">
         <v>46073.7175905787</v>
@@ -2934,16 +2921,16 @@
         <v>46097.52605688658</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I27" s="8">
         <v>46006</v>
@@ -2961,13 +2948,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>79</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2975,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U27" s="10" t="s">
         <v>56</v>
@@ -2983,7 +2970,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B28" s="5">
         <v>46073.71759086805</v>
@@ -2995,16 +2982,16 @@
         <v>46155.866878229164</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I28" s="5">
         <v>46027</v>
@@ -3022,13 +3009,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3036,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U28" s="10" t="s">
         <v>56</v>
@@ -3044,7 +3031,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B29" s="8">
         <v>46073.71759118055</v>
@@ -3056,16 +3043,16 @@
         <v>46128.63717174769</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I29" s="8">
         <v>46027</v>
@@ -3083,13 +3070,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3097,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U29" s="10" t="s">
         <v>56</v>
@@ -3105,7 +3092,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B30" s="5">
         <v>46073.7175909838</v>
@@ -3117,16 +3104,16 @@
         <v>46155.90358277778</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I30" s="5">
         <v>46013</v>
@@ -3144,13 +3131,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q30" s="5">
         <v>46013</v>
@@ -3170,7 +3157,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B31" s="8">
         <v>46073.71759126158</v>
@@ -3182,16 +3169,16 @@
         <v>46097.52608802084</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I31" s="8">
         <v>46013</v>
@@ -3209,13 +3196,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>82</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3223,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U31" s="10" t="s">
         <v>56</v>
@@ -3231,7 +3218,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B32" s="5">
         <v>46073.71759153935</v>
@@ -3243,16 +3230,16 @@
         <v>46155.90355751157</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I32" s="5">
         <v>46017</v>
@@ -3270,13 +3257,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="O32" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="O32" s="6" t="s">
-        <v>121</v>
-      </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3284,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U32" s="10" t="s">
         <v>56</v>
@@ -3292,7 +3279,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B33" s="8">
         <v>46073.717592685185</v>
@@ -3304,16 +3291,16 @@
         <v>46182.683057222224</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I33" s="8">
         <v>46013</v>
@@ -3331,13 +3318,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q33" s="8">
         <v>46013</v>
@@ -3357,7 +3344,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B34" s="5">
         <v>46073.71759302083</v>
@@ -3369,16 +3356,16 @@
         <v>46182.6827475</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I34" s="5">
         <v>46013</v>
@@ -3396,13 +3383,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3410,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U34" s="10" t="s">
         <v>56</v>
@@ -3418,7 +3405,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B35" s="8">
         <v>46073.71758986111</v>
@@ -3430,16 +3417,16 @@
         <v>46182.682943541666</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I35" s="8">
         <v>46017</v>
@@ -3457,13 +3444,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="O35" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="O35" s="9" t="s">
-        <v>130</v>
-      </c>
       <c r="P35" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3471,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U35" s="10" t="s">
         <v>56</v>
@@ -3479,7 +3466,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46073.7175918287</v>
@@ -3491,16 +3478,16 @@
         <v>46191.89070638889</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I36" s="5">
         <v>46007</v>
@@ -3518,13 +3505,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q36" s="5">
         <v>46007</v>
@@ -3544,7 +3531,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B37" s="8">
         <v>46073.71759209491</v>
@@ -3556,16 +3543,16 @@
         <v>46169.84329747685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I37" s="8">
         <v>46007</v>
@@ -3583,13 +3570,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3597,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U37" s="10" t="s">
         <v>56</v>
@@ -3605,7 +3592,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46073.71759234954</v>
@@ -3615,16 +3602,16 @@
         <v>46191.88833190972</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I38" s="5">
         <v>46017</v>
@@ -3642,13 +3629,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="O38" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="O38" s="6" t="s">
-        <v>139</v>
-      </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3656,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U38" s="10" t="s">
         <v>56</v>
@@ -3664,7 +3651,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B39" s="8">
         <v>46076.59415034722</v>
@@ -3676,16 +3663,16 @@
         <v>46156.618615775464</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I39" s="8">
         <v>46013</v>
@@ -3703,13 +3690,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q39" s="8">
         <v>46013</v>
@@ -3729,7 +3716,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46076.59428157407</v>
@@ -3741,16 +3728,16 @@
         <v>46154.86737356482</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I40" s="5">
         <v>46013</v>
@@ -3768,13 +3755,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="Q40" s="5">
         <v>46013</v>
@@ -3786,7 +3773,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U40" s="10" t="s">
         <v>56</v>
@@ -3794,7 +3781,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B41" s="8">
         <v>46076.59448399306</v>
@@ -3806,16 +3793,16 @@
         <v>46154.86810545139</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I41" s="8">
         <v>46057</v>
@@ -3833,13 +3820,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="Q41" s="8">
         <v>46057</v>
@@ -3851,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U41" s="10" t="s">
         <v>56</v>
@@ -3859,7 +3846,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46073.71759148148</v>
@@ -3871,16 +3858,16 @@
         <v>46182.53063152778</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I42" s="5">
         <v>46013</v>
@@ -3898,13 +3885,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q42" s="5">
         <v>46013</v>
@@ -3924,7 +3911,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B43" s="8">
         <v>46073.717591759254</v>
@@ -3936,16 +3923,16 @@
         <v>46182.53047055556</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I43" s="8">
         <v>46013</v>
@@ -3963,13 +3950,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3977,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="T43" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U43" s="10" t="s">
         <v>56</v>
@@ -3985,7 +3972,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B44" s="5">
         <v>46073.71759204861</v>
@@ -3997,16 +3984,16 @@
         <v>46182.53060627315</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I44" s="5">
         <v>46037</v>
@@ -4024,13 +4011,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="O44" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="O44" s="6" t="s">
-        <v>159</v>
-      </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4038,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="T44" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U44" s="10" t="s">
         <v>56</v>
@@ -4046,7 +4033,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B45" s="8">
         <v>46073.71759234954</v>
@@ -4058,7 +4045,7 @@
         <v>46210.531792002315</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4082,7 +4069,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4099,7 +4086,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B46" s="5">
         <v>46073.717592615736</v>
@@ -4111,16 +4098,16 @@
         <v>46154.09504209491</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I46" s="5">
         <v>46009</v>
@@ -4138,13 +4125,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="Q46" s="5">
         <v>46009</v>
@@ -4164,7 +4151,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46073.71758997685</v>
@@ -4176,16 +4163,16 @@
         <v>46154.09509461805</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I47" s="8">
         <v>46065</v>
@@ -4203,13 +4190,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="Q47" s="8">
         <v>46065</v>
@@ -4229,7 +4216,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B48" s="5">
         <v>46091.72801988426</v>
@@ -4241,16 +4228,16 @@
         <v>46154.09513386574</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I48" s="5">
         <v>46072</v>
@@ -4268,13 +4255,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="Q48" s="5">
         <v>46072</v>
@@ -4294,7 +4281,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B49" s="8">
         <v>46091.728057939814</v>
@@ -4306,16 +4293,16 @@
         <v>46210.53201784722</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I49" s="8">
         <v>46160</v>
@@ -4333,13 +4320,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="Q49" s="8">
         <v>46160</v>
@@ -4359,7 +4346,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46073.71759030093</v>
@@ -4371,7 +4358,7 @@
         <v>46191.789304328704</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4395,7 +4382,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4412,7 +4399,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46073.7175905787</v>
@@ -4424,16 +4411,16 @@
         <v>46191.788422488426</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I51" s="8">
         <v>46069</v>
@@ -4451,13 +4438,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q51" s="8">
         <v>46069</v>
@@ -4477,7 +4464,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5">
         <v>46073.717590810185</v>
@@ -4489,16 +4476,16 @@
         <v>46191.789293194444</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I52" s="5">
         <v>46071</v>
@@ -4516,13 +4503,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="5">
         <v>46071</v>
@@ -4542,7 +4529,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46073.717591099536</v>
@@ -4554,7 +4541,7 @@
         <v>46191.79038505787</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4578,7 +4565,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4595,7 +4582,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46073.71759134259</v>
@@ -4607,16 +4594,16 @@
         <v>46191.7899528125</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I54" s="5">
         <v>46073</v>
@@ -4634,13 +4621,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46073</v>
@@ -4660,7 +4647,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B55" s="8">
         <v>46073.71759157407</v>
@@ -4672,16 +4659,16 @@
         <v>46191.790375833334</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I55" s="8">
         <v>46084</v>
@@ -4699,13 +4686,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="Q55" s="8">
         <v>46084</v>
@@ -4725,7 +4712,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
         <v>46073.71759181713</v>
@@ -4737,16 +4724,16 @@
         <v>46191.79037549769</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I56" s="5">
         <v>46104</v>
@@ -4764,13 +4751,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="Q56" s="5">
         <v>46104</v>
@@ -4785,12 +4772,12 @@
         <v>31</v>
       </c>
       <c r="U56" s="12" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B57" s="8">
         <v>46073.71759206019</v>
@@ -4800,7 +4787,7 @@
         <v>46198.827981574075</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4824,7 +4811,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4837,7 +4824,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46073.71759105324</v>
@@ -4849,16 +4836,16 @@
         <v>46195.60893649305</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I58" s="5">
         <v>46153</v>
@@ -4876,13 +4863,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q58" s="5">
         <v>46153</v>
@@ -4902,7 +4889,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B59" s="8">
         <v>46073.71759083333</v>
@@ -4914,16 +4901,16 @@
         <v>46195.60910890046</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I59" s="8">
         <v>46135</v>
@@ -4941,13 +4928,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Q59" s="8">
         <v>46134</v>
@@ -4967,7 +4954,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46073.71759233796</v>
@@ -4979,16 +4966,16 @@
         <v>46198.82799237268</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I60" s="5">
         <v>46071</v>
@@ -5006,13 +4993,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Q60" s="5">
         <v>46071</v>
@@ -5032,7 +5019,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B61" s="8">
         <v>46073.71759050926</v>
@@ -5048,10 +5035,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I61" s="8">
         <v>46115</v>
@@ -5069,13 +5056,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Q61" s="8">
         <v>46115</v>
@@ -5090,12 +5077,12 @@
         <v>31</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46076.59959273148</v>
@@ -5107,16 +5094,16 @@
         <v>46198.829483009264</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I62" s="5">
         <v>46139</v>
@@ -5134,13 +5121,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Q62" s="5">
         <v>46139</v>
@@ -5152,7 +5139,7 @@
         <v>1</v>
       </c>
       <c r="T62" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="U62" s="11" t="s">
         <v>32</v>
@@ -5160,7 +5147,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B63" s="8">
         <v>46073.71759130787</v>
@@ -5170,7 +5157,7 @@
         <v>46195.86820844907</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5194,7 +5181,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5207,7 +5194,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B64" s="5">
         <v>46073.71759155093</v>
@@ -5219,17 +5206,15 @@
         <v>46193.60726542824</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>86</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H64" s="6"/>
       <c r="I64" s="5">
         <v>46106</v>
       </c>
@@ -5246,13 +5231,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="Q64" s="5">
         <v>46106</v>
@@ -5272,7 +5257,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B65" s="8">
         <v>46073.71759180556</v>
@@ -5284,17 +5269,15 @@
         <v>46210.82564115741</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>86</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H65" s="9"/>
       <c r="I65" s="8">
         <v>46155</v>
       </c>
@@ -5311,13 +5294,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Q65" s="8">
         <v>46155</v>
@@ -5337,7 +5320,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B66" s="5">
         <v>46073.717592037036</v>
@@ -5349,17 +5332,15 @@
         <v>46210.825641759264</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>86</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H66" s="6"/>
       <c r="I66" s="5">
         <v>46139</v>
       </c>
@@ -5376,13 +5357,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="Q66" s="5">
         <v>46139</v>
@@ -5394,7 +5375,7 @@
         <v>1</v>
       </c>
       <c r="T66" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="U66" s="11" t="s">
         <v>32</v>
@@ -5402,7 +5383,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B67" s="8">
         <v>46073.71759226852</v>
@@ -5414,17 +5395,15 @@
         <v>46210.82564222222</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>86</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H67" s="9"/>
       <c r="I67" s="8">
         <v>46141</v>
       </c>
@@ -5441,13 +5420,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Q67" s="8">
         <v>46141</v>
@@ -5467,7 +5446,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B68" s="5">
         <v>46076.600719699076</v>
@@ -5479,17 +5458,15 @@
         <v>46210.82564268519</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>86</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H68" s="6"/>
       <c r="I68" s="5">
         <v>46146</v>
       </c>
@@ -5506,13 +5483,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Q68" s="5">
         <v>46146</v>
@@ -5532,7 +5509,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B69" s="8">
         <v>46073.71759252315</v>
@@ -5544,17 +5521,15 @@
         <v>46195.868219131946</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>86</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H69" s="9"/>
       <c r="I69" s="8">
         <v>46157</v>
       </c>
@@ -5571,13 +5546,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="Q69" s="8">
         <v>46157</v>
@@ -5597,7 +5572,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B70" s="5">
         <v>46073.7175927662</v>
@@ -5607,17 +5582,15 @@
         <v>46212.62926046296</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>86</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H70" s="6"/>
       <c r="I70" s="5">
         <v>46161</v>
       </c>
@@ -5634,13 +5607,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="Q70" s="5">
         <v>46161</v>
@@ -5655,12 +5628,12 @@
         <v>31</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B71" s="8">
         <v>46073.71759042824</v>
@@ -5670,7 +5643,7 @@
         <v>46091.73446609954</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5694,7 +5667,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5707,7 +5680,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B72" s="5">
         <v>46073.71759075232</v>
@@ -5717,16 +5690,16 @@
         <v>46212.62932537037</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I72" s="5">
         <v>46162</v>
@@ -5744,13 +5717,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q72" s="5">
         <v>46162</v>
@@ -5770,7 +5743,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B73" s="8">
         <v>46073.71759101852</v>
@@ -5780,17 +5753,15 @@
         <v>46212.62935025463</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>86</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H73" s="9"/>
       <c r="I73" s="8">
         <v>46163</v>
       </c>
@@ -5807,13 +5778,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Q73" s="8">
         <v>46163</v>
@@ -5833,7 +5804,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B74" s="5">
         <v>46073.71759130787</v>
@@ -5843,16 +5814,16 @@
         <v>46212.62937076389</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="I74" s="5">
         <v>46168</v>
@@ -5870,13 +5841,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Q74" s="5">
         <v>46168</v>
@@ -5896,7 +5867,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B75" s="8">
         <v>46073.7175915625</v>
@@ -5906,16 +5877,16 @@
         <v>46212.62939324074</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -5931,13 +5902,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Q75" s="8">
         <v>46169</v>
@@ -5957,7 +5928,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B76" s="5">
         <v>46073.71759184028</v>
@@ -5967,7 +5938,7 @@
         <v>46091.73446550926</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5991,7 +5962,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6002,7 +5973,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U76" s="10" t="s">
         <v>56</v>
@@ -6010,7 +5981,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B77" s="8">
         <v>46073.71759210648</v>
@@ -6020,16 +5991,16 @@
         <v>46179.199858576394</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I77" s="8">
         <v>46170</v>
@@ -6047,13 +6018,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="O77" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="P77" s="9" t="s">
         <v>273</v>
-      </c>
-      <c r="P77" s="9" t="s">
-        <v>276</v>
       </c>
       <c r="Q77" s="8">
         <v>46170</v>
@@ -6073,7 +6044,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B78" s="5">
         <v>46073.71759238426</v>
@@ -6083,16 +6054,16 @@
         <v>46179.19985642361</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I78" s="5">
         <v>46170</v>
@@ -6110,13 +6081,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="Q78" s="5">
         <v>46170</v>
@@ -6136,7 +6107,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B79" s="8">
         <v>46091.72839834491</v>
@@ -6146,7 +6117,7 @@
         <v>46091.73565777778</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6170,7 +6141,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6181,7 +6152,7 @@
         <v>0</v>
       </c>
       <c r="T79" s="11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U79" s="10" t="s">
         <v>56</v>
@@ -6189,7 +6160,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B80" s="5">
         <v>46091.72894082176</v>
@@ -6199,7 +6170,7 @@
         <v>46179.199856562496</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6226,13 +6197,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="Q80" s="5">
         <v>46170</v>
@@ -6252,7 +6223,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B81" s="8">
         <v>46091.72900166667</v>
@@ -6262,7 +6233,7 @@
         <v>46190.17451866898</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6289,13 +6260,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="O81" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="O81" s="9" t="s">
-        <v>289</v>
-      </c>
       <c r="P81" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="Q81" s="8">
         <v>46181</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="291">
   <si>
     <t xml:space="preserve">50001498-CALABRESSE METRO STO DOMINGO  POZOS  </t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>propuesta Nucleo rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete OT 4200</t>
@@ -2544,7 +2547,7 @@
         <v>46128.433728668984</v>
       </c>
       <c r="D21" s="8">
-        <v>46128.433750393524</v>
+        <v>46223.823994606486</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2553,9 +2556,11 @@
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="9"/>
+        <v>86</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>86</v>
+      </c>
       <c r="I21" s="8">
         <v>46009</v>
       </c>
@@ -2578,7 +2583,7 @@
         <v>66</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q21" s="8">
         <v>46009</v>
@@ -2598,7 +2603,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5">
         <v>46073.71759302083</v>
@@ -2610,7 +2615,7 @@
         <v>46097.52662200232</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2643,7 +2648,7 @@
         <v>48</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q22" s="5">
         <v>46004</v>
@@ -2663,7 +2668,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B23" s="8">
         <v>46076.593357997685</v>
@@ -2675,7 +2680,7 @@
         <v>46114.51047230324</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2708,7 +2713,7 @@
         <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="8">
         <v>46009</v>
@@ -2728,7 +2733,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B24" s="5">
         <v>46073.71759033565</v>
@@ -2737,18 +2742,20 @@
         <v>46169.88422872685</v>
       </c>
       <c r="D24" s="5">
-        <v>46169.884247326394</v>
+        <v>46223.82399125</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="6"/>
+        <v>86</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="I24" s="5">
         <v>46009</v>
       </c>
@@ -2771,7 +2778,7 @@
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q24" s="5">
         <v>46009</v>
@@ -2791,7 +2798,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B25" s="8">
         <v>46073.71759071759</v>
@@ -2803,7 +2810,7 @@
         <v>46204.69942763889</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2827,7 +2834,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2844,7 +2851,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B26" s="5">
         <v>46073.7175902662</v>
@@ -2856,16 +2863,16 @@
         <v>46155.86710392361</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I26" s="5">
         <v>46006</v>
@@ -2883,13 +2890,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q26" s="5">
         <v>46006</v>
@@ -2909,7 +2916,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B27" s="8">
         <v>46073.7175905787</v>
@@ -2921,16 +2928,16 @@
         <v>46097.52605688658</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I27" s="8">
         <v>46006</v>
@@ -2948,13 +2955,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>79</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2962,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U27" s="10" t="s">
         <v>56</v>
@@ -2970,7 +2977,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B28" s="5">
         <v>46073.71759086805</v>
@@ -2982,16 +2989,16 @@
         <v>46155.866878229164</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I28" s="5">
         <v>46027</v>
@@ -3009,13 +3016,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3023,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U28" s="10" t="s">
         <v>56</v>
@@ -3031,7 +3038,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B29" s="8">
         <v>46073.71759118055</v>
@@ -3043,16 +3050,16 @@
         <v>46128.63717174769</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I29" s="8">
         <v>46027</v>
@@ -3070,13 +3077,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3084,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U29" s="10" t="s">
         <v>56</v>
@@ -3092,7 +3099,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46073.7175909838</v>
@@ -3104,16 +3111,16 @@
         <v>46155.90358277778</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I30" s="5">
         <v>46013</v>
@@ -3131,13 +3138,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q30" s="5">
         <v>46013</v>
@@ -3157,7 +3164,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46073.71759126158</v>
@@ -3169,16 +3176,16 @@
         <v>46097.52608802084</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I31" s="8">
         <v>46013</v>
@@ -3196,13 +3203,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>82</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3210,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U31" s="10" t="s">
         <v>56</v>
@@ -3218,7 +3225,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46073.71759153935</v>
@@ -3230,16 +3237,16 @@
         <v>46155.90355751157</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I32" s="5">
         <v>46017</v>
@@ -3257,13 +3264,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3271,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U32" s="10" t="s">
         <v>56</v>
@@ -3279,7 +3286,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B33" s="8">
         <v>46073.717592685185</v>
@@ -3291,16 +3298,16 @@
         <v>46182.683057222224</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I33" s="8">
         <v>46013</v>
@@ -3318,13 +3325,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q33" s="8">
         <v>46013</v>
@@ -3344,7 +3351,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B34" s="5">
         <v>46073.71759302083</v>
@@ -3356,16 +3363,16 @@
         <v>46182.6827475</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I34" s="5">
         <v>46013</v>
@@ -3383,13 +3390,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3397,7 +3404,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U34" s="10" t="s">
         <v>56</v>
@@ -3405,7 +3412,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B35" s="8">
         <v>46073.71758986111</v>
@@ -3417,16 +3424,16 @@
         <v>46182.682943541666</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I35" s="8">
         <v>46017</v>
@@ -3444,13 +3451,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3458,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U35" s="10" t="s">
         <v>56</v>
@@ -3466,7 +3473,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B36" s="5">
         <v>46073.7175918287</v>
@@ -3478,16 +3485,16 @@
         <v>46191.89070638889</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I36" s="5">
         <v>46007</v>
@@ -3505,13 +3512,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q36" s="5">
         <v>46007</v>
@@ -3531,7 +3538,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B37" s="8">
         <v>46073.71759209491</v>
@@ -3543,16 +3550,16 @@
         <v>46169.84329747685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I37" s="8">
         <v>46007</v>
@@ -3570,13 +3577,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3584,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U37" s="10" t="s">
         <v>56</v>
@@ -3592,7 +3599,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46073.71759234954</v>
@@ -3602,16 +3609,16 @@
         <v>46191.88833190972</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I38" s="5">
         <v>46017</v>
@@ -3629,13 +3636,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3643,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U38" s="10" t="s">
         <v>56</v>
@@ -3651,7 +3658,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B39" s="8">
         <v>46076.59415034722</v>
@@ -3663,16 +3670,16 @@
         <v>46156.618615775464</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I39" s="8">
         <v>46013</v>
@@ -3690,13 +3697,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q39" s="8">
         <v>46013</v>
@@ -3716,7 +3723,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46076.59428157407</v>
@@ -3728,16 +3735,16 @@
         <v>46154.86737356482</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I40" s="5">
         <v>46013</v>
@@ -3755,13 +3762,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q40" s="5">
         <v>46013</v>
@@ -3773,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U40" s="10" t="s">
         <v>56</v>
@@ -3781,7 +3788,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
         <v>46076.59448399306</v>
@@ -3793,16 +3800,16 @@
         <v>46154.86810545139</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I41" s="8">
         <v>46057</v>
@@ -3820,13 +3827,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="8">
         <v>46057</v>
@@ -3838,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U41" s="10" t="s">
         <v>56</v>
@@ -3846,7 +3853,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46073.71759148148</v>
@@ -3858,16 +3865,16 @@
         <v>46182.53063152778</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I42" s="5">
         <v>46013</v>
@@ -3885,13 +3892,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q42" s="5">
         <v>46013</v>
@@ -3911,7 +3918,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B43" s="8">
         <v>46073.717591759254</v>
@@ -3923,16 +3930,16 @@
         <v>46182.53047055556</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I43" s="8">
         <v>46013</v>
@@ -3950,13 +3957,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3964,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="T43" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U43" s="10" t="s">
         <v>56</v>
@@ -3972,7 +3979,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
         <v>46073.71759204861</v>
@@ -3984,16 +3991,16 @@
         <v>46182.53060627315</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I44" s="5">
         <v>46037</v>
@@ -4011,13 +4018,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4025,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="T44" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U44" s="10" t="s">
         <v>56</v>
@@ -4033,7 +4040,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B45" s="8">
         <v>46073.71759234954</v>
@@ -4045,7 +4052,7 @@
         <v>46210.531792002315</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4069,7 +4076,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4086,7 +4093,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B46" s="5">
         <v>46073.717592615736</v>
@@ -4098,16 +4105,16 @@
         <v>46154.09504209491</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I46" s="5">
         <v>46009</v>
@@ -4125,13 +4132,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q46" s="5">
         <v>46009</v>
@@ -4151,7 +4158,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46073.71758997685</v>
@@ -4163,16 +4170,16 @@
         <v>46154.09509461805</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I47" s="8">
         <v>46065</v>
@@ -4190,13 +4197,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q47" s="8">
         <v>46065</v>
@@ -4216,7 +4223,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46091.72801988426</v>
@@ -4228,16 +4235,16 @@
         <v>46154.09513386574</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I48" s="5">
         <v>46072</v>
@@ -4255,13 +4262,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q48" s="5">
         <v>46072</v>
@@ -4281,7 +4288,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B49" s="8">
         <v>46091.728057939814</v>
@@ -4293,16 +4300,16 @@
         <v>46210.53201784722</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I49" s="8">
         <v>46160</v>
@@ -4320,13 +4327,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="8">
         <v>46160</v>
@@ -4346,7 +4353,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46073.71759030093</v>
@@ -4358,7 +4365,7 @@
         <v>46191.789304328704</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4382,7 +4389,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4399,7 +4406,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B51" s="8">
         <v>46073.7175905787</v>
@@ -4411,16 +4418,16 @@
         <v>46191.788422488426</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I51" s="8">
         <v>46069</v>
@@ -4438,13 +4445,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q51" s="8">
         <v>46069</v>
@@ -4464,7 +4471,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5">
         <v>46073.717590810185</v>
@@ -4476,16 +4483,16 @@
         <v>46191.789293194444</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I52" s="5">
         <v>46071</v>
@@ -4503,13 +4510,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="5">
         <v>46071</v>
@@ -4529,7 +4536,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="8">
         <v>46073.717591099536</v>
@@ -4541,7 +4548,7 @@
         <v>46191.79038505787</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4565,7 +4572,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4582,7 +4589,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46073.71759134259</v>
@@ -4594,16 +4601,16 @@
         <v>46191.7899528125</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I54" s="5">
         <v>46073</v>
@@ -4621,13 +4628,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q54" s="5">
         <v>46073</v>
@@ -4647,7 +4654,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B55" s="8">
         <v>46073.71759157407</v>
@@ -4659,16 +4666,16 @@
         <v>46191.790375833334</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I55" s="8">
         <v>46084</v>
@@ -4686,13 +4693,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q55" s="8">
         <v>46084</v>
@@ -4712,7 +4719,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46073.71759181713</v>
@@ -4724,16 +4731,16 @@
         <v>46191.79037549769</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I56" s="5">
         <v>46104</v>
@@ -4751,13 +4758,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="5">
         <v>46104</v>
@@ -4772,12 +4779,12 @@
         <v>31</v>
       </c>
       <c r="U56" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B57" s="8">
         <v>46073.71759206019</v>
@@ -4787,7 +4794,7 @@
         <v>46198.827981574075</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4811,7 +4818,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4824,7 +4831,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
         <v>46073.71759105324</v>
@@ -4836,16 +4843,16 @@
         <v>46195.60893649305</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I58" s="5">
         <v>46153</v>
@@ -4863,13 +4870,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q58" s="5">
         <v>46153</v>
@@ -4889,7 +4896,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B59" s="8">
         <v>46073.71759083333</v>
@@ -4901,16 +4908,16 @@
         <v>46195.60910890046</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I59" s="8">
         <v>46135</v>
@@ -4928,13 +4935,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q59" s="8">
         <v>46134</v>
@@ -4954,7 +4961,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B60" s="5">
         <v>46073.71759233796</v>
@@ -4966,16 +4973,16 @@
         <v>46198.82799237268</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I60" s="5">
         <v>46071</v>
@@ -4993,13 +5000,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q60" s="5">
         <v>46071</v>
@@ -5019,7 +5026,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B61" s="8">
         <v>46073.71759050926</v>
@@ -5035,10 +5042,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I61" s="8">
         <v>46115</v>
@@ -5056,13 +5063,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q61" s="8">
         <v>46115</v>
@@ -5077,12 +5084,12 @@
         <v>31</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B62" s="5">
         <v>46076.59959273148</v>
@@ -5094,16 +5101,16 @@
         <v>46198.829483009264</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I62" s="5">
         <v>46139</v>
@@ -5121,13 +5128,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q62" s="5">
         <v>46139</v>
@@ -5139,7 +5146,7 @@
         <v>1</v>
       </c>
       <c r="T62" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="U62" s="11" t="s">
         <v>32</v>
@@ -5147,7 +5154,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B63" s="8">
         <v>46073.71759130787</v>
@@ -5157,7 +5164,7 @@
         <v>46195.86820844907</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5181,7 +5188,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5194,7 +5201,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B64" s="5">
         <v>46073.71759155093</v>
@@ -5203,18 +5210,20 @@
         <v>46193.60723070602</v>
       </c>
       <c r="D64" s="5">
-        <v>46193.60726542824</v>
+        <v>46223.82415971065</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H64" s="6"/>
+        <v>86</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="I64" s="5">
         <v>46106</v>
       </c>
@@ -5231,13 +5240,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q64" s="5">
         <v>46106</v>
@@ -5257,7 +5266,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B65" s="8">
         <v>46073.71759180556</v>
@@ -5266,18 +5275,20 @@
         <v>46193.60739422454</v>
       </c>
       <c r="D65" s="8">
-        <v>46210.82564115741</v>
+        <v>46223.82415605324</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H65" s="9"/>
+        <v>86</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>86</v>
+      </c>
       <c r="I65" s="8">
         <v>46155</v>
       </c>
@@ -5294,13 +5305,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q65" s="8">
         <v>46155</v>
@@ -5320,7 +5331,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B66" s="5">
         <v>46073.717592037036</v>
@@ -5329,18 +5340,20 @@
         <v>46193.60745574074</v>
       </c>
       <c r="D66" s="5">
-        <v>46210.825641759264</v>
+        <v>46223.824151967594</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H66" s="6"/>
+        <v>86</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="I66" s="5">
         <v>46139</v>
       </c>
@@ -5357,13 +5370,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q66" s="5">
         <v>46139</v>
@@ -5375,7 +5388,7 @@
         <v>1</v>
       </c>
       <c r="T66" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="U66" s="11" t="s">
         <v>32</v>
@@ -5383,7 +5396,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B67" s="8">
         <v>46073.71759226852</v>
@@ -5392,18 +5405,20 @@
         <v>46193.607493668984</v>
       </c>
       <c r="D67" s="8">
-        <v>46210.82564222222</v>
+        <v>46223.8241483912</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H67" s="9"/>
+        <v>86</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>86</v>
+      </c>
       <c r="I67" s="8">
         <v>46141</v>
       </c>
@@ -5420,13 +5435,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q67" s="8">
         <v>46141</v>
@@ -5446,7 +5461,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B68" s="5">
         <v>46076.600719699076</v>
@@ -5455,18 +5470,20 @@
         <v>46193.60764289352</v>
       </c>
       <c r="D68" s="5">
-        <v>46210.82564268519</v>
+        <v>46223.82414435185</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H68" s="6"/>
+        <v>86</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="I68" s="5">
         <v>46146</v>
       </c>
@@ -5483,13 +5500,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q68" s="5">
         <v>46146</v>
@@ -5509,7 +5526,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B69" s="8">
         <v>46073.71759252315</v>
@@ -5518,18 +5535,20 @@
         <v>46195.86820241898</v>
       </c>
       <c r="D69" s="8">
-        <v>46195.868219131946</v>
+        <v>46223.824139282406</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H69" s="9"/>
+        <v>86</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>86</v>
+      </c>
       <c r="I69" s="8">
         <v>46157</v>
       </c>
@@ -5546,13 +5565,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q69" s="8">
         <v>46157</v>
@@ -5572,25 +5591,27 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B70" s="5">
         <v>46073.7175927662</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46212.62926046296</v>
+        <v>46223.82413376158</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H70" s="6"/>
+        <v>86</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="I70" s="5">
         <v>46161</v>
       </c>
@@ -5607,13 +5628,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q70" s="5">
         <v>46161</v>
@@ -5628,12 +5649,12 @@
         <v>31</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B71" s="8">
         <v>46073.71759042824</v>
@@ -5643,7 +5664,7 @@
         <v>46091.73446609954</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5667,7 +5688,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5680,7 +5701,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B72" s="5">
         <v>46073.71759075232</v>
@@ -5690,16 +5711,16 @@
         <v>46212.62932537037</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I72" s="5">
         <v>46162</v>
@@ -5717,13 +5738,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q72" s="5">
         <v>46162</v>
@@ -5743,25 +5764,27 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B73" s="8">
         <v>46073.71759101852</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46212.62935025463</v>
+        <v>46223.82419773148</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H73" s="9"/>
+        <v>86</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>86</v>
+      </c>
       <c r="I73" s="8">
         <v>46163</v>
       </c>
@@ -5778,13 +5801,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q73" s="8">
         <v>46163</v>
@@ -5804,7 +5827,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B74" s="5">
         <v>46073.71759130787</v>
@@ -5814,16 +5837,16 @@
         <v>46212.62937076389</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I74" s="5">
         <v>46168</v>
@@ -5841,13 +5864,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q74" s="5">
         <v>46168</v>
@@ -5867,7 +5890,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B75" s="8">
         <v>46073.7175915625</v>
@@ -5877,16 +5900,16 @@
         <v>46212.62939324074</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -5902,13 +5925,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q75" s="8">
         <v>46169</v>
@@ -5928,7 +5951,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B76" s="5">
         <v>46073.71759184028</v>
@@ -5938,7 +5961,7 @@
         <v>46091.73446550926</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5962,7 +5985,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5973,7 +5996,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U76" s="10" t="s">
         <v>56</v>
@@ -5981,7 +6004,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B77" s="8">
         <v>46073.71759210648</v>
@@ -5991,16 +6014,16 @@
         <v>46179.199858576394</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I77" s="8">
         <v>46170</v>
@@ -6018,13 +6041,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q77" s="8">
         <v>46170</v>
@@ -6044,7 +6067,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B78" s="5">
         <v>46073.71759238426</v>
@@ -6054,16 +6077,16 @@
         <v>46179.19985642361</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I78" s="5">
         <v>46170</v>
@@ -6081,13 +6104,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q78" s="5">
         <v>46170</v>
@@ -6107,7 +6130,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B79" s="8">
         <v>46091.72839834491</v>
@@ -6117,7 +6140,7 @@
         <v>46091.73565777778</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6141,7 +6164,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6152,7 +6175,7 @@
         <v>0</v>
       </c>
       <c r="T79" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U79" s="10" t="s">
         <v>56</v>
@@ -6160,7 +6183,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B80" s="5">
         <v>46091.72894082176</v>
@@ -6170,7 +6193,7 @@
         <v>46179.199856562496</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6197,13 +6220,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q80" s="5">
         <v>46170</v>
@@ -6223,7 +6246,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B81" s="8">
         <v>46091.72900166667</v>
@@ -6233,7 +6256,7 @@
         <v>46190.17451866898</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6260,13 +6283,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q81" s="8">
         <v>46181</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="292">
   <si>
     <t xml:space="preserve">50001498-CALABRESSE METRO STO DOMINGO  POZOS  </t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>propuesta Nucleo rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2559,7 +2562,7 @@
         <v>86</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I21" s="8">
         <v>46009</v>
@@ -2583,7 +2586,7 @@
         <v>66</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q21" s="8">
         <v>46009</v>
@@ -2603,7 +2606,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46073.71759302083</v>
@@ -2615,7 +2618,7 @@
         <v>46097.52662200232</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2648,7 +2651,7 @@
         <v>48</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q22" s="5">
         <v>46004</v>
@@ -2668,7 +2671,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="8">
         <v>46076.593357997685</v>
@@ -2680,7 +2683,7 @@
         <v>46114.51047230324</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2713,7 +2716,7 @@
         <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q23" s="8">
         <v>46009</v>
@@ -2733,7 +2736,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5">
         <v>46073.71759033565</v>
@@ -2745,7 +2748,7 @@
         <v>46223.82399125</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2754,7 +2757,7 @@
         <v>86</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I24" s="5">
         <v>46009</v>
@@ -2778,7 +2781,7 @@
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q24" s="5">
         <v>46009</v>
@@ -2798,7 +2801,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B25" s="8">
         <v>46073.71759071759</v>
@@ -2810,7 +2813,7 @@
         <v>46204.69942763889</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2834,7 +2837,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2851,7 +2854,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B26" s="5">
         <v>46073.7175902662</v>
@@ -2863,16 +2866,16 @@
         <v>46155.86710392361</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I26" s="5">
         <v>46006</v>
@@ -2890,13 +2893,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="5">
         <v>46006</v>
@@ -2916,7 +2919,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B27" s="8">
         <v>46073.7175905787</v>
@@ -2928,16 +2931,16 @@
         <v>46097.52605688658</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I27" s="8">
         <v>46006</v>
@@ -2955,13 +2958,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>79</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2969,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U27" s="10" t="s">
         <v>56</v>
@@ -2977,7 +2980,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46073.71759086805</v>
@@ -2989,16 +2992,16 @@
         <v>46155.866878229164</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I28" s="5">
         <v>46027</v>
@@ -3016,13 +3019,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3030,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U28" s="10" t="s">
         <v>56</v>
@@ -3038,7 +3041,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="8">
         <v>46073.71759118055</v>
@@ -3050,16 +3053,16 @@
         <v>46128.63717174769</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I29" s="8">
         <v>46027</v>
@@ -3077,13 +3080,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3091,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U29" s="10" t="s">
         <v>56</v>
@@ -3099,7 +3102,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46073.7175909838</v>
@@ -3111,16 +3114,16 @@
         <v>46155.90358277778</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I30" s="5">
         <v>46013</v>
@@ -3138,13 +3141,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q30" s="5">
         <v>46013</v>
@@ -3164,7 +3167,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" s="8">
         <v>46073.71759126158</v>
@@ -3176,16 +3179,16 @@
         <v>46097.52608802084</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I31" s="8">
         <v>46013</v>
@@ -3203,13 +3206,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>82</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3217,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U31" s="10" t="s">
         <v>56</v>
@@ -3225,7 +3228,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46073.71759153935</v>
@@ -3237,16 +3240,16 @@
         <v>46155.90355751157</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I32" s="5">
         <v>46017</v>
@@ -3264,13 +3267,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3278,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U32" s="10" t="s">
         <v>56</v>
@@ -3286,7 +3289,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B33" s="8">
         <v>46073.717592685185</v>
@@ -3298,16 +3301,16 @@
         <v>46182.683057222224</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I33" s="8">
         <v>46013</v>
@@ -3325,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q33" s="8">
         <v>46013</v>
@@ -3351,7 +3354,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46073.71759302083</v>
@@ -3363,16 +3366,16 @@
         <v>46182.6827475</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I34" s="5">
         <v>46013</v>
@@ -3390,13 +3393,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3404,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U34" s="10" t="s">
         <v>56</v>
@@ -3412,7 +3415,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="8">
         <v>46073.71758986111</v>
@@ -3424,16 +3427,16 @@
         <v>46182.682943541666</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I35" s="8">
         <v>46017</v>
@@ -3451,13 +3454,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3465,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U35" s="10" t="s">
         <v>56</v>
@@ -3473,7 +3476,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B36" s="5">
         <v>46073.7175918287</v>
@@ -3485,16 +3488,16 @@
         <v>46191.89070638889</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I36" s="5">
         <v>46007</v>
@@ -3512,13 +3515,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q36" s="5">
         <v>46007</v>
@@ -3538,7 +3541,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B37" s="8">
         <v>46073.71759209491</v>
@@ -3550,16 +3553,16 @@
         <v>46169.84329747685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I37" s="8">
         <v>46007</v>
@@ -3577,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3591,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U37" s="10" t="s">
         <v>56</v>
@@ -3599,7 +3602,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46073.71759234954</v>
@@ -3609,16 +3612,16 @@
         <v>46191.88833190972</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I38" s="5">
         <v>46017</v>
@@ -3636,13 +3639,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3650,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U38" s="10" t="s">
         <v>56</v>
@@ -3658,7 +3661,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46076.59415034722</v>
@@ -3670,16 +3673,16 @@
         <v>46156.618615775464</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I39" s="8">
         <v>46013</v>
@@ -3697,13 +3700,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q39" s="8">
         <v>46013</v>
@@ -3723,7 +3726,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46076.59428157407</v>
@@ -3735,16 +3738,16 @@
         <v>46154.86737356482</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I40" s="5">
         <v>46013</v>
@@ -3762,13 +3765,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="5">
         <v>46013</v>
@@ -3780,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U40" s="10" t="s">
         <v>56</v>
@@ -3788,7 +3791,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46076.59448399306</v>
@@ -3800,16 +3803,16 @@
         <v>46154.86810545139</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I41" s="8">
         <v>46057</v>
@@ -3827,13 +3830,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="8">
         <v>46057</v>
@@ -3845,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U41" s="10" t="s">
         <v>56</v>
@@ -3853,7 +3856,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46073.71759148148</v>
@@ -3865,16 +3868,16 @@
         <v>46182.53063152778</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I42" s="5">
         <v>46013</v>
@@ -3892,13 +3895,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q42" s="5">
         <v>46013</v>
@@ -3918,7 +3921,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B43" s="8">
         <v>46073.717591759254</v>
@@ -3930,16 +3933,16 @@
         <v>46182.53047055556</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I43" s="8">
         <v>46013</v>
@@ -3957,13 +3960,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3971,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="T43" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U43" s="10" t="s">
         <v>56</v>
@@ -3979,7 +3982,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46073.71759204861</v>
@@ -3991,16 +3994,16 @@
         <v>46182.53060627315</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I44" s="5">
         <v>46037</v>
@@ -4018,13 +4021,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4032,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="T44" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U44" s="10" t="s">
         <v>56</v>
@@ -4040,7 +4043,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B45" s="8">
         <v>46073.71759234954</v>
@@ -4052,7 +4055,7 @@
         <v>46210.531792002315</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4076,7 +4079,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4093,7 +4096,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46073.717592615736</v>
@@ -4105,16 +4108,16 @@
         <v>46154.09504209491</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I46" s="5">
         <v>46009</v>
@@ -4132,13 +4135,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q46" s="5">
         <v>46009</v>
@@ -4158,7 +4161,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46073.71758997685</v>
@@ -4170,16 +4173,16 @@
         <v>46154.09509461805</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I47" s="8">
         <v>46065</v>
@@ -4197,13 +4200,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q47" s="8">
         <v>46065</v>
@@ -4223,7 +4226,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46091.72801988426</v>
@@ -4235,16 +4238,16 @@
         <v>46154.09513386574</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I48" s="5">
         <v>46072</v>
@@ -4262,13 +4265,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q48" s="5">
         <v>46072</v>
@@ -4288,7 +4291,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B49" s="8">
         <v>46091.728057939814</v>
@@ -4300,16 +4303,16 @@
         <v>46210.53201784722</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I49" s="8">
         <v>46160</v>
@@ -4327,13 +4330,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="8">
         <v>46160</v>
@@ -4353,7 +4356,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46073.71759030093</v>
@@ -4365,7 +4368,7 @@
         <v>46191.789304328704</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4389,7 +4392,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4406,7 +4409,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B51" s="8">
         <v>46073.7175905787</v>
@@ -4418,16 +4421,16 @@
         <v>46191.788422488426</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I51" s="8">
         <v>46069</v>
@@ -4445,13 +4448,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="8">
         <v>46069</v>
@@ -4471,7 +4474,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46073.717590810185</v>
@@ -4483,16 +4486,16 @@
         <v>46191.789293194444</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I52" s="5">
         <v>46071</v>
@@ -4510,13 +4513,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="5">
         <v>46071</v>
@@ -4536,7 +4539,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="8">
         <v>46073.717591099536</v>
@@ -4548,7 +4551,7 @@
         <v>46191.79038505787</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4572,7 +4575,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4589,7 +4592,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46073.71759134259</v>
@@ -4601,16 +4604,16 @@
         <v>46191.7899528125</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I54" s="5">
         <v>46073</v>
@@ -4628,13 +4631,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q54" s="5">
         <v>46073</v>
@@ -4654,7 +4657,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B55" s="8">
         <v>46073.71759157407</v>
@@ -4666,16 +4669,16 @@
         <v>46191.790375833334</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I55" s="8">
         <v>46084</v>
@@ -4693,13 +4696,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q55" s="8">
         <v>46084</v>
@@ -4719,7 +4722,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
         <v>46073.71759181713</v>
@@ -4731,16 +4734,16 @@
         <v>46191.79037549769</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I56" s="5">
         <v>46104</v>
@@ -4758,13 +4761,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q56" s="5">
         <v>46104</v>
@@ -4779,12 +4782,12 @@
         <v>31</v>
       </c>
       <c r="U56" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B57" s="8">
         <v>46073.71759206019</v>
@@ -4794,7 +4797,7 @@
         <v>46198.827981574075</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4818,7 +4821,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4831,7 +4834,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B58" s="5">
         <v>46073.71759105324</v>
@@ -4843,16 +4846,16 @@
         <v>46195.60893649305</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I58" s="5">
         <v>46153</v>
@@ -4870,13 +4873,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q58" s="5">
         <v>46153</v>
@@ -4896,7 +4899,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B59" s="8">
         <v>46073.71759083333</v>
@@ -4908,16 +4911,16 @@
         <v>46195.60910890046</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I59" s="8">
         <v>46135</v>
@@ -4935,13 +4938,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q59" s="8">
         <v>46134</v>
@@ -4961,7 +4964,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B60" s="5">
         <v>46073.71759233796</v>
@@ -4973,16 +4976,16 @@
         <v>46198.82799237268</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I60" s="5">
         <v>46071</v>
@@ -5000,13 +5003,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q60" s="5">
         <v>46071</v>
@@ -5026,7 +5029,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B61" s="8">
         <v>46073.71759050926</v>
@@ -5042,10 +5045,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I61" s="8">
         <v>46115</v>
@@ -5063,13 +5066,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q61" s="8">
         <v>46115</v>
@@ -5084,12 +5087,12 @@
         <v>31</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B62" s="5">
         <v>46076.59959273148</v>
@@ -5101,16 +5104,16 @@
         <v>46198.829483009264</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I62" s="5">
         <v>46139</v>
@@ -5128,13 +5131,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q62" s="5">
         <v>46139</v>
@@ -5146,7 +5149,7 @@
         <v>1</v>
       </c>
       <c r="T62" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="U62" s="11" t="s">
         <v>32</v>
@@ -5154,7 +5157,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B63" s="8">
         <v>46073.71759130787</v>
@@ -5164,7 +5167,7 @@
         <v>46195.86820844907</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5188,7 +5191,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5201,7 +5204,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B64" s="5">
         <v>46073.71759155093</v>
@@ -5213,7 +5216,7 @@
         <v>46223.82415971065</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5222,7 +5225,7 @@
         <v>86</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I64" s="5">
         <v>46106</v>
@@ -5240,13 +5243,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q64" s="5">
         <v>46106</v>
@@ -5266,7 +5269,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B65" s="8">
         <v>46073.71759180556</v>
@@ -5278,7 +5281,7 @@
         <v>46223.82415605324</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5287,7 +5290,7 @@
         <v>86</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I65" s="8">
         <v>46155</v>
@@ -5305,13 +5308,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q65" s="8">
         <v>46155</v>
@@ -5331,7 +5334,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B66" s="5">
         <v>46073.717592037036</v>
@@ -5343,7 +5346,7 @@
         <v>46223.824151967594</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5352,7 +5355,7 @@
         <v>86</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I66" s="5">
         <v>46139</v>
@@ -5370,13 +5373,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q66" s="5">
         <v>46139</v>
@@ -5388,7 +5391,7 @@
         <v>1</v>
       </c>
       <c r="T66" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="U66" s="11" t="s">
         <v>32</v>
@@ -5396,7 +5399,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B67" s="8">
         <v>46073.71759226852</v>
@@ -5408,7 +5411,7 @@
         <v>46223.8241483912</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5417,7 +5420,7 @@
         <v>86</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I67" s="8">
         <v>46141</v>
@@ -5435,13 +5438,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q67" s="8">
         <v>46141</v>
@@ -5461,7 +5464,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B68" s="5">
         <v>46076.600719699076</v>
@@ -5473,7 +5476,7 @@
         <v>46223.82414435185</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5482,7 +5485,7 @@
         <v>86</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I68" s="5">
         <v>46146</v>
@@ -5500,13 +5503,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q68" s="5">
         <v>46146</v>
@@ -5526,7 +5529,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B69" s="8">
         <v>46073.71759252315</v>
@@ -5538,7 +5541,7 @@
         <v>46223.824139282406</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5547,7 +5550,7 @@
         <v>86</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I69" s="8">
         <v>46157</v>
@@ -5565,13 +5568,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q69" s="8">
         <v>46157</v>
@@ -5591,7 +5594,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B70" s="5">
         <v>46073.7175927662</v>
@@ -5601,7 +5604,7 @@
         <v>46223.82413376158</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5610,7 +5613,7 @@
         <v>86</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I70" s="5">
         <v>46161</v>
@@ -5628,13 +5631,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q70" s="5">
         <v>46161</v>
@@ -5649,12 +5652,12 @@
         <v>31</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B71" s="8">
         <v>46073.71759042824</v>
@@ -5664,7 +5667,7 @@
         <v>46091.73446609954</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5688,7 +5691,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5701,7 +5704,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B72" s="5">
         <v>46073.71759075232</v>
@@ -5711,16 +5714,16 @@
         <v>46212.62932537037</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I72" s="5">
         <v>46162</v>
@@ -5738,13 +5741,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q72" s="5">
         <v>46162</v>
@@ -5764,7 +5767,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B73" s="8">
         <v>46073.71759101852</v>
@@ -5774,7 +5777,7 @@
         <v>46223.82419773148</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5783,7 +5786,7 @@
         <v>86</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I73" s="8">
         <v>46163</v>
@@ -5801,13 +5804,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q73" s="8">
         <v>46163</v>
@@ -5827,7 +5830,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B74" s="5">
         <v>46073.71759130787</v>
@@ -5837,16 +5840,16 @@
         <v>46212.62937076389</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I74" s="5">
         <v>46168</v>
@@ -5864,13 +5867,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q74" s="5">
         <v>46168</v>
@@ -5890,7 +5893,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B75" s="8">
         <v>46073.7175915625</v>
@@ -5900,16 +5903,16 @@
         <v>46212.62939324074</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -5925,13 +5928,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q75" s="8">
         <v>46169</v>
@@ -5951,7 +5954,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B76" s="5">
         <v>46073.71759184028</v>
@@ -5961,7 +5964,7 @@
         <v>46091.73446550926</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5985,7 +5988,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5996,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U76" s="10" t="s">
         <v>56</v>
@@ -6004,7 +6007,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B77" s="8">
         <v>46073.71759210648</v>
@@ -6014,16 +6017,16 @@
         <v>46179.199858576394</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I77" s="8">
         <v>46170</v>
@@ -6041,13 +6044,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q77" s="8">
         <v>46170</v>
@@ -6067,7 +6070,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B78" s="5">
         <v>46073.71759238426</v>
@@ -6077,16 +6080,16 @@
         <v>46179.19985642361</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I78" s="5">
         <v>46170</v>
@@ -6104,13 +6107,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q78" s="5">
         <v>46170</v>
@@ -6130,7 +6133,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B79" s="8">
         <v>46091.72839834491</v>
@@ -6140,7 +6143,7 @@
         <v>46091.73565777778</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6164,7 +6167,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6175,7 +6178,7 @@
         <v>0</v>
       </c>
       <c r="T79" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U79" s="10" t="s">
         <v>56</v>
@@ -6183,7 +6186,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B80" s="5">
         <v>46091.72894082176</v>
@@ -6193,7 +6196,7 @@
         <v>46179.199856562496</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6220,13 +6223,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q80" s="5">
         <v>46170</v>
@@ -6246,7 +6249,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B81" s="8">
         <v>46091.72900166667</v>
@@ -6256,7 +6259,7 @@
         <v>46190.17451866898</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6283,13 +6286,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q81" s="8">
         <v>46181</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="294">
   <si>
     <t xml:space="preserve">50001498-CALABRESSE METRO STO DOMINGO  POZOS  </t>
   </si>
@@ -775,6 +775,18 @@
     <t>Montaje:,4200-4201Coordinacion Entrega con Cliente</t>
   </si>
   <si>
+    <t>1217113716777447</t>
+  </si>
+  <si>
+    <t>MONTAJE DAMPER INOX</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
     <t>1213380471139143</t>
   </si>
   <si>
@@ -815,12 +827,6 @@
   </si>
   <si>
     <t>4200-4201 PACKING LIST</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
     <t>4200-4201 Despacho,Logistica:</t>
@@ -1410,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U81"/>
+  <dimension ref="A1:U82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -5164,7 +5170,7 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.86820844907</v>
+        <v>46237.553995243055</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>231</v>
@@ -5200,7 +5206,9 @@
       <c r="R63" s="9"/>
       <c r="S63" s="9"/>
       <c r="T63" s="9"/>
-      <c r="U63" s="9"/>
+      <c r="U63" s="12" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
@@ -5599,9 +5607,11 @@
       <c r="B70" s="5">
         <v>46073.7175927662</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46237.55397583333</v>
+      </c>
       <c r="D70" s="5">
-        <v>46223.82413376158</v>
+        <v>46237.55399104167</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>183</v>
@@ -5646,13 +5656,13 @@
         <v>46161</v>
       </c>
       <c r="S70" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U70" s="12" t="s">
-        <v>212</v>
+      <c r="U70" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5660,22 +5670,24 @@
         <v>254</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.71759042824</v>
+        <v>46237.53415582176</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46091.73446609954</v>
+        <v>46237.53470668981</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>255</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H71" s="9"/>
+        <v>256</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>257</v>
+      </c>
       <c r="I71" s="9"/>
       <c r="J71" s="9"/>
       <c r="K71" s="9" t="s">
@@ -5685,114 +5697,106 @@
         <v>26</v>
       </c>
       <c r="M71" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>26</v>
+        <v>231</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>256</v>
+        <v>26</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="Q71" s="9"/>
+      <c r="Q71" s="8">
+        <v>46216</v>
+      </c>
       <c r="R71" s="9"/>
-      <c r="S71" s="9"/>
-      <c r="T71" s="9"/>
-      <c r="U71" s="9"/>
+      <c r="S71" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="T71" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="U71" s="12" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.71759075232</v>
+        <v>46073.71759042824</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46212.62932537037</v>
+        <v>46237.553960046294</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="H72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O72" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="I72" s="5">
-        <v>46162</v>
-      </c>
-      <c r="J72" s="5">
-        <v>46162</v>
-      </c>
-      <c r="K72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N72" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="O72" s="6" t="s">
-        <v>183</v>
-      </c>
       <c r="P72" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q72" s="5">
-        <v>46162</v>
-      </c>
-      <c r="R72" s="5">
-        <v>46162</v>
-      </c>
-      <c r="S72" s="6">
-        <v>0</v>
-      </c>
-      <c r="T72" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U72" s="10" t="s">
-        <v>56</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q72" s="6"/>
+      <c r="R72" s="6"/>
+      <c r="S72" s="6"/>
+      <c r="T72" s="6"/>
+      <c r="U72" s="6"/>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.71759101852</v>
+        <v>46073.71759075232</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46223.82419773148</v>
+        <v>46237.553996331015</v>
       </c>
       <c r="E73" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="F73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>86</v>
-      </c>
       <c r="H73" s="9" t="s">
-        <v>87</v>
+        <v>264</v>
       </c>
       <c r="I73" s="8">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="J73" s="8">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="K73" s="9" t="s">
         <v>26</v>
@@ -5804,19 +5808,19 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>264</v>
+        <v>183</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>265</v>
       </c>
       <c r="Q73" s="8">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="R73" s="8">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="S73" s="9">
         <v>0</v>
@@ -5824,8 +5828,8 @@
       <c r="T73" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U73" s="10" t="s">
-        <v>56</v>
+      <c r="U73" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5833,11 +5837,13 @@
         <v>266</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.71759130787</v>
-      </c>
-      <c r="C74" s="6"/>
+        <v>46073.71759101852</v>
+      </c>
+      <c r="C74" s="5">
+        <v>46237.553950601854</v>
+      </c>
       <c r="D74" s="5">
-        <v>46212.62937076389</v>
+        <v>46237.553970810186</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>267</v>
@@ -5846,77 +5852,79 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="I74" s="5">
+        <v>46163</v>
+      </c>
+      <c r="J74" s="5">
+        <v>46167</v>
+      </c>
+      <c r="K74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="O74" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="H74" s="6" t="s">
+      <c r="P74" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="I74" s="5">
-        <v>46168</v>
-      </c>
-      <c r="J74" s="5">
-        <v>46168</v>
-      </c>
-      <c r="K74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N74" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="O74" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>270</v>
-      </c>
       <c r="Q74" s="5">
-        <v>46168</v>
+        <v>46163</v>
       </c>
       <c r="R74" s="5">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="S74" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U74" s="10" t="s">
-        <v>56</v>
+      <c r="U74" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.7175915625</v>
+        <v>46073.71759130787</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46212.62939324074</v>
+        <v>46237.55396895834</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="I75" s="9"/>
+        <v>257</v>
+      </c>
+      <c r="I75" s="8">
+        <v>46168</v>
+      </c>
       <c r="J75" s="8">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="K75" s="9" t="s">
         <v>26</v>
@@ -5928,19 +5936,19 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="O75" s="9" t="s">
         <v>267</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q75" s="8">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="R75" s="8">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="S75" s="9">
         <v>0</v>
@@ -5948,58 +5956,66 @@
       <c r="T75" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U75" s="10" t="s">
-        <v>56</v>
+      <c r="U75" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.71759184028</v>
+        <v>46073.7175915625</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46091.73446550926</v>
+        <v>46212.62939324074</v>
       </c>
       <c r="E76" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="I76" s="6"/>
+      <c r="J76" s="5">
+        <v>46169</v>
+      </c>
+      <c r="K76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N76" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="O76" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="F76" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
-      <c r="K76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M76" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O76" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="6"/>
+      <c r="Q76" s="5">
+        <v>46169</v>
+      </c>
+      <c r="R76" s="5">
+        <v>46169</v>
+      </c>
       <c r="S76" s="6">
         <v>0</v>
       </c>
-      <c r="T76" s="11" t="s">
-        <v>109</v>
+      <c r="T76" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U76" s="10" t="s">
         <v>56</v>
@@ -6007,62 +6023,52 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.71759210648</v>
+        <v>46073.71759184028</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46179.199858576394</v>
+        <v>46091.73446550926</v>
       </c>
       <c r="E77" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H77" s="9"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
+      <c r="K77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M77" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O77" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="F77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="I77" s="8">
-        <v>46170</v>
-      </c>
-      <c r="J77" s="8">
-        <v>46178</v>
-      </c>
-      <c r="K77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N77" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="O77" s="9" t="s">
-        <v>272</v>
-      </c>
       <c r="P77" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q77" s="8">
-        <v>46170</v>
-      </c>
-      <c r="R77" s="8">
-        <v>46178</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q77" s="9"/>
+      <c r="R77" s="9"/>
       <c r="S77" s="9">
         <v>0</v>
       </c>
-      <c r="T77" s="10" t="s">
-        <v>31</v>
+      <c r="T77" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="U77" s="10" t="s">
         <v>56</v>
@@ -6070,26 +6076,26 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.71759238426</v>
+        <v>46073.71759210648</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46179.19985642361</v>
+        <v>46179.199858576394</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>280</v>
       </c>
       <c r="I78" s="5">
         <v>46170</v>
@@ -6107,13 +6113,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q78" s="5">
         <v>46170</v>
@@ -6133,52 +6139,62 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B79" s="8">
-        <v>46091.72839834491</v>
+        <v>46073.71759238426</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46091.73565777778</v>
+        <v>46179.19985642361</v>
       </c>
       <c r="E79" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="I79" s="8">
+        <v>46170</v>
+      </c>
+      <c r="J79" s="8">
+        <v>46178</v>
+      </c>
+      <c r="K79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N79" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="O79" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="F79" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="9"/>
-      <c r="I79" s="9"/>
-      <c r="J79" s="9"/>
-      <c r="K79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M79" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O79" s="9" t="s">
-        <v>286</v>
-      </c>
       <c r="P79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q79" s="9"/>
-      <c r="R79" s="9"/>
+        <v>277</v>
+      </c>
+      <c r="Q79" s="8">
+        <v>46170</v>
+      </c>
+      <c r="R79" s="8">
+        <v>46178</v>
+      </c>
       <c r="S79" s="9">
         <v>0</v>
       </c>
-      <c r="T79" s="11" t="s">
-        <v>109</v>
+      <c r="T79" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U79" s="10" t="s">
         <v>56</v>
@@ -6186,62 +6202,52 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B80" s="5">
-        <v>46091.72894082176</v>
+        <v>46091.72839834491</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46179.199856562496</v>
+        <v>46091.73565777778</v>
       </c>
       <c r="E80" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
+      <c r="K80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O80" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="F80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I80" s="5">
-        <v>46170</v>
-      </c>
-      <c r="J80" s="5">
-        <v>46178</v>
-      </c>
-      <c r="K80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N80" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>272</v>
-      </c>
       <c r="P80" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q80" s="5">
-        <v>46170</v>
-      </c>
-      <c r="R80" s="5">
-        <v>46178</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q80" s="6"/>
+      <c r="R80" s="6"/>
       <c r="S80" s="6">
         <v>0</v>
       </c>
-      <c r="T80" s="10" t="s">
-        <v>31</v>
+      <c r="T80" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="U80" s="10" t="s">
         <v>56</v>
@@ -6249,17 +6255,17 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B81" s="8">
-        <v>46091.72900166667</v>
+        <v>46091.72894082176</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46190.17451866898</v>
+        <v>46179.199856562496</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6271,10 +6277,10 @@
         <v>50</v>
       </c>
       <c r="I81" s="8">
-        <v>46181</v>
+        <v>46170</v>
       </c>
       <c r="J81" s="8">
-        <v>46189</v>
+        <v>46178</v>
       </c>
       <c r="K81" s="9" t="s">
         <v>26</v>
@@ -6286,19 +6292,19 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="Q81" s="8">
-        <v>46181</v>
+        <v>46170</v>
       </c>
       <c r="R81" s="8">
-        <v>46189</v>
+        <v>46178</v>
       </c>
       <c r="S81" s="9">
         <v>0</v>
@@ -6307,6 +6313,69 @@
         <v>31</v>
       </c>
       <c r="U81" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B82" s="5">
+        <v>46091.72900166667</v>
+      </c>
+      <c r="C82" s="6"/>
+      <c r="D82" s="5">
+        <v>46190.17451866898</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I82" s="5">
+        <v>46181</v>
+      </c>
+      <c r="J82" s="5">
+        <v>46189</v>
+      </c>
+      <c r="K82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="P82" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q82" s="5">
+        <v>46181</v>
+      </c>
+      <c r="R82" s="5">
+        <v>46189</v>
+      </c>
+      <c r="S82" s="6">
+        <v>0</v>
+      </c>
+      <c r="T82" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="U82" s="10" t="s">
         <v>56</v>
       </c>
     </row>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="286">
   <si>
     <t xml:space="preserve">50001498-CALABRESSE METRO STO DOMINGO  POZOS  </t>
   </si>
@@ -838,7 +838,7 @@
     <t>4200-4201 Despacho</t>
   </si>
   <si>
-    <t>Gestion,Costos,Logistica:,Instalación componentes</t>
+    <t>Gestion,Costos,Logistica:</t>
   </si>
   <si>
     <t>1213380471139148</t>
@@ -869,30 +869,6 @@
   </si>
   <si>
     <t>4200-4201 Despacho,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213595645393448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puesta en Marcha </t>
-  </si>
-  <si>
-    <t>Instalación componentes,Pruebas instalacion componentes</t>
-  </si>
-  <si>
-    <t>1213595645393450</t>
-  </si>
-  <si>
-    <t>Instalación componentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruebas instalacion componentes,Puesta en Marcha </t>
-  </si>
-  <si>
-    <t>1213595645393452</t>
-  </si>
-  <si>
-    <t>Pruebas instalacion componentes</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U82"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -5969,7 +5945,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46212.62939324074</v>
+        <v>46240.72145917824</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>274</v>
@@ -6197,185 +6173,6 @@
         <v>31</v>
       </c>
       <c r="U79" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="B80" s="5">
-        <v>46091.72839834491</v>
-      </c>
-      <c r="C80" s="6"/>
-      <c r="D80" s="5">
-        <v>46091.73565777778</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="6"/>
-      <c r="K80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M80" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q80" s="6"/>
-      <c r="R80" s="6"/>
-      <c r="S80" s="6">
-        <v>0</v>
-      </c>
-      <c r="T80" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="U80" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B81" s="8">
-        <v>46091.72894082176</v>
-      </c>
-      <c r="C81" s="9"/>
-      <c r="D81" s="8">
-        <v>46179.199856562496</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I81" s="8">
-        <v>46170</v>
-      </c>
-      <c r="J81" s="8">
-        <v>46178</v>
-      </c>
-      <c r="K81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N81" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="O81" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="P81" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q81" s="8">
-        <v>46170</v>
-      </c>
-      <c r="R81" s="8">
-        <v>46178</v>
-      </c>
-      <c r="S81" s="9">
-        <v>0</v>
-      </c>
-      <c r="T81" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U81" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="B82" s="5">
-        <v>46091.72900166667</v>
-      </c>
-      <c r="C82" s="6"/>
-      <c r="D82" s="5">
-        <v>46190.17451866898</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="F82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I82" s="5">
-        <v>46181</v>
-      </c>
-      <c r="J82" s="5">
-        <v>46189</v>
-      </c>
-      <c r="K82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N82" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q82" s="5">
-        <v>46181</v>
-      </c>
-      <c r="R82" s="5">
-        <v>46189</v>
-      </c>
-      <c r="S82" s="6">
-        <v>0</v>
-      </c>
-      <c r="T82" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="U82" s="10" t="s">
         <v>56</v>
       </c>
     </row>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="286">
   <si>
     <t xml:space="preserve">50001498-CALABRESSE METRO STO DOMINGO  POZOS  </t>
   </si>
@@ -181,166 +181,166 @@
     <t>Ingenieria Servicios:,4200-4201 Embalaje</t>
   </si>
   <si>
+    <t>1213333303431785</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete,Analisis de costeo</t>
+  </si>
+  <si>
+    <t>1213333303431786</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor</t>
+  </si>
+  <si>
+    <t>Carlos Pérez</t>
+  </si>
+  <si>
+    <t>cperez@zitron.com</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
+  </si>
+  <si>
+    <t>1213333303431788</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta Nucleo rodete,propuesta alabes</t>
+  </si>
+  <si>
+    <t>1213333303431789</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,Propuesta Sensores ,propuesta compras a codigo // aprovisionamiento 4200,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>1213333303431790</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Costos</t>
+  </si>
+  <si>
+    <t>1213333303431791</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">propuesta Nucleo rodete,propuesta alabes,propuesta motor,propuesta tableros,propuesta compras a codigo // aprovisionamiento 4200,Propuesta Sensores </t>
+  </si>
+  <si>
+    <t>1213333303431793</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC motor</t>
+  </si>
+  <si>
+    <t>1213333303431792</t>
+  </si>
+  <si>
+    <t>propuesta alabes</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe</t>
+  </si>
+  <si>
+    <t>1213380470331412</t>
+  </si>
+  <si>
+    <t>propuesta Nucleo rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete OT 4200</t>
+  </si>
+  <si>
+    <t>1213380470331411</t>
+  </si>
+  <si>
+    <t>propuesta tableros</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Tableros ot 4201</t>
+  </si>
+  <si>
+    <t>1213402049403976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Sensores </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta compras:,Generación OC Sensores </t>
+  </si>
+  <si>
+    <t>1213380470331413</t>
+  </si>
+  <si>
+    <t>propuesta compras a codigo // aprovisionamiento 4200</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales OT 4200</t>
+  </si>
+  <si>
+    <t>1213380470331414</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Alabe,Tablero OT 4201,rodete OT 4200,Motor,Sensores,Materiales a codigo // compras locales aprovisionamientomiento:OT  4200</t>
+  </si>
+  <si>
+    <t>1213380470331424</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC motor,Fabricación motor,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>1213380470331425</t>
+  </si>
+  <si>
+    <t>Generación OC motor</t>
+  </si>
+  <si>
+    <t>Fabricación motor,Planos motor proveedor,Motor</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1213333303431785</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213333303431786</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor</t>
-  </si>
-  <si>
-    <t>Carlos Pérez</t>
-  </si>
-  <si>
-    <t>cperez@zitron.com</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
-  </si>
-  <si>
-    <t>1213333303431788</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta Nucleo rodete,propuesta alabes</t>
-  </si>
-  <si>
-    <t>1213333303431789</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,Propuesta Sensores ,propuesta compras a codigo // aprovisionamiento 4200,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1213333303431790</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>1213333303431791</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">propuesta Nucleo rodete,propuesta alabes,propuesta motor,propuesta tableros,propuesta compras a codigo // aprovisionamiento 4200,Propuesta Sensores </t>
-  </si>
-  <si>
-    <t>1213333303431793</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC motor</t>
-  </si>
-  <si>
-    <t>1213333303431792</t>
-  </si>
-  <si>
-    <t>propuesta alabes</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe</t>
-  </si>
-  <si>
-    <t>1213380470331412</t>
-  </si>
-  <si>
-    <t>propuesta Nucleo rodete</t>
-  </si>
-  <si>
-    <t>NATALYA ESPINOZA</t>
-  </si>
-  <si>
-    <t>nespinoza@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete OT 4200</t>
-  </si>
-  <si>
-    <t>1213380470331411</t>
-  </si>
-  <si>
-    <t>propuesta tableros</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Tableros ot 4201</t>
-  </si>
-  <si>
-    <t>1213402049403976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Sensores </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta compras:,Generación OC Sensores </t>
-  </si>
-  <si>
-    <t>1213380470331413</t>
-  </si>
-  <si>
-    <t>propuesta compras a codigo // aprovisionamiento 4200</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales OT 4200</t>
-  </si>
-  <si>
-    <t>1213380470331414</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Alabe,Tablero OT 4201,rodete OT 4200,Motor,Sensores,Materiales a codigo // compras locales aprovisionamientomiento:OT  4200</t>
-  </si>
-  <si>
-    <t>1213380470331424</t>
-  </si>
-  <si>
-    <t>Motor</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC motor,Fabricación motor,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>1213380470331425</t>
-  </si>
-  <si>
-    <t>Generación OC motor</t>
-  </si>
-  <si>
-    <t>Fabricación motor,Planos motor proveedor,Motor</t>
-  </si>
-  <si>
-    <t>Baja</t>
   </si>
   <si>
     <t>1213380470331426</t>
@@ -1865,9 +1865,11 @@
       <c r="B10" s="5">
         <v>46073.71759215278</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46245.76911814815</v>
+      </c>
       <c r="D10" s="5">
-        <v>46097.5263790625</v>
+        <v>46245.769130659726</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1901,9 +1903,13 @@
       </c>
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
+      <c r="S10" s="6">
+        <v>1</v>
+      </c>
       <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
+      <c r="U10" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
@@ -1977,9 +1983,11 @@
       <c r="B12" s="5">
         <v>46073.71759273148</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46245.76910020833</v>
+      </c>
       <c r="D12" s="5">
-        <v>46126.19500706019</v>
+        <v>46245.76911736111</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2024,18 +2032,18 @@
         <v>46125</v>
       </c>
       <c r="S12" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U12" s="10" t="s">
-        <v>56</v>
+      <c r="U12" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B13" s="8">
         <v>46073.71759298611</v>
@@ -2047,7 +2055,7 @@
         <v>46169.884381701384</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2071,7 +2079,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2084,7 +2092,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" s="5">
         <v>46073.71759060185</v>
@@ -2096,16 +2104,16 @@
         <v>46100.761380717595</v>
       </c>
       <c r="E14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="6" t="s">
+      <c r="H14" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="I14" s="5">
         <v>46000</v>
@@ -2123,13 +2131,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q14" s="5">
         <v>46000</v>
@@ -2149,7 +2157,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" s="8">
         <v>46073.71759128472</v>
@@ -2161,16 +2169,16 @@
         <v>46114.50880758102</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="I15" s="8">
         <v>46000</v>
@@ -2188,13 +2196,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>40</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q15" s="8">
         <v>46000</v>
@@ -2214,7 +2222,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B16" s="5">
         <v>46073.71759157407</v>
@@ -2226,16 +2234,16 @@
         <v>46114.509243865745</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="I16" s="5">
         <v>46000</v>
@@ -2253,13 +2261,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q16" s="5">
         <v>46000</v>
@@ -2279,7 +2287,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B17" s="8">
         <v>46073.71759186343</v>
@@ -2291,16 +2299,16 @@
         <v>46114.51026347222</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H17" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="I17" s="8">
         <v>46000</v>
@@ -2318,13 +2326,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O17" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="P17" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>74</v>
       </c>
       <c r="Q17" s="8">
         <v>46000</v>
@@ -2344,7 +2352,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="5">
         <v>46073.717592141205</v>
@@ -2356,7 +2364,7 @@
         <v>46169.88433502315</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>25</v>
@@ -2380,7 +2388,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>26</v>
@@ -2393,7 +2401,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B19" s="8">
         <v>46073.71759269676</v>
@@ -2405,16 +2413,16 @@
         <v>46156.61850119213</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H19" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="I19" s="8">
         <v>46002</v>
@@ -2432,13 +2440,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q19" s="8">
         <v>46002</v>
@@ -2458,7 +2466,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B20" s="5">
         <v>46073.71759241898</v>
@@ -2470,16 +2478,16 @@
         <v>46156.61851966435</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="I20" s="5">
         <v>46009</v>
@@ -2497,13 +2505,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q20" s="5">
         <v>46009</v>
@@ -2523,7 +2531,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B21" s="8">
         <v>46073.717593298614</v>
@@ -2535,16 +2543,16 @@
         <v>46223.823994606486</v>
       </c>
       <c r="E21" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="9" t="s">
+      <c r="H21" s="9" t="s">
         <v>86</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>87</v>
       </c>
       <c r="I21" s="8">
         <v>46009</v>
@@ -2562,13 +2570,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q21" s="8">
         <v>46009</v>
@@ -2588,7 +2596,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5">
         <v>46073.71759302083</v>
@@ -2600,16 +2608,16 @@
         <v>46097.52662200232</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="I22" s="5">
         <v>46004</v>
@@ -2627,13 +2635,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>48</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q22" s="5">
         <v>46004</v>
@@ -2653,7 +2661,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B23" s="8">
         <v>46076.593357997685</v>
@@ -2665,16 +2673,16 @@
         <v>46114.51047230324</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>63</v>
       </c>
       <c r="I23" s="8">
         <v>46009</v>
@@ -2692,13 +2700,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="8">
         <v>46009</v>
@@ -2718,7 +2726,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B24" s="5">
         <v>46073.71759033565</v>
@@ -2730,16 +2738,16 @@
         <v>46223.82399125</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>87</v>
       </c>
       <c r="I24" s="5">
         <v>46009</v>
@@ -2757,13 +2765,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q24" s="5">
         <v>46009</v>
@@ -2783,7 +2791,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B25" s="8">
         <v>46073.71759071759</v>
@@ -2795,7 +2803,7 @@
         <v>46204.69942763889</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2819,7 +2827,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2836,7 +2844,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B26" s="5">
         <v>46073.7175902662</v>
@@ -2848,16 +2856,16 @@
         <v>46155.86710392361</v>
       </c>
       <c r="E26" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I26" s="5">
         <v>46006</v>
@@ -2875,13 +2883,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q26" s="5">
         <v>46006</v>
@@ -2901,7 +2909,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B27" s="8">
         <v>46073.7175905787</v>
@@ -2913,16 +2921,16 @@
         <v>46097.52605688658</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="I27" s="8">
         <v>46006</v>
@@ -2940,13 +2948,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2954,10 +2962,10 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="U27" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="U27" s="10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -2980,10 +2988,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I28" s="5">
         <v>46027</v>
@@ -3001,10 +3009,10 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>112</v>
@@ -3015,10 +3023,10 @@
         <v>0</v>
       </c>
       <c r="T28" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="U28" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="U28" s="10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3041,10 +3049,10 @@
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="I29" s="8">
         <v>46027</v>
@@ -3062,10 +3070,10 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>115</v>
@@ -3076,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="U29" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="U29" s="10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3102,10 +3110,10 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I30" s="5">
         <v>46013</v>
@@ -3123,13 +3131,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>118</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q30" s="5">
         <v>46013</v>
@@ -3167,10 +3175,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="I31" s="8">
         <v>46013</v>
@@ -3191,7 +3199,7 @@
         <v>117</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>121</v>
@@ -3202,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="T31" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="U31" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="U31" s="10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3228,10 +3236,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I32" s="5">
         <v>46017</v>
@@ -3263,10 +3271,10 @@
         <v>0</v>
       </c>
       <c r="T32" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="U32" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="U32" s="10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3289,10 +3297,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="I33" s="8">
         <v>46013</v>
@@ -3310,13 +3318,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>127</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q33" s="8">
         <v>46013</v>
@@ -3354,10 +3362,10 @@
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I34" s="5">
         <v>46013</v>
@@ -3378,7 +3386,7 @@
         <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>130</v>
@@ -3389,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="U34" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="U34" s="10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3415,10 +3423,10 @@
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="I35" s="8">
         <v>46017</v>
@@ -3450,10 +3458,10 @@
         <v>0</v>
       </c>
       <c r="T35" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="U35" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="U35" s="10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3476,10 +3484,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I36" s="5">
         <v>46007</v>
@@ -3497,13 +3505,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>136</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q36" s="5">
         <v>46007</v>
@@ -3541,10 +3549,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="I37" s="8">
         <v>46007</v>
@@ -3565,7 +3573,7 @@
         <v>135</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P37" s="9" t="s">
         <v>139</v>
@@ -3576,10 +3584,10 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="U37" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="U37" s="10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -3600,10 +3608,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="I38" s="5">
         <v>46017</v>
@@ -3635,10 +3643,10 @@
         <v>0</v>
       </c>
       <c r="T38" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="U38" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="U38" s="10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -3682,13 +3690,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>147</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q39" s="8">
         <v>46013</v>
@@ -3750,7 +3758,7 @@
         <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>150</v>
@@ -3765,10 +3773,10 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="U40" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="U40" s="10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -3830,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="T41" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="U41" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="U41" s="10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -3877,13 +3885,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>156</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q42" s="5">
         <v>46013</v>
@@ -3945,7 +3953,7 @@
         <v>155</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>159</v>
@@ -3956,10 +3964,10 @@
         <v>0</v>
       </c>
       <c r="T43" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="U43" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="U43" s="10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4017,10 +4025,10 @@
         <v>0</v>
       </c>
       <c r="T44" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="U44" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="U44" s="10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4120,7 +4128,7 @@
         <v>164</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>170</v>
@@ -5206,10 +5214,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>87</v>
       </c>
       <c r="I64" s="5">
         <v>46106</v>
@@ -5271,10 +5279,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>86</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>87</v>
       </c>
       <c r="I65" s="8">
         <v>46155</v>
@@ -5336,10 +5344,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>87</v>
       </c>
       <c r="I66" s="5">
         <v>46139</v>
@@ -5401,10 +5409,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>86</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>87</v>
       </c>
       <c r="I67" s="8">
         <v>46141</v>
@@ -5466,10 +5474,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>87</v>
       </c>
       <c r="I68" s="5">
         <v>46146</v>
@@ -5531,10 +5539,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>86</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>87</v>
       </c>
       <c r="I69" s="8">
         <v>46157</v>
@@ -5596,10 +5604,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>87</v>
       </c>
       <c r="I70" s="5">
         <v>46161</v>
@@ -5819,7 +5827,7 @@
         <v>46237.553950601854</v>
       </c>
       <c r="D74" s="5">
-        <v>46237.553970810186</v>
+        <v>46245.76911054398</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>267</v>
@@ -5828,10 +5836,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>87</v>
       </c>
       <c r="I74" s="5">
         <v>46163</v>
@@ -5994,7 +6002,7 @@
         <v>31</v>
       </c>
       <c r="U76" s="10" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6044,10 +6052,10 @@
         <v>0</v>
       </c>
       <c r="T77" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="U77" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="U77" s="10" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6110,7 +6118,7 @@
         <v>31</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6173,7 +6181,7 @@
         <v>31</v>
       </c>
       <c r="U79" s="10" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="286">
   <si>
     <t xml:space="preserve">50001498-CALABRESSE METRO STO DOMINGO  POZOS  </t>
   </si>
@@ -181,6 +181,9 @@
     <t>Ingenieria Servicios:,4200-4201 Embalaje</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1213333303431785</t>
   </si>
   <si>
@@ -647,9 +650,6 @@
   </si>
   <si>
     <t>Fabricación externa ,Revestimiento</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213380470331441</t>
@@ -1987,7 +1987,7 @@
         <v>46245.76910020833</v>
       </c>
       <c r="D12" s="5">
-        <v>46245.76911736111</v>
+        <v>46246.8105005324</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2037,13 +2037,13 @@
       <c r="T12" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U12" s="11" t="s">
-        <v>32</v>
+      <c r="U12" s="12" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B13" s="8">
         <v>46073.71759298611</v>
@@ -2055,7 +2055,7 @@
         <v>46169.884381701384</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2079,7 +2079,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2092,7 +2092,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="5">
         <v>46073.71759060185</v>
@@ -2104,16 +2104,16 @@
         <v>46100.761380717595</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I14" s="5">
         <v>46000</v>
@@ -2131,13 +2131,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q14" s="5">
         <v>46000</v>
@@ -2157,7 +2157,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" s="8">
         <v>46073.71759128472</v>
@@ -2169,16 +2169,16 @@
         <v>46114.50880758102</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I15" s="8">
         <v>46000</v>
@@ -2196,13 +2196,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>40</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q15" s="8">
         <v>46000</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16" s="5">
         <v>46073.71759157407</v>
@@ -2234,16 +2234,16 @@
         <v>46114.509243865745</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I16" s="5">
         <v>46000</v>
@@ -2261,13 +2261,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="5">
         <v>46000</v>
@@ -2287,7 +2287,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" s="8">
         <v>46073.71759186343</v>
@@ -2299,16 +2299,16 @@
         <v>46114.51026347222</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I17" s="8">
         <v>46000</v>
@@ -2326,13 +2326,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="8">
         <v>46000</v>
@@ -2352,7 +2352,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="5">
         <v>46073.717592141205</v>
@@ -2364,7 +2364,7 @@
         <v>46169.88433502315</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>25</v>
@@ -2388,7 +2388,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>26</v>
@@ -2401,7 +2401,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B19" s="8">
         <v>46073.71759269676</v>
@@ -2413,16 +2413,16 @@
         <v>46156.61850119213</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I19" s="8">
         <v>46002</v>
@@ -2440,13 +2440,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q19" s="8">
         <v>46002</v>
@@ -2466,7 +2466,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B20" s="5">
         <v>46073.71759241898</v>
@@ -2478,16 +2478,16 @@
         <v>46156.61851966435</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I20" s="5">
         <v>46009</v>
@@ -2505,13 +2505,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q20" s="5">
         <v>46009</v>
@@ -2531,7 +2531,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" s="8">
         <v>46073.717593298614</v>
@@ -2543,16 +2543,16 @@
         <v>46223.823994606486</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I21" s="8">
         <v>46009</v>
@@ -2570,13 +2570,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q21" s="8">
         <v>46009</v>
@@ -2596,7 +2596,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46073.71759302083</v>
@@ -2608,16 +2608,16 @@
         <v>46097.52662200232</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I22" s="5">
         <v>46004</v>
@@ -2635,13 +2635,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>48</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q22" s="5">
         <v>46004</v>
@@ -2661,7 +2661,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="8">
         <v>46076.593357997685</v>
@@ -2673,16 +2673,16 @@
         <v>46114.51047230324</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I23" s="8">
         <v>46009</v>
@@ -2700,13 +2700,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q23" s="8">
         <v>46009</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5">
         <v>46073.71759033565</v>
@@ -2738,16 +2738,16 @@
         <v>46223.82399125</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I24" s="5">
         <v>46009</v>
@@ -2765,13 +2765,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q24" s="5">
         <v>46009</v>
@@ -2791,7 +2791,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B25" s="8">
         <v>46073.71759071759</v>
@@ -2803,7 +2803,7 @@
         <v>46204.69942763889</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2827,7 +2827,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B26" s="5">
         <v>46073.7175902662</v>
@@ -2856,16 +2856,16 @@
         <v>46155.86710392361</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I26" s="5">
         <v>46006</v>
@@ -2883,13 +2883,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="5">
         <v>46006</v>
@@ -2909,7 +2909,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B27" s="8">
         <v>46073.7175905787</v>
@@ -2921,16 +2921,16 @@
         <v>46097.52605688658</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I27" s="8">
         <v>46006</v>
@@ -2948,13 +2948,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2962,15 +2962,15 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46073.71759086805</v>
@@ -2982,16 +2982,16 @@
         <v>46155.866878229164</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I28" s="5">
         <v>46027</v>
@@ -3009,13 +3009,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3023,15 +3023,15 @@
         <v>0</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46073.71759118055</v>
@@ -3043,16 +3043,16 @@
         <v>46128.63717174769</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I29" s="8">
         <v>46027</v>
@@ -3070,13 +3070,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3084,15 +3084,15 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46073.7175909838</v>
@@ -3104,16 +3104,16 @@
         <v>46155.90358277778</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I30" s="5">
         <v>46013</v>
@@ -3131,13 +3131,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q30" s="5">
         <v>46013</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B31" s="8">
         <v>46073.71759126158</v>
@@ -3169,16 +3169,16 @@
         <v>46097.52608802084</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I31" s="8">
         <v>46013</v>
@@ -3196,13 +3196,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3210,15 +3210,15 @@
         <v>0</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46073.71759153935</v>
@@ -3230,16 +3230,16 @@
         <v>46155.90355751157</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I32" s="5">
         <v>46017</v>
@@ -3257,13 +3257,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3271,15 +3271,15 @@
         <v>0</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46073.717592685185</v>
@@ -3291,16 +3291,16 @@
         <v>46182.683057222224</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I33" s="8">
         <v>46013</v>
@@ -3318,13 +3318,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q33" s="8">
         <v>46013</v>
@@ -3344,7 +3344,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46073.71759302083</v>
@@ -3356,16 +3356,16 @@
         <v>46182.6827475</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I34" s="5">
         <v>46013</v>
@@ -3383,13 +3383,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3397,15 +3397,15 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46073.71758986111</v>
@@ -3417,16 +3417,16 @@
         <v>46182.682943541666</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I35" s="8">
         <v>46017</v>
@@ -3444,13 +3444,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3458,15 +3458,15 @@
         <v>0</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46073.7175918287</v>
@@ -3475,19 +3475,19 @@
         <v>46191.888280127314</v>
       </c>
       <c r="D36" s="5">
-        <v>46191.89070638889</v>
+        <v>46246.81058185185</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I36" s="5">
         <v>46007</v>
@@ -3505,13 +3505,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q36" s="5">
         <v>46007</v>
@@ -3525,13 +3525,13 @@
       <c r="T36" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U36" s="11" t="s">
-        <v>32</v>
+      <c r="U36" s="12" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8">
         <v>46073.71759209491</v>
@@ -3543,16 +3543,16 @@
         <v>46169.84329747685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I37" s="8">
         <v>46007</v>
@@ -3570,13 +3570,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3584,34 +3584,36 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46073.71759234954</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46246.81056665509</v>
+      </c>
       <c r="D38" s="5">
-        <v>46191.88833190972</v>
+        <v>46246.810568113426</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I38" s="5">
         <v>46017</v>
@@ -3629,13 +3631,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3643,15 +3645,15 @@
         <v>0</v>
       </c>
       <c r="T38" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46076.59415034722</v>
@@ -3663,16 +3665,16 @@
         <v>46156.618615775464</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I39" s="8">
         <v>46013</v>
@@ -3690,13 +3692,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q39" s="8">
         <v>46013</v>
@@ -3716,7 +3718,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46076.59428157407</v>
@@ -3728,16 +3730,16 @@
         <v>46154.86737356482</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I40" s="5">
         <v>46013</v>
@@ -3755,13 +3757,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="5">
         <v>46013</v>
@@ -3773,15 +3775,15 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46076.59448399306</v>
@@ -3793,16 +3795,16 @@
         <v>46154.86810545139</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I41" s="8">
         <v>46057</v>
@@ -3820,13 +3822,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="8">
         <v>46057</v>
@@ -3838,15 +3840,15 @@
         <v>0</v>
       </c>
       <c r="T41" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46073.71759148148</v>
@@ -3858,16 +3860,16 @@
         <v>46182.53063152778</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I42" s="5">
         <v>46013</v>
@@ -3885,13 +3887,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q42" s="5">
         <v>46013</v>
@@ -3911,7 +3913,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46073.717591759254</v>
@@ -3923,16 +3925,16 @@
         <v>46182.53047055556</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I43" s="8">
         <v>46013</v>
@@ -3950,13 +3952,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3964,15 +3966,15 @@
         <v>0</v>
       </c>
       <c r="T43" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46073.71759204861</v>
@@ -3984,16 +3986,16 @@
         <v>46182.53060627315</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I44" s="5">
         <v>46037</v>
@@ -4011,13 +4013,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4025,15 +4027,15 @@
         <v>0</v>
       </c>
       <c r="T44" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U44" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8">
         <v>46073.71759234954</v>
@@ -4045,7 +4047,7 @@
         <v>46210.531792002315</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4069,7 +4071,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4086,7 +4088,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46073.717592615736</v>
@@ -4098,16 +4100,16 @@
         <v>46154.09504209491</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I46" s="5">
         <v>46009</v>
@@ -4125,13 +4127,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q46" s="5">
         <v>46009</v>
@@ -4151,7 +4153,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="8">
         <v>46073.71758997685</v>
@@ -4163,16 +4165,16 @@
         <v>46154.09509461805</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I47" s="8">
         <v>46065</v>
@@ -4190,13 +4192,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="8">
         <v>46065</v>
@@ -4216,7 +4218,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46091.72801988426</v>
@@ -4228,16 +4230,16 @@
         <v>46154.09513386574</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I48" s="5">
         <v>46072</v>
@@ -4255,13 +4257,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="5">
         <v>46072</v>
@@ -4281,7 +4283,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46091.728057939814</v>
@@ -4293,16 +4295,16 @@
         <v>46210.53201784722</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I49" s="8">
         <v>46160</v>
@@ -4320,13 +4322,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="8">
         <v>46160</v>
@@ -4346,7 +4348,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46073.71759030093</v>
@@ -4358,7 +4360,7 @@
         <v>46191.789304328704</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4382,7 +4384,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4399,7 +4401,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B51" s="8">
         <v>46073.7175905787</v>
@@ -4411,16 +4413,16 @@
         <v>46191.788422488426</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I51" s="8">
         <v>46069</v>
@@ -4438,13 +4440,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="8">
         <v>46069</v>
@@ -4464,7 +4466,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46073.717590810185</v>
@@ -4476,16 +4478,16 @@
         <v>46191.789293194444</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I52" s="5">
         <v>46071</v>
@@ -4503,13 +4505,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q52" s="5">
         <v>46071</v>
@@ -4529,7 +4531,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B53" s="8">
         <v>46073.717591099536</v>
@@ -4541,7 +4543,7 @@
         <v>46191.79038505787</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4565,7 +4567,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4582,7 +4584,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B54" s="5">
         <v>46073.71759134259</v>
@@ -4594,16 +4596,16 @@
         <v>46191.7899528125</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I54" s="5">
         <v>46073</v>
@@ -4621,13 +4623,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q54" s="5">
         <v>46073</v>
@@ -4647,7 +4649,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B55" s="8">
         <v>46073.71759157407</v>
@@ -4659,16 +4661,16 @@
         <v>46191.790375833334</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I55" s="8">
         <v>46084</v>
@@ -4686,13 +4688,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q55" s="8">
         <v>46084</v>
@@ -4712,7 +4714,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B56" s="5">
         <v>46073.71759181713</v>
@@ -4724,16 +4726,16 @@
         <v>46191.79037549769</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I56" s="5">
         <v>46104</v>
@@ -4751,13 +4753,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q56" s="5">
         <v>46104</v>
@@ -4772,7 +4774,7 @@
         <v>31</v>
       </c>
       <c r="U56" s="12" t="s">
-        <v>212</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4782,12 +4784,14 @@
       <c r="B57" s="8">
         <v>46073.71759206019</v>
       </c>
-      <c r="C57" s="9"/>
+      <c r="C57" s="8">
+        <v>46246.810500127314</v>
+      </c>
       <c r="D57" s="8">
-        <v>46198.827981574075</v>
+        <v>46246.81051277778</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4818,9 +4822,13 @@
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
-      <c r="S57" s="9"/>
+      <c r="S57" s="9">
+        <v>1</v>
+      </c>
       <c r="T57" s="9"/>
-      <c r="U57" s="9"/>
+      <c r="U57" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
@@ -4842,10 +4850,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I58" s="5">
         <v>46153</v>
@@ -4863,10 +4871,10 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>217</v>
@@ -4907,10 +4915,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I59" s="8">
         <v>46135</v>
@@ -4928,10 +4936,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>220</v>
@@ -4972,10 +4980,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I60" s="5">
         <v>46071</v>
@@ -4993,10 +5001,10 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>223</v>
@@ -5024,9 +5032,11 @@
       <c r="B61" s="8">
         <v>46073.71759050926</v>
       </c>
-      <c r="C61" s="9"/>
+      <c r="C61" s="8">
+        <v>46246.810483368055</v>
+      </c>
       <c r="D61" s="8">
-        <v>46191.88833803241</v>
+        <v>46246.81058188657</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5035,10 +5045,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I61" s="8">
         <v>46115</v>
@@ -5056,10 +5066,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>225</v>
@@ -5071,13 +5081,13 @@
         <v>46118</v>
       </c>
       <c r="S61" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" s="10" t="s">
         <v>31</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>212</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5100,10 +5110,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I62" s="5">
         <v>46139</v>
@@ -5121,10 +5131,10 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>228</v>
@@ -5152,9 +5162,11 @@
       <c r="B63" s="8">
         <v>46073.71759130787</v>
       </c>
-      <c r="C63" s="9"/>
+      <c r="C63" s="8">
+        <v>46246.81031905093</v>
+      </c>
       <c r="D63" s="8">
-        <v>46237.553995243055</v>
+        <v>46246.81033018518</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>231</v>
@@ -5188,10 +5200,12 @@
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
-      <c r="S63" s="9"/>
+      <c r="S63" s="9">
+        <v>1</v>
+      </c>
       <c r="T63" s="9"/>
-      <c r="U63" s="12" t="s">
-        <v>212</v>
+      <c r="U63" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5214,10 +5228,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I64" s="5">
         <v>46106</v>
@@ -5238,7 +5252,7 @@
         <v>231</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>235</v>
@@ -5279,10 +5293,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I65" s="8">
         <v>46155</v>
@@ -5344,10 +5358,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I66" s="5">
         <v>46139</v>
@@ -5409,10 +5423,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I67" s="8">
         <v>46141</v>
@@ -5474,10 +5488,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I68" s="5">
         <v>46146</v>
@@ -5533,16 +5547,16 @@
         <v>46223.824139282406</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I69" s="8">
         <v>46157</v>
@@ -5598,16 +5612,16 @@
         <v>46237.55399104167</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I70" s="5">
         <v>46161</v>
@@ -5628,7 +5642,7 @@
         <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>253</v>
@@ -5656,9 +5670,11 @@
       <c r="B71" s="8">
         <v>46237.53415582176</v>
       </c>
-      <c r="C71" s="9"/>
+      <c r="C71" s="8">
+        <v>46246.81030045139</v>
+      </c>
       <c r="D71" s="8">
-        <v>46237.53470668981</v>
+        <v>46246.81031961806</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>255</v>
@@ -5697,13 +5713,13 @@
       </c>
       <c r="R71" s="9"/>
       <c r="S71" s="9">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="T71" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U71" s="12" t="s">
-        <v>212</v>
+      <c r="U71" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5715,7 +5731,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46237.553960046294</v>
+        <v>46246.81082678241</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5749,9 +5765,13 @@
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
-      <c r="S72" s="6"/>
+      <c r="S72" s="6">
+        <v>1</v>
+      </c>
       <c r="T72" s="6"/>
-      <c r="U72" s="6"/>
+      <c r="U72" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
@@ -5760,9 +5780,11 @@
       <c r="B73" s="8">
         <v>46073.71759075232</v>
       </c>
-      <c r="C73" s="9"/>
+      <c r="C73" s="8">
+        <v>46246.81072086806</v>
+      </c>
       <c r="D73" s="8">
-        <v>46237.553996331015</v>
+        <v>46246.810735231484</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>262</v>
@@ -5795,7 +5817,7 @@
         <v>259</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>265</v>
@@ -5807,13 +5829,13 @@
         <v>46162</v>
       </c>
       <c r="S73" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U73" s="12" t="s">
-        <v>212</v>
+      <c r="U73" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5827,7 +5849,7 @@
         <v>46237.553950601854</v>
       </c>
       <c r="D74" s="5">
-        <v>46245.76911054398</v>
+        <v>46246.81073557871</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>267</v>
@@ -5836,10 +5858,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I74" s="5">
         <v>46163</v>
@@ -5877,8 +5899,8 @@
       <c r="T74" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U74" s="11" t="s">
-        <v>32</v>
+      <c r="U74" s="12" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5888,9 +5910,11 @@
       <c r="B75" s="8">
         <v>46073.71759130787</v>
       </c>
-      <c r="C75" s="9"/>
+      <c r="C75" s="8">
+        <v>46246.81074608796</v>
+      </c>
       <c r="D75" s="8">
-        <v>46237.55396895834</v>
+        <v>46246.810762395835</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>271</v>
@@ -5935,13 +5959,13 @@
         <v>46168</v>
       </c>
       <c r="S75" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U75" s="12" t="s">
-        <v>212</v>
+      <c r="U75" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -5951,9 +5975,11 @@
       <c r="B76" s="5">
         <v>46073.7175915625</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46246.810786064816</v>
+      </c>
       <c r="D76" s="5">
-        <v>46240.72145917824</v>
+        <v>46246.81080219908</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>274</v>
@@ -5996,13 +6022,13 @@
         <v>46169</v>
       </c>
       <c r="S76" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T76" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U76" s="10" t="s">
-        <v>109</v>
+      <c r="U76" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6052,10 +6078,10 @@
         <v>0</v>
       </c>
       <c r="T77" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U77" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6067,7 +6093,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46179.199858576394</v>
+        <v>46246.81080466435</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>280</v>
@@ -6117,8 +6143,8 @@
       <c r="T78" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U78" s="10" t="s">
-        <v>109</v>
+      <c r="U78" s="12" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6130,7 +6156,7 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46179.19985642361</v>
+        <v>46246.81080506944</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>284</v>
@@ -6180,8 +6206,8 @@
       <c r="T79" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U79" s="10" t="s">
-        <v>109</v>
+      <c r="U79" s="12" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -5729,9 +5729,11 @@
       <c r="B72" s="5">
         <v>46073.71759042824</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46247.63130804399</v>
+      </c>
       <c r="D72" s="5">
-        <v>46246.81082678241</v>
+        <v>46247.63131010417</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -3288,7 +3288,7 @@
         <v>46182.68305543982</v>
       </c>
       <c r="D33" s="8">
-        <v>46182.683057222224</v>
+        <v>46250.22105207176</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -1495,13 +1495,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.717590115746</v>
+        <v>46073.550923449075</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.724617025466</v>
+        <v>46092.557950358794</v>
       </c>
       <c r="D4" s="5">
-        <v>46114.81259290509</v>
+        <v>46114.64592623843</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1544,13 +1544,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.71759079861</v>
+        <v>46073.550924131945</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.724584826385</v>
+        <v>46092.55791815972</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.72461795139</v>
+        <v>46092.55795128472</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1609,13 +1609,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.71759107639</v>
+        <v>46073.55092440972</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.72458534723</v>
+        <v>46092.557918680555</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.72461783564</v>
+        <v>46092.55795116899</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1674,13 +1674,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.717591354165</v>
+        <v>46073.5509246875</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.72458572917</v>
+        <v>46092.5579190625</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.72461775463</v>
+        <v>46092.55795108796</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1737,13 +1737,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.71759162037</v>
+        <v>46073.5509249537</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72458613426</v>
+        <v>46092.557919467596</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.71077443287</v>
+        <v>46100.5441077662</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1800,13 +1800,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.71759189815</v>
+        <v>46073.55092523148</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.72458673611</v>
+        <v>46092.55792006945</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.72461730324</v>
+        <v>46092.557950636576</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1863,13 +1863,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.71759215278</v>
+        <v>46073.55092548611</v>
       </c>
       <c r="C10" s="5">
-        <v>46245.76911814815</v>
+        <v>46245.60245148148</v>
       </c>
       <c r="D10" s="5">
-        <v>46245.769130659726</v>
+        <v>46245.602463993055</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1916,13 +1916,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.71759246528</v>
+        <v>46073.55092579861</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.526363854166</v>
+        <v>46097.3596971875</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.52638289351</v>
+        <v>46097.359716226856</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1981,13 +1981,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.71759273148</v>
+        <v>46073.55092606481</v>
       </c>
       <c r="C12" s="5">
-        <v>46245.76910020833</v>
+        <v>46245.602433541666</v>
       </c>
       <c r="D12" s="5">
-        <v>46246.8105005324</v>
+        <v>46246.64383386574</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2046,13 +2046,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.71759298611</v>
+        <v>46073.55092631944</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51026252315</v>
+        <v>46114.34359585648</v>
       </c>
       <c r="D13" s="8">
-        <v>46169.884381701384</v>
+        <v>46169.71771503473</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2095,13 +2095,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.71759060185</v>
+        <v>46073.55092393518</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.52584498843</v>
+        <v>46097.359178321756</v>
       </c>
       <c r="D14" s="5">
-        <v>46100.761380717595</v>
+        <v>46100.59471405092</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2160,13 +2160,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.71759128472</v>
+        <v>46073.55092461806</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.50878793982</v>
+        <v>46114.34212127315</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.50880758102</v>
+        <v>46114.34214091435</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2225,13 +2225,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.71759157407</v>
+        <v>46073.55092490741</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.50922814815</v>
+        <v>46114.34256148148</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.509243865745</v>
+        <v>46114.34257719907</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2290,13 +2290,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.71759186343</v>
+        <v>46073.55092519676</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.51024402778</v>
+        <v>46114.34357736111</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.51026347222</v>
+        <v>46114.34359680556</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2355,13 +2355,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.717592141205</v>
+        <v>46073.55092547454</v>
       </c>
       <c r="C18" s="5">
-        <v>46169.88424704861</v>
+        <v>46169.71758038194</v>
       </c>
       <c r="D18" s="5">
-        <v>46169.88433502315</v>
+        <v>46169.71766835648</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2404,13 +2404,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.71759269676</v>
+        <v>46073.55092603009</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.525949456016</v>
+        <v>46097.35928278935</v>
       </c>
       <c r="D19" s="8">
-        <v>46156.61850119213</v>
+        <v>46156.45183452546</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2469,13 +2469,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.71759241898</v>
+        <v>46073.550925752315</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.5259784375</v>
+        <v>46097.35931177084</v>
       </c>
       <c r="D20" s="5">
-        <v>46156.61851966435</v>
+        <v>46156.451852997685</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2534,13 +2534,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.717593298614</v>
+        <v>46073.55092663194</v>
       </c>
       <c r="C21" s="8">
-        <v>46128.433728668984</v>
+        <v>46128.26706200231</v>
       </c>
       <c r="D21" s="8">
-        <v>46223.823994606486</v>
+        <v>46223.657327939814</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2599,13 +2599,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.71759302083</v>
+        <v>46073.55092635417</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.52660114583</v>
+        <v>46097.359934479166</v>
       </c>
       <c r="D22" s="5">
-        <v>46097.52662200232</v>
+        <v>46097.35995533565</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2664,13 +2664,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.593357997685</v>
+        <v>46076.42669133102</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.51032266204</v>
+        <v>46114.34365599537</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.51047230324</v>
+        <v>46114.34380563657</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2729,13 +2729,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.71759033565</v>
+        <v>46073.55092366898</v>
       </c>
       <c r="C24" s="5">
-        <v>46169.88422872685</v>
+        <v>46169.717562060185</v>
       </c>
       <c r="D24" s="5">
-        <v>46223.82399125</v>
+        <v>46223.657324583335</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2794,13 +2794,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.71759071759</v>
+        <v>46073.55092405093</v>
       </c>
       <c r="C25" s="8">
-        <v>46204.6994087037</v>
+        <v>46204.53274203704</v>
       </c>
       <c r="D25" s="8">
-        <v>46204.69942763889</v>
+        <v>46204.53276097222</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2847,13 +2847,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.7175902662</v>
+        <v>46073.55092359954</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.86689138889</v>
+        <v>46155.700224722226</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.86710392361</v>
+        <v>46155.70043725694</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2912,13 +2912,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.7175905787</v>
+        <v>46073.55092391204</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.52605542824</v>
+        <v>46097.35938876157</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.52605688658</v>
+        <v>46097.359390219906</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2973,13 +2973,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.71759086805</v>
+        <v>46073.550924201394</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.86687702546</v>
+        <v>46155.700210358795</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.866878229164</v>
+        <v>46155.7002115625</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3034,13 +3034,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.71759118055</v>
+        <v>46073.55092451389</v>
       </c>
       <c r="C29" s="8">
-        <v>46128.637161886574</v>
+        <v>46128.47049521991</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.63717174769</v>
+        <v>46128.470505081015</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3095,13 +3095,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.7175909838</v>
+        <v>46073.550924317125</v>
       </c>
       <c r="C30" s="5">
-        <v>46155.903569421294</v>
+        <v>46155.73690275463</v>
       </c>
       <c r="D30" s="5">
-        <v>46155.90358277778</v>
+        <v>46155.73691611111</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3160,13 +3160,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.71759126158</v>
+        <v>46073.55092459491</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.526086377315</v>
+        <v>46097.35941971064</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.52608802084</v>
+        <v>46097.359421354166</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3221,13 +3221,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.71759153935</v>
+        <v>46073.55092487269</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.903555972225</v>
+        <v>46155.73688930555</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.90355751157</v>
+        <v>46155.736890844906</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3282,13 +3282,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.717592685185</v>
+        <v>46073.55092601852</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.68305543982</v>
+        <v>46182.51638877315</v>
       </c>
       <c r="D33" s="8">
-        <v>46250.22105207176</v>
+        <v>46250.05438540509</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3347,13 +3347,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.71759302083</v>
+        <v>46073.55092635417</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.68274605324</v>
+        <v>46182.51607938657</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.6827475</v>
+        <v>46182.51608083333</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3408,13 +3408,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.71758986111</v>
+        <v>46073.550923194445</v>
       </c>
       <c r="C35" s="8">
-        <v>46182.682942314816</v>
+        <v>46182.516275648144</v>
       </c>
       <c r="D35" s="8">
-        <v>46182.682943541666</v>
+        <v>46182.516276875</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3469,13 +3469,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.7175918287</v>
+        <v>46073.55092516204</v>
       </c>
       <c r="C36" s="5">
-        <v>46191.888280127314</v>
+        <v>46191.72161346065</v>
       </c>
       <c r="D36" s="5">
-        <v>46246.81058185185</v>
+        <v>46246.64391518518</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3534,13 +3534,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.71759209491</v>
+        <v>46073.55092542824</v>
       </c>
       <c r="C37" s="8">
-        <v>46097.526664247685</v>
+        <v>46097.35999758102</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.84329747685</v>
+        <v>46169.67663081019</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3595,13 +3595,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.71759234954</v>
+        <v>46073.55092568287</v>
       </c>
       <c r="C38" s="5">
-        <v>46246.81056665509</v>
+        <v>46246.64389998843</v>
       </c>
       <c r="D38" s="5">
-        <v>46246.810568113426</v>
+        <v>46246.64390144676</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3656,13 +3656,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46076.59415034722</v>
+        <v>46076.427483680556</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.86805253472</v>
+        <v>46154.70138586806</v>
       </c>
       <c r="D39" s="8">
-        <v>46156.618615775464</v>
+        <v>46156.4519491088</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3721,13 +3721,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46076.59428157407</v>
+        <v>46076.42761490741</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.86737157407</v>
+        <v>46154.70070490741</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.86737356482</v>
+        <v>46154.70070689815</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3786,13 +3786,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46076.59448399306</v>
+        <v>46076.42781732639</v>
       </c>
       <c r="C41" s="8">
-        <v>46154.86810417824</v>
+        <v>46154.70143751157</v>
       </c>
       <c r="D41" s="8">
-        <v>46154.86810545139</v>
+        <v>46154.70143878472</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3851,13 +3851,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.71759148148</v>
+        <v>46073.550924814816</v>
       </c>
       <c r="C42" s="5">
-        <v>46182.530618530094</v>
+        <v>46182.36395186343</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.53063152778</v>
+        <v>46182.36396486111</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3916,13 +3916,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.717591759254</v>
+        <v>46073.5509250926</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.53046844907</v>
+        <v>46182.36380178241</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.53047055556</v>
+        <v>46182.36380388889</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3977,13 +3977,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.71759204861</v>
+        <v>46073.55092538195</v>
       </c>
       <c r="C44" s="5">
-        <v>46182.530605011576</v>
+        <v>46182.363938344904</v>
       </c>
       <c r="D44" s="5">
-        <v>46182.53060627315</v>
+        <v>46182.36393960648</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4038,13 +4038,13 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.71759234954</v>
+        <v>46073.55092568287</v>
       </c>
       <c r="C45" s="8">
-        <v>46210.531775787036</v>
+        <v>46210.36510912037</v>
       </c>
       <c r="D45" s="8">
-        <v>46210.531792002315</v>
+        <v>46210.36512533565</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4091,13 +4091,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.717592615736</v>
+        <v>46073.55092594908</v>
       </c>
       <c r="C46" s="5">
-        <v>46154.09501991898</v>
+        <v>46153.92835325231</v>
       </c>
       <c r="D46" s="5">
-        <v>46154.09504209491</v>
+        <v>46153.92837542824</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4156,13 +4156,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.71758997685</v>
+        <v>46073.550923310184</v>
       </c>
       <c r="C47" s="8">
-        <v>46154.09507998843</v>
+        <v>46153.92841332176</v>
       </c>
       <c r="D47" s="8">
-        <v>46154.09509461805</v>
+        <v>46153.92842795139</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4221,13 +4221,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46091.72801988426</v>
+        <v>46091.56135321759</v>
       </c>
       <c r="C48" s="5">
-        <v>46154.09511894676</v>
+        <v>46153.92845228009</v>
       </c>
       <c r="D48" s="5">
-        <v>46154.09513386574</v>
+        <v>46153.928467199075</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4286,13 +4286,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46091.728057939814</v>
+        <v>46091.56139127315</v>
       </c>
       <c r="C49" s="8">
-        <v>46210.531998136576</v>
+        <v>46210.365331469904</v>
       </c>
       <c r="D49" s="8">
-        <v>46210.53201784722</v>
+        <v>46210.36535118056</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4351,13 +4351,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.71759030093</v>
+        <v>46073.55092363426</v>
       </c>
       <c r="C50" s="5">
-        <v>46191.78929271991</v>
+        <v>46191.62262605324</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.789304328704</v>
+        <v>46191.62263766203</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4404,13 +4404,13 @@
         <v>188</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.7175905787</v>
+        <v>46073.55092391204</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.788401875005</v>
+        <v>46191.62173520833</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.788422488426</v>
+        <v>46191.62175582176</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>163</v>
@@ -4469,13 +4469,13 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.717590810185</v>
+        <v>46073.55092414352</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.78927659722</v>
+        <v>46191.62260993056</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.789293194444</v>
+        <v>46191.62262652778</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4534,13 +4534,13 @@
         <v>197</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.717591099536</v>
+        <v>46073.55092443287</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.79037481482</v>
+        <v>46191.62370814815</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.79038505787</v>
+        <v>46191.6237183912</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>198</v>
@@ -4587,13 +4587,13 @@
         <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.71759134259</v>
+        <v>46073.550924675925</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.7899369213</v>
+        <v>46191.623270254626</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.7899528125</v>
+        <v>46191.623286145834</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>201</v>
@@ -4652,13 +4652,13 @@
         <v>205</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.71759157407</v>
+        <v>46073.55092490741</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.79035826389</v>
+        <v>46191.623691597226</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.790375833334</v>
+        <v>46191.62370916667</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>206</v>
@@ -4717,13 +4717,13 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.71759181713</v>
+        <v>46073.55092515046</v>
       </c>
       <c r="C56" s="5">
-        <v>46191.789681423616</v>
+        <v>46191.623014756944</v>
       </c>
       <c r="D56" s="5">
-        <v>46191.79037549769</v>
+        <v>46191.623708831015</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4782,13 +4782,13 @@
         <v>213</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.71759206019</v>
+        <v>46073.550925393516</v>
       </c>
       <c r="C57" s="8">
-        <v>46246.810500127314</v>
+        <v>46246.64383346065</v>
       </c>
       <c r="D57" s="8">
-        <v>46246.81051277778</v>
+        <v>46246.64384611111</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>186</v>
@@ -4835,13 +4835,13 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.71759105324</v>
+        <v>46073.550924386574</v>
       </c>
       <c r="C58" s="5">
-        <v>46195.608916770834</v>
+        <v>46195.44225010417</v>
       </c>
       <c r="D58" s="5">
-        <v>46195.60893649305</v>
+        <v>46195.44226982639</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>216</v>
@@ -4900,13 +4900,13 @@
         <v>218</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.71759083333</v>
+        <v>46073.550924166666</v>
       </c>
       <c r="C59" s="8">
-        <v>46195.60909078704</v>
+        <v>46195.44242412037</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.60910890046</v>
+        <v>46195.4424422338</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>219</v>
@@ -4965,13 +4965,13 @@
         <v>221</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.71759233796</v>
+        <v>46073.5509256713</v>
       </c>
       <c r="C60" s="5">
-        <v>46198.82797583334</v>
+        <v>46198.661309166666</v>
       </c>
       <c r="D60" s="5">
-        <v>46198.82799237268</v>
+        <v>46198.66132570602</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>222</v>
@@ -5030,13 +5030,13 @@
         <v>224</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.71759050926</v>
+        <v>46073.55092384259</v>
       </c>
       <c r="C61" s="8">
-        <v>46246.810483368055</v>
+        <v>46246.643816701384</v>
       </c>
       <c r="D61" s="8">
-        <v>46246.81058188657</v>
+        <v>46246.64391521991</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5095,13 +5095,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.59959273148</v>
+        <v>46076.432926064816</v>
       </c>
       <c r="C62" s="5">
-        <v>46198.82946502315</v>
+        <v>46198.66279835648</v>
       </c>
       <c r="D62" s="5">
-        <v>46198.829483009264</v>
+        <v>46198.66281634259</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>227</v>
@@ -5160,13 +5160,13 @@
         <v>230</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.71759130787</v>
+        <v>46073.550924641204</v>
       </c>
       <c r="C63" s="8">
-        <v>46246.81031905093</v>
+        <v>46246.64365238426</v>
       </c>
       <c r="D63" s="8">
-        <v>46246.81033018518</v>
+        <v>46246.643663518524</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>231</v>
@@ -5213,13 +5213,13 @@
         <v>233</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.71759155093</v>
+        <v>46073.55092488426</v>
       </c>
       <c r="C64" s="5">
-        <v>46193.60723070602</v>
+        <v>46193.44056403935</v>
       </c>
       <c r="D64" s="5">
-        <v>46223.82415971065</v>
+        <v>46223.65749304398</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5278,13 +5278,13 @@
         <v>236</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.71759180556</v>
+        <v>46073.55092513889</v>
       </c>
       <c r="C65" s="8">
-        <v>46193.60739422454</v>
+        <v>46193.44072755787</v>
       </c>
       <c r="D65" s="8">
-        <v>46223.82415605324</v>
+        <v>46223.657489386576</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>237</v>
@@ -5343,13 +5343,13 @@
         <v>240</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.717592037036</v>
+        <v>46073.55092537037</v>
       </c>
       <c r="C66" s="5">
-        <v>46193.60745574074</v>
+        <v>46193.44078907407</v>
       </c>
       <c r="D66" s="5">
-        <v>46223.824151967594</v>
+        <v>46223.65748530092</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>241</v>
@@ -5408,13 +5408,13 @@
         <v>244</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.71759226852</v>
+        <v>46073.550925601856</v>
       </c>
       <c r="C67" s="8">
-        <v>46193.607493668984</v>
+        <v>46193.44082700231</v>
       </c>
       <c r="D67" s="8">
-        <v>46223.8241483912</v>
+        <v>46223.65748172454</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>245</v>
@@ -5473,13 +5473,13 @@
         <v>247</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.600719699076</v>
+        <v>46076.43405303241</v>
       </c>
       <c r="C68" s="5">
-        <v>46193.60764289352</v>
+        <v>46193.44097622685</v>
       </c>
       <c r="D68" s="5">
-        <v>46223.82414435185</v>
+        <v>46223.657477685185</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>228</v>
@@ -5538,13 +5538,13 @@
         <v>249</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.71759252315</v>
+        <v>46073.550925856485</v>
       </c>
       <c r="C69" s="8">
-        <v>46195.86820241898</v>
+        <v>46195.70153575232</v>
       </c>
       <c r="D69" s="8">
-        <v>46223.824139282406</v>
+        <v>46223.65747261574</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>183</v>
@@ -5603,13 +5603,13 @@
         <v>252</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.7175927662</v>
+        <v>46073.55092609954</v>
       </c>
       <c r="C70" s="5">
-        <v>46237.55397583333</v>
+        <v>46237.38730916667</v>
       </c>
       <c r="D70" s="5">
-        <v>46237.55399104167</v>
+        <v>46237.387324375</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>184</v>
@@ -5668,13 +5668,13 @@
         <v>254</v>
       </c>
       <c r="B71" s="8">
-        <v>46237.53415582176</v>
+        <v>46237.36748915509</v>
       </c>
       <c r="C71" s="8">
-        <v>46246.81030045139</v>
+        <v>46246.643633784726</v>
       </c>
       <c r="D71" s="8">
-        <v>46246.81031961806</v>
+        <v>46246.64365295139</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>255</v>
@@ -5727,13 +5727,13 @@
         <v>258</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.71759042824</v>
+        <v>46073.55092376158</v>
       </c>
       <c r="C72" s="5">
-        <v>46247.63130804399</v>
+        <v>46247.464641377315</v>
       </c>
       <c r="D72" s="5">
-        <v>46247.63131010417</v>
+        <v>46247.4646434375</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5780,13 +5780,13 @@
         <v>261</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.71759075232</v>
+        <v>46073.55092408565</v>
       </c>
       <c r="C73" s="8">
-        <v>46246.81072086806</v>
+        <v>46246.64405420139</v>
       </c>
       <c r="D73" s="8">
-        <v>46246.810735231484</v>
+        <v>46246.64406856481</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>262</v>
@@ -5845,13 +5845,13 @@
         <v>266</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.71759101852</v>
+        <v>46073.55092435185</v>
       </c>
       <c r="C74" s="5">
-        <v>46237.553950601854</v>
+        <v>46237.38728393518</v>
       </c>
       <c r="D74" s="5">
-        <v>46246.81073557871</v>
+        <v>46246.644068912035</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>267</v>
@@ -5910,13 +5910,13 @@
         <v>270</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.71759130787</v>
+        <v>46073.550924641204</v>
       </c>
       <c r="C75" s="8">
-        <v>46246.81074608796</v>
+        <v>46246.6440794213</v>
       </c>
       <c r="D75" s="8">
-        <v>46246.810762395835</v>
+        <v>46246.64409572916</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>271</v>
@@ -5975,13 +5975,13 @@
         <v>273</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.7175915625</v>
+        <v>46073.55092489583</v>
       </c>
       <c r="C76" s="5">
-        <v>46246.810786064816</v>
+        <v>46246.644119398145</v>
       </c>
       <c r="D76" s="5">
-        <v>46246.81080219908</v>
+        <v>46246.644135532406</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>274</v>
@@ -6038,11 +6038,11 @@
         <v>276</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.71759184028</v>
+        <v>46073.55092517361</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46091.73446550926</v>
+        <v>46091.56779884259</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>277</v>
@@ -6091,11 +6091,11 @@
         <v>279</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.71759210648</v>
+        <v>46073.55092543981</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46246.81080466435</v>
+        <v>46246.64413799769</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>280</v>
@@ -6154,11 +6154,11 @@
         <v>283</v>
       </c>
       <c r="B79" s="8">
-        <v>46073.71759238426</v>
+        <v>46073.55092571759</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46246.81080506944</v>
+        <v>46246.64413840278</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>284</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -1495,13 +1495,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.550923449075</v>
+        <v>46073.717590115746</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.557950358794</v>
+        <v>46092.724617025466</v>
       </c>
       <c r="D4" s="5">
-        <v>46114.64592623843</v>
+        <v>46114.81259290509</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1544,13 +1544,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.550924131945</v>
+        <v>46073.71759079861</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55791815972</v>
+        <v>46092.724584826385</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55795128472</v>
+        <v>46092.72461795139</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1609,13 +1609,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.55092440972</v>
+        <v>46073.71759107639</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.557918680555</v>
+        <v>46092.72458534723</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55795116899</v>
+        <v>46092.72461783564</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1674,13 +1674,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.5509246875</v>
+        <v>46073.717591354165</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.5579190625</v>
+        <v>46092.72458572917</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.55795108796</v>
+        <v>46092.72461775463</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1737,13 +1737,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.5509249537</v>
+        <v>46073.71759162037</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.557919467596</v>
+        <v>46092.72458613426</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.5441077662</v>
+        <v>46100.71077443287</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1800,13 +1800,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.55092523148</v>
+        <v>46073.71759189815</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55792006945</v>
+        <v>46092.72458673611</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.557950636576</v>
+        <v>46092.72461730324</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1863,13 +1863,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.55092548611</v>
+        <v>46073.71759215278</v>
       </c>
       <c r="C10" s="5">
-        <v>46245.60245148148</v>
+        <v>46245.76911814815</v>
       </c>
       <c r="D10" s="5">
-        <v>46245.602463993055</v>
+        <v>46245.769130659726</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1916,13 +1916,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.55092579861</v>
+        <v>46073.71759246528</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.3596971875</v>
+        <v>46097.526363854166</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.359716226856</v>
+        <v>46097.52638289351</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1981,13 +1981,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.55092606481</v>
+        <v>46073.71759273148</v>
       </c>
       <c r="C12" s="5">
-        <v>46245.602433541666</v>
+        <v>46245.76910020833</v>
       </c>
       <c r="D12" s="5">
-        <v>46246.64383386574</v>
+        <v>46246.8105005324</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2046,13 +2046,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.55092631944</v>
+        <v>46073.71759298611</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.34359585648</v>
+        <v>46114.51026252315</v>
       </c>
       <c r="D13" s="8">
-        <v>46169.71771503473</v>
+        <v>46169.884381701384</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2095,13 +2095,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.55092393518</v>
+        <v>46073.71759060185</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.359178321756</v>
+        <v>46097.52584498843</v>
       </c>
       <c r="D14" s="5">
-        <v>46100.59471405092</v>
+        <v>46100.761380717595</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2160,13 +2160,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.55092461806</v>
+        <v>46073.71759128472</v>
       </c>
       <c r="C15" s="8">
-        <v>46114.34212127315</v>
+        <v>46114.50878793982</v>
       </c>
       <c r="D15" s="8">
-        <v>46114.34214091435</v>
+        <v>46114.50880758102</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2225,13 +2225,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.55092490741</v>
+        <v>46073.71759157407</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.34256148148</v>
+        <v>46114.50922814815</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.34257719907</v>
+        <v>46114.509243865745</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2290,13 +2290,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.55092519676</v>
+        <v>46073.71759186343</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34357736111</v>
+        <v>46114.51024402778</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.34359680556</v>
+        <v>46114.51026347222</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2355,13 +2355,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.55092547454</v>
+        <v>46073.717592141205</v>
       </c>
       <c r="C18" s="5">
-        <v>46169.71758038194</v>
+        <v>46169.88424704861</v>
       </c>
       <c r="D18" s="5">
-        <v>46169.71766835648</v>
+        <v>46169.88433502315</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2404,13 +2404,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.55092603009</v>
+        <v>46073.71759269676</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.35928278935</v>
+        <v>46097.525949456016</v>
       </c>
       <c r="D19" s="8">
-        <v>46156.45183452546</v>
+        <v>46156.61850119213</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2469,13 +2469,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.550925752315</v>
+        <v>46073.71759241898</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.35931177084</v>
+        <v>46097.5259784375</v>
       </c>
       <c r="D20" s="5">
-        <v>46156.451852997685</v>
+        <v>46156.61851966435</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2534,13 +2534,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.55092663194</v>
+        <v>46073.717593298614</v>
       </c>
       <c r="C21" s="8">
-        <v>46128.26706200231</v>
+        <v>46128.433728668984</v>
       </c>
       <c r="D21" s="8">
-        <v>46223.657327939814</v>
+        <v>46223.823994606486</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2599,13 +2599,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.55092635417</v>
+        <v>46073.71759302083</v>
       </c>
       <c r="C22" s="5">
-        <v>46097.359934479166</v>
+        <v>46097.52660114583</v>
       </c>
       <c r="D22" s="5">
-        <v>46097.35995533565</v>
+        <v>46097.52662200232</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2664,13 +2664,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46076.42669133102</v>
+        <v>46076.593357997685</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.34365599537</v>
+        <v>46114.51032266204</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.34380563657</v>
+        <v>46114.51047230324</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2729,13 +2729,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.55092366898</v>
+        <v>46073.71759033565</v>
       </c>
       <c r="C24" s="5">
-        <v>46169.717562060185</v>
+        <v>46169.88422872685</v>
       </c>
       <c r="D24" s="5">
-        <v>46223.657324583335</v>
+        <v>46223.82399125</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2794,13 +2794,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.55092405093</v>
+        <v>46073.71759071759</v>
       </c>
       <c r="C25" s="8">
-        <v>46204.53274203704</v>
+        <v>46204.6994087037</v>
       </c>
       <c r="D25" s="8">
-        <v>46204.53276097222</v>
+        <v>46204.69942763889</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2847,13 +2847,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.55092359954</v>
+        <v>46073.7175902662</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.700224722226</v>
+        <v>46155.86689138889</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.70043725694</v>
+        <v>46155.86710392361</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2912,13 +2912,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.55092391204</v>
+        <v>46073.7175905787</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.35938876157</v>
+        <v>46097.52605542824</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.359390219906</v>
+        <v>46097.52605688658</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2973,13 +2973,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.550924201394</v>
+        <v>46073.71759086805</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.700210358795</v>
+        <v>46155.86687702546</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.7002115625</v>
+        <v>46155.866878229164</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3034,13 +3034,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.55092451389</v>
+        <v>46073.71759118055</v>
       </c>
       <c r="C29" s="8">
-        <v>46128.47049521991</v>
+        <v>46128.637161886574</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.470505081015</v>
+        <v>46128.63717174769</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3095,13 +3095,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.550924317125</v>
+        <v>46073.7175909838</v>
       </c>
       <c r="C30" s="5">
-        <v>46155.73690275463</v>
+        <v>46155.903569421294</v>
       </c>
       <c r="D30" s="5">
-        <v>46155.73691611111</v>
+        <v>46155.90358277778</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3160,13 +3160,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.55092459491</v>
+        <v>46073.71759126158</v>
       </c>
       <c r="C31" s="8">
-        <v>46097.35941971064</v>
+        <v>46097.526086377315</v>
       </c>
       <c r="D31" s="8">
-        <v>46097.359421354166</v>
+        <v>46097.52608802084</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3221,13 +3221,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.55092487269</v>
+        <v>46073.71759153935</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.73688930555</v>
+        <v>46155.903555972225</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.736890844906</v>
+        <v>46155.90355751157</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3282,13 +3282,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.55092601852</v>
+        <v>46073.717592685185</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.51638877315</v>
+        <v>46182.68305543982</v>
       </c>
       <c r="D33" s="8">
-        <v>46250.05438540509</v>
+        <v>46250.22105207176</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3347,13 +3347,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.55092635417</v>
+        <v>46073.71759302083</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.51607938657</v>
+        <v>46182.68274605324</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.51608083333</v>
+        <v>46182.6827475</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3408,13 +3408,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.550923194445</v>
+        <v>46073.71758986111</v>
       </c>
       <c r="C35" s="8">
-        <v>46182.516275648144</v>
+        <v>46182.682942314816</v>
       </c>
       <c r="D35" s="8">
-        <v>46182.516276875</v>
+        <v>46182.682943541666</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3469,13 +3469,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.55092516204</v>
+        <v>46073.7175918287</v>
       </c>
       <c r="C36" s="5">
-        <v>46191.72161346065</v>
+        <v>46191.888280127314</v>
       </c>
       <c r="D36" s="5">
-        <v>46246.64391518518</v>
+        <v>46246.81058185185</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3534,13 +3534,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.55092542824</v>
+        <v>46073.71759209491</v>
       </c>
       <c r="C37" s="8">
-        <v>46097.35999758102</v>
+        <v>46097.526664247685</v>
       </c>
       <c r="D37" s="8">
-        <v>46169.67663081019</v>
+        <v>46169.84329747685</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3595,13 +3595,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.55092568287</v>
+        <v>46073.71759234954</v>
       </c>
       <c r="C38" s="5">
-        <v>46246.64389998843</v>
+        <v>46246.81056665509</v>
       </c>
       <c r="D38" s="5">
-        <v>46246.64390144676</v>
+        <v>46246.810568113426</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3656,13 +3656,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46076.427483680556</v>
+        <v>46076.59415034722</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.70138586806</v>
+        <v>46154.86805253472</v>
       </c>
       <c r="D39" s="8">
-        <v>46156.4519491088</v>
+        <v>46156.618615775464</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3721,13 +3721,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46076.42761490741</v>
+        <v>46076.59428157407</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.70070490741</v>
+        <v>46154.86737157407</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.70070689815</v>
+        <v>46154.86737356482</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -3786,13 +3786,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46076.42781732639</v>
+        <v>46076.59448399306</v>
       </c>
       <c r="C41" s="8">
-        <v>46154.70143751157</v>
+        <v>46154.86810417824</v>
       </c>
       <c r="D41" s="8">
-        <v>46154.70143878472</v>
+        <v>46154.86810545139</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -3851,13 +3851,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.550924814816</v>
+        <v>46073.71759148148</v>
       </c>
       <c r="C42" s="5">
-        <v>46182.36395186343</v>
+        <v>46182.530618530094</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.36396486111</v>
+        <v>46182.53063152778</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -3916,13 +3916,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.5509250926</v>
+        <v>46073.717591759254</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.36380178241</v>
+        <v>46182.53046844907</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.36380388889</v>
+        <v>46182.53047055556</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3977,13 +3977,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.55092538195</v>
+        <v>46073.71759204861</v>
       </c>
       <c r="C44" s="5">
-        <v>46182.363938344904</v>
+        <v>46182.530605011576</v>
       </c>
       <c r="D44" s="5">
-        <v>46182.36393960648</v>
+        <v>46182.53060627315</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4038,13 +4038,13 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.55092568287</v>
+        <v>46073.71759234954</v>
       </c>
       <c r="C45" s="8">
-        <v>46210.36510912037</v>
+        <v>46210.531775787036</v>
       </c>
       <c r="D45" s="8">
-        <v>46210.36512533565</v>
+        <v>46210.531792002315</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4091,13 +4091,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.55092594908</v>
+        <v>46073.717592615736</v>
       </c>
       <c r="C46" s="5">
-        <v>46153.92835325231</v>
+        <v>46154.09501991898</v>
       </c>
       <c r="D46" s="5">
-        <v>46153.92837542824</v>
+        <v>46154.09504209491</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4156,13 +4156,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.550923310184</v>
+        <v>46073.71758997685</v>
       </c>
       <c r="C47" s="8">
-        <v>46153.92841332176</v>
+        <v>46154.09507998843</v>
       </c>
       <c r="D47" s="8">
-        <v>46153.92842795139</v>
+        <v>46154.09509461805</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4221,13 +4221,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46091.56135321759</v>
+        <v>46091.72801988426</v>
       </c>
       <c r="C48" s="5">
-        <v>46153.92845228009</v>
+        <v>46154.09511894676</v>
       </c>
       <c r="D48" s="5">
-        <v>46153.928467199075</v>
+        <v>46154.09513386574</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4286,13 +4286,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46091.56139127315</v>
+        <v>46091.728057939814</v>
       </c>
       <c r="C49" s="8">
-        <v>46210.365331469904</v>
+        <v>46210.531998136576</v>
       </c>
       <c r="D49" s="8">
-        <v>46210.36535118056</v>
+        <v>46210.53201784722</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4351,13 +4351,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.55092363426</v>
+        <v>46073.71759030093</v>
       </c>
       <c r="C50" s="5">
-        <v>46191.62262605324</v>
+        <v>46191.78929271991</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.62263766203</v>
+        <v>46191.789304328704</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4404,13 +4404,13 @@
         <v>188</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.55092391204</v>
+        <v>46073.7175905787</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.62173520833</v>
+        <v>46191.788401875005</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.62175582176</v>
+        <v>46191.788422488426</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>163</v>
@@ -4469,13 +4469,13 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.55092414352</v>
+        <v>46073.717590810185</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.62260993056</v>
+        <v>46191.78927659722</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.62262652778</v>
+        <v>46191.789293194444</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4534,13 +4534,13 @@
         <v>197</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.55092443287</v>
+        <v>46073.717591099536</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.62370814815</v>
+        <v>46191.79037481482</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.6237183912</v>
+        <v>46191.79038505787</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>198</v>
@@ -4587,13 +4587,13 @@
         <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.550924675925</v>
+        <v>46073.71759134259</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.623270254626</v>
+        <v>46191.7899369213</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.623286145834</v>
+        <v>46191.7899528125</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>201</v>
@@ -4652,13 +4652,13 @@
         <v>205</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.55092490741</v>
+        <v>46073.71759157407</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.623691597226</v>
+        <v>46191.79035826389</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.62370916667</v>
+        <v>46191.790375833334</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>206</v>
@@ -4717,13 +4717,13 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.55092515046</v>
+        <v>46073.71759181713</v>
       </c>
       <c r="C56" s="5">
-        <v>46191.623014756944</v>
+        <v>46191.789681423616</v>
       </c>
       <c r="D56" s="5">
-        <v>46191.623708831015</v>
+        <v>46191.79037549769</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4782,13 +4782,13 @@
         <v>213</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.550925393516</v>
+        <v>46073.71759206019</v>
       </c>
       <c r="C57" s="8">
-        <v>46246.64383346065</v>
+        <v>46246.810500127314</v>
       </c>
       <c r="D57" s="8">
-        <v>46246.64384611111</v>
+        <v>46246.81051277778</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>186</v>
@@ -4835,13 +4835,13 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.550924386574</v>
+        <v>46073.71759105324</v>
       </c>
       <c r="C58" s="5">
-        <v>46195.44225010417</v>
+        <v>46195.608916770834</v>
       </c>
       <c r="D58" s="5">
-        <v>46195.44226982639</v>
+        <v>46195.60893649305</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>216</v>
@@ -4900,13 +4900,13 @@
         <v>218</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.550924166666</v>
+        <v>46073.71759083333</v>
       </c>
       <c r="C59" s="8">
-        <v>46195.44242412037</v>
+        <v>46195.60909078704</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.4424422338</v>
+        <v>46195.60910890046</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>219</v>
@@ -4965,13 +4965,13 @@
         <v>221</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.5509256713</v>
+        <v>46073.71759233796</v>
       </c>
       <c r="C60" s="5">
-        <v>46198.661309166666</v>
+        <v>46198.82797583334</v>
       </c>
       <c r="D60" s="5">
-        <v>46198.66132570602</v>
+        <v>46198.82799237268</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>222</v>
@@ -5030,13 +5030,13 @@
         <v>224</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.55092384259</v>
+        <v>46073.71759050926</v>
       </c>
       <c r="C61" s="8">
-        <v>46246.643816701384</v>
+        <v>46246.810483368055</v>
       </c>
       <c r="D61" s="8">
-        <v>46246.64391521991</v>
+        <v>46246.81058188657</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5095,13 +5095,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46076.432926064816</v>
+        <v>46076.59959273148</v>
       </c>
       <c r="C62" s="5">
-        <v>46198.66279835648</v>
+        <v>46198.82946502315</v>
       </c>
       <c r="D62" s="5">
-        <v>46198.66281634259</v>
+        <v>46198.829483009264</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>227</v>
@@ -5160,13 +5160,13 @@
         <v>230</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.550924641204</v>
+        <v>46073.71759130787</v>
       </c>
       <c r="C63" s="8">
-        <v>46246.64365238426</v>
+        <v>46246.81031905093</v>
       </c>
       <c r="D63" s="8">
-        <v>46246.643663518524</v>
+        <v>46246.81033018518</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>231</v>
@@ -5213,13 +5213,13 @@
         <v>233</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.55092488426</v>
+        <v>46073.71759155093</v>
       </c>
       <c r="C64" s="5">
-        <v>46193.44056403935</v>
+        <v>46193.60723070602</v>
       </c>
       <c r="D64" s="5">
-        <v>46223.65749304398</v>
+        <v>46223.82415971065</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>234</v>
@@ -5278,13 +5278,13 @@
         <v>236</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.55092513889</v>
+        <v>46073.71759180556</v>
       </c>
       <c r="C65" s="8">
-        <v>46193.44072755787</v>
+        <v>46193.60739422454</v>
       </c>
       <c r="D65" s="8">
-        <v>46223.657489386576</v>
+        <v>46223.82415605324</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>237</v>
@@ -5343,13 +5343,13 @@
         <v>240</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.55092537037</v>
+        <v>46073.717592037036</v>
       </c>
       <c r="C66" s="5">
-        <v>46193.44078907407</v>
+        <v>46193.60745574074</v>
       </c>
       <c r="D66" s="5">
-        <v>46223.65748530092</v>
+        <v>46223.824151967594</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>241</v>
@@ -5408,13 +5408,13 @@
         <v>244</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.550925601856</v>
+        <v>46073.71759226852</v>
       </c>
       <c r="C67" s="8">
-        <v>46193.44082700231</v>
+        <v>46193.607493668984</v>
       </c>
       <c r="D67" s="8">
-        <v>46223.65748172454</v>
+        <v>46223.8241483912</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>245</v>
@@ -5473,13 +5473,13 @@
         <v>247</v>
       </c>
       <c r="B68" s="5">
-        <v>46076.43405303241</v>
+        <v>46076.600719699076</v>
       </c>
       <c r="C68" s="5">
-        <v>46193.44097622685</v>
+        <v>46193.60764289352</v>
       </c>
       <c r="D68" s="5">
-        <v>46223.657477685185</v>
+        <v>46223.82414435185</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>228</v>
@@ -5538,13 +5538,13 @@
         <v>249</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.550925856485</v>
+        <v>46073.71759252315</v>
       </c>
       <c r="C69" s="8">
-        <v>46195.70153575232</v>
+        <v>46195.86820241898</v>
       </c>
       <c r="D69" s="8">
-        <v>46223.65747261574</v>
+        <v>46223.824139282406</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>183</v>
@@ -5603,13 +5603,13 @@
         <v>252</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.55092609954</v>
+        <v>46073.7175927662</v>
       </c>
       <c r="C70" s="5">
-        <v>46237.38730916667</v>
+        <v>46237.55397583333</v>
       </c>
       <c r="D70" s="5">
-        <v>46237.387324375</v>
+        <v>46237.55399104167</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>184</v>
@@ -5668,13 +5668,13 @@
         <v>254</v>
       </c>
       <c r="B71" s="8">
-        <v>46237.36748915509</v>
+        <v>46237.53415582176</v>
       </c>
       <c r="C71" s="8">
-        <v>46246.643633784726</v>
+        <v>46246.81030045139</v>
       </c>
       <c r="D71" s="8">
-        <v>46246.64365295139</v>
+        <v>46246.81031961806</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>255</v>
@@ -5727,13 +5727,13 @@
         <v>258</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.55092376158</v>
+        <v>46073.71759042824</v>
       </c>
       <c r="C72" s="5">
-        <v>46247.464641377315</v>
+        <v>46247.63130804399</v>
       </c>
       <c r="D72" s="5">
-        <v>46247.4646434375</v>
+        <v>46247.63131010417</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5780,13 +5780,13 @@
         <v>261</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.55092408565</v>
+        <v>46073.71759075232</v>
       </c>
       <c r="C73" s="8">
-        <v>46246.64405420139</v>
+        <v>46246.81072086806</v>
       </c>
       <c r="D73" s="8">
-        <v>46246.64406856481</v>
+        <v>46246.810735231484</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>262</v>
@@ -5845,13 +5845,13 @@
         <v>266</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.55092435185</v>
+        <v>46073.71759101852</v>
       </c>
       <c r="C74" s="5">
-        <v>46237.38728393518</v>
+        <v>46237.553950601854</v>
       </c>
       <c r="D74" s="5">
-        <v>46246.644068912035</v>
+        <v>46246.81073557871</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>267</v>
@@ -5910,13 +5910,13 @@
         <v>270</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.550924641204</v>
+        <v>46073.71759130787</v>
       </c>
       <c r="C75" s="8">
-        <v>46246.6440794213</v>
+        <v>46246.81074608796</v>
       </c>
       <c r="D75" s="8">
-        <v>46246.64409572916</v>
+        <v>46246.810762395835</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>271</v>
@@ -5975,13 +5975,13 @@
         <v>273</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.55092489583</v>
+        <v>46073.7175915625</v>
       </c>
       <c r="C76" s="5">
-        <v>46246.644119398145</v>
+        <v>46246.810786064816</v>
       </c>
       <c r="D76" s="5">
-        <v>46246.644135532406</v>
+        <v>46246.81080219908</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>274</v>
@@ -6038,11 +6038,11 @@
         <v>276</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.55092517361</v>
+        <v>46073.71759184028</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46091.56779884259</v>
+        <v>46091.73446550926</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>277</v>
@@ -6091,11 +6091,11 @@
         <v>279</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.55092543981</v>
+        <v>46073.71759210648</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46246.64413799769</v>
+        <v>46246.81080466435</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>280</v>
@@ -6154,11 +6154,11 @@
         <v>283</v>
       </c>
       <c r="B79" s="8">
-        <v>46073.55092571759</v>
+        <v>46073.71759238426</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46246.64413840278</v>
+        <v>46246.81080506944</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>284</v>

--- a/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
+++ b/data/50001498 - CALABRESSE METRO STO DOMINGO POZOS.xlsx
@@ -3475,7 +3475,7 @@
         <v>46191.888280127314</v>
       </c>
       <c r="D36" s="5">
-        <v>46246.81058185185</v>
+        <v>46263.39095371528</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
